--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -119,60 +119,60 @@
     <t>ハンター</t>
   </si>
   <si>
+    <t>Armor</t>
+  </si>
+  <si>
+    <t>ウィザード</t>
+  </si>
+  <si>
+    <t>Seacher</t>
+  </si>
+  <si>
+    <t>白</t>
+  </si>
+  <si>
+    <t>ホワイトナイト</t>
+  </si>
+  <si>
+    <t>Shiled</t>
+  </si>
+  <si>
+    <t>ホブリタイ</t>
+  </si>
+  <si>
+    <t>Dryad</t>
+  </si>
+  <si>
+    <t>ウィッチ</t>
+  </si>
+  <si>
+    <t>Scorpion</t>
+  </si>
+  <si>
+    <t>ソルジャー</t>
+  </si>
+  <si>
+    <t>Squid</t>
+  </si>
+  <si>
+    <t>グリフォンナイト</t>
+  </si>
+  <si>
     <t>NY_CJ_monster_010_3</t>
   </si>
   <si>
-    <t>ウィザード</t>
-  </si>
-  <si>
-    <t>Seacher</t>
-  </si>
-  <si>
-    <t>白</t>
-  </si>
-  <si>
-    <t>ホワイトナイト</t>
-  </si>
-  <si>
-    <t>Shiled</t>
-  </si>
-  <si>
-    <t>ホブリタイ</t>
-  </si>
-  <si>
-    <t>Dryad</t>
-  </si>
-  <si>
-    <t>ウィッチ</t>
-  </si>
-  <si>
-    <t>Scorpion</t>
-  </si>
-  <si>
-    <t>ソルジャー</t>
-  </si>
-  <si>
-    <t>Squid</t>
-  </si>
-  <si>
-    <t>グリフォンナイト</t>
+    <t>シャーマン</t>
+  </si>
+  <si>
+    <t>Imp</t>
+  </si>
+  <si>
+    <t>クレリック</t>
   </si>
   <si>
     <t>Creeper</t>
   </si>
   <si>
-    <t>シャーマン</t>
-  </si>
-  <si>
-    <t>Imp</t>
-  </si>
-  <si>
-    <t>クレリック</t>
-  </si>
-  <si>
-    <t>Armor</t>
-  </si>
-  <si>
     <t>グラディエイター</t>
   </si>
   <si>
@@ -311,31 +311,31 @@
     <t>クロウ</t>
   </si>
   <si>
+    <t>ゴーストアーマー</t>
+  </si>
+  <si>
+    <t>サーチャー</t>
+  </si>
+  <si>
+    <t>シールド</t>
+  </si>
+  <si>
+    <t>ドライアド</t>
+  </si>
+  <si>
+    <t>スコーピオン</t>
+  </si>
+  <si>
+    <t>スクイッド</t>
+  </si>
+  <si>
     <t>ネームレス</t>
   </si>
   <si>
-    <t>サーチャー</t>
-  </si>
-  <si>
-    <t>シールド</t>
-  </si>
-  <si>
-    <t>ドライアド</t>
-  </si>
-  <si>
-    <t>スコーピオン</t>
-  </si>
-  <si>
-    <t>スクイッド</t>
+    <t>インプ</t>
   </si>
   <si>
     <t>クリーパー</t>
-  </si>
-  <si>
-    <t>インプ</t>
-  </si>
-  <si>
-    <t>ゴーストアーマー</t>
   </si>
   <si>
     <t>ソード</t>
@@ -460,9 +460,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -482,7 +482,37 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -503,81 +533,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -593,17 +549,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -618,10 +603,25 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -634,7 +634,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -646,7 +658,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -658,19 +736,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -682,49 +754,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -742,7 +772,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -754,67 +814,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -825,6 +825,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -844,36 +859,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -887,17 +882,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -925,6 +914,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -933,145 +933,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2496,7 +2496,7 @@
             <v>100210</v>
           </cell>
           <cell r="B167" t="str">
-            <v>アブソリュートパリィ</v>
+            <v>ピースメーカー</v>
           </cell>
         </row>
         <row r="168">
@@ -6822,11 +6822,11 @@
         <v>2</v>
       </c>
       <c r="B8">
-        <v>5020</v>
+        <v>15010</v>
       </c>
       <c r="C8" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B8,[1]TextData!A:A))</f>
-        <v>カウントジャグラー</v>
+        <v>ワンスパニッシュ</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -6846,11 +6846,11 @@
         <v>2</v>
       </c>
       <c r="B9">
-        <v>15010</v>
+        <v>3110</v>
       </c>
       <c r="C9" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B9,[1]TextData!A:A))</f>
-        <v>ワンスパニッシュ</v>
+        <v>ポイズン</v>
       </c>
       <c r="D9">
         <v>10</v>
@@ -6870,11 +6870,11 @@
         <v>2</v>
       </c>
       <c r="B10">
-        <v>15010</v>
+        <v>13020</v>
       </c>
       <c r="C10" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B10,[1]TextData!A:A))</f>
-        <v>ワンスパニッシュ</v>
+        <v>アイシクルエッジ</v>
       </c>
       <c r="D10">
         <v>15</v>
@@ -8022,11 +8022,11 @@
         <v>12</v>
       </c>
       <c r="B58">
-        <v>5030</v>
+        <v>5020</v>
       </c>
       <c r="C58" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B58,[1]TextData!A:A))</f>
-        <v>パッシブカース</v>
+        <v>カウントジャグラー</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="C120" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B120,[1]TextData!A:A))</f>
-        <v>アブソリュートパリィ</v>
+        <v>ピースメーカー</v>
       </c>
       <c r="D120">
         <v>1</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -460,9 +460,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -481,46 +481,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -528,14 +490,6 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -557,7 +511,38 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -571,18 +556,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -594,9 +579,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -610,10 +609,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -634,13 +634,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -652,7 +676,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -664,7 +730,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -676,13 +748,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -694,7 +772,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -706,91 +784,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -802,19 +808,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -825,6 +825,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -843,17 +867,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -875,33 +908,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -914,17 +925,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -933,145 +933,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -460,10 +460,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -482,6 +482,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -489,22 +503,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -519,6 +533,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -526,6 +556,21 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -548,9 +593,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -558,14 +611,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -578,52 +624,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -631,6 +631,30 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -646,7 +670,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -664,7 +694,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -676,13 +742,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -694,55 +754,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -760,13 +784,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -778,43 +814,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -843,11 +843,59 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -869,59 +917,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -933,145 +933,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -461,8 +461,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -482,14 +482,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -502,18 +495,57 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -524,16 +556,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -549,37 +589,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -587,7 +604,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -595,33 +619,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -634,7 +634,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -646,7 +778,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -658,13 +796,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -676,145 +814,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -825,6 +825,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -858,48 +867,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -925,6 +892,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -933,145 +933,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5601,40 +5601,40 @@
         <v>0</v>
       </c>
       <c r="G19">
+        <v>14</v>
+      </c>
+      <c r="H19">
+        <v>6</v>
+      </c>
+      <c r="I19">
+        <v>17</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>3</v>
+      </c>
+      <c r="L19">
+        <v>11</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>105</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>75</v>
+      </c>
+      <c r="Q19">
+        <v>40</v>
+      </c>
+      <c r="R19">
         <v>25</v>
-      </c>
-      <c r="H19">
-        <v>15</v>
-      </c>
-      <c r="I19">
-        <v>15</v>
-      </c>
-      <c r="J19">
-        <v>1</v>
-      </c>
-      <c r="K19">
-        <v>4</v>
-      </c>
-      <c r="L19">
-        <v>12</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>160</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>90</v>
-      </c>
-      <c r="Q19">
-        <v>35</v>
-      </c>
-      <c r="R19">
-        <v>60</v>
       </c>
       <c r="S19" t="s">
         <v>22</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -460,10 +460,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -489,7 +489,30 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -503,8 +526,60 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -520,14 +595,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -536,36 +611,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -578,52 +624,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -634,7 +634,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -646,13 +670,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -670,6 +688,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -682,13 +742,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -700,67 +802,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -772,49 +814,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -825,6 +825,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -852,36 +867,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -902,6 +887,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -916,15 +925,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -933,145 +933,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5542,13 +5542,13 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I18">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -5557,25 +5557,25 @@
         <v>3</v>
       </c>
       <c r="L18">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M18">
         <v>0</v>
       </c>
       <c r="N18">
-        <v>160</v>
+        <v>105</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q18">
         <v>40</v>
       </c>
       <c r="R18">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="S18" t="s">
         <v>28</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -185,18 +185,18 @@
     <t>Orga</t>
   </si>
   <si>
+    <t>Andras</t>
+  </si>
+  <si>
+    <t>Berith</t>
+  </si>
+  <si>
+    <t>Paimon</t>
+  </si>
+  <si>
     <t>Ammon</t>
   </si>
   <si>
-    <t>Berith</t>
-  </si>
-  <si>
-    <t>Paimon</t>
-  </si>
-  <si>
-    <t>Andras</t>
-  </si>
-  <si>
     <t>Bifrons</t>
   </si>
   <si>
@@ -344,16 +344,16 @@
     <t>オーガ</t>
   </si>
   <si>
+    <t>アンドラス</t>
+  </si>
+  <si>
+    <t>ベリト</t>
+  </si>
+  <si>
+    <t>パイモン</t>
+  </si>
+  <si>
     <t>アモン</t>
-  </si>
-  <si>
-    <t>ベリト</t>
-  </si>
-  <si>
-    <t>パイモン</t>
-  </si>
-  <si>
-    <t>アンドラス</t>
   </si>
   <si>
     <t>ビフロンス</t>
@@ -460,10 +460,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -478,13 +478,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -504,15 +497,37 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -520,6 +535,21 @@
     <font>
       <b/>
       <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -535,28 +565,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -564,22 +572,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -595,14 +588,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -611,15 +604,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -634,13 +634,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -658,7 +664,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -670,25 +790,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -700,109 +802,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -814,7 +814,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -829,16 +829,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -853,16 +853,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -902,15 +902,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -925,6 +916,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -933,145 +933,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2704,7 +2704,7 @@
             <v>200110</v>
           </cell>
           <cell r="B193" t="str">
-            <v>スリータイムス</v>
+            <v>ティアーズスクリプト</v>
           </cell>
         </row>
         <row r="194">
@@ -5477,7 +5477,7 @@
         <v>1</v>
       </c>
       <c r="E17">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -5533,7 +5533,7 @@
         <v>54</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E18">
         <v>100</v>
@@ -5542,19 +5542,19 @@
         <v>0</v>
       </c>
       <c r="G18">
+        <v>12</v>
+      </c>
+      <c r="H18">
+        <v>4</v>
+      </c>
+      <c r="I18">
         <v>14</v>
       </c>
-      <c r="H18">
-        <v>6</v>
-      </c>
-      <c r="I18">
-        <v>17</v>
-      </c>
       <c r="J18">
         <v>1</v>
       </c>
       <c r="K18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L18">
         <v>11</v>
@@ -5569,16 +5569,16 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="Q18">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="R18">
         <v>25</v>
       </c>
       <c r="S18" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -8550,11 +8550,11 @@
         <v>101</v>
       </c>
       <c r="B80">
-        <v>1010</v>
+        <v>2010</v>
       </c>
       <c r="C80" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B80,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -8574,11 +8574,11 @@
         <v>101</v>
       </c>
       <c r="B81">
-        <v>1110</v>
+        <v>2030</v>
       </c>
       <c r="C81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B81,[1]TextData!A:A))</f>
-        <v>バーンストーム</v>
+        <v>ロングスラスト</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -8598,17 +8598,17 @@
         <v>101</v>
       </c>
       <c r="B82">
-        <v>11040</v>
+        <v>4020</v>
       </c>
       <c r="C82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B82,[1]TextData!A:A))</f>
-        <v>ウルフソウル</v>
+        <v>ペネトレイト</v>
       </c>
       <c r="D82">
         <v>1</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -8646,11 +8646,11 @@
         <v>101</v>
       </c>
       <c r="B84">
-        <v>11120</v>
+        <v>14030</v>
       </c>
       <c r="C84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B84,[1]TextData!A:A))</f>
-        <v>パワーエール</v>
+        <v>ガードバインド</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="C85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B85,[1]TextData!A:A))</f>
-        <v>スリータイムス</v>
+        <v>ティアーズスクリプト</v>
       </c>
       <c r="D85">
         <v>1</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -461,9 +461,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -482,7 +482,59 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -496,25 +548,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -527,7 +565,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -542,14 +580,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -558,21 +603,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -588,38 +619,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -634,13 +634,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -652,7 +652,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -664,37 +664,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -712,7 +688,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -730,13 +706,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -748,31 +778,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -784,37 +790,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -839,15 +839,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -887,17 +878,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -917,11 +911,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -933,145 +933,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -6644,7 +6644,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G216"/>
+  <dimension ref="A1:G231"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="16.7272727272727" customWidth="1"/>
@@ -6750,17 +6750,17 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>13070</v>
+        <v>13040</v>
       </c>
       <c r="C5" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B5,[1]TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
+        <v>アーマーコード</v>
       </c>
       <c r="D5">
         <v>15</v>
       </c>
       <c r="E5">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -6774,17 +6774,17 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>403060</v>
+        <v>13070</v>
       </c>
       <c r="C6" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B6,[1]TextData!A:A))</f>
-        <v>バブルブロウ+</v>
+        <v>アシッドラッシュ</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -6795,20 +6795,20 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7">
-        <v>5010</v>
+        <v>403060</v>
       </c>
       <c r="C7" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B7,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>バブルブロウ+</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -6822,17 +6822,17 @@
         <v>2</v>
       </c>
       <c r="B8">
-        <v>15010</v>
+        <v>5010</v>
       </c>
       <c r="C8" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B8,[1]TextData!A:A))</f>
-        <v>ワンスパニッシュ</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -6846,17 +6846,17 @@
         <v>2</v>
       </c>
       <c r="B9">
-        <v>3110</v>
+        <v>15010</v>
       </c>
       <c r="C9" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B9,[1]TextData!A:A))</f>
-        <v>ポイズン</v>
+        <v>ワンスパニッシュ</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -6870,17 +6870,17 @@
         <v>2</v>
       </c>
       <c r="B10">
-        <v>13020</v>
+        <v>3110</v>
       </c>
       <c r="C10" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B10,[1]TextData!A:A))</f>
-        <v>アイシクルエッジ</v>
+        <v>ポイズン</v>
       </c>
       <c r="D10">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E10">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -6894,14 +6894,14 @@
         <v>2</v>
       </c>
       <c r="B11">
-        <v>415090</v>
+        <v>12040</v>
       </c>
       <c r="C11" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B11,[1]TextData!A:A))</f>
-        <v>クイックカース+</v>
+        <v>ヘブンリーラック</v>
       </c>
       <c r="D11">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6915,20 +6915,20 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12">
-        <v>2010</v>
+        <v>13020</v>
       </c>
       <c r="C12" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B12,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>アイシクルエッジ</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -6939,17 +6939,17 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13">
-        <v>12020</v>
+        <v>415090</v>
       </c>
       <c r="C13" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B13,[1]TextData!A:A))</f>
-        <v>ファストファクション</v>
+        <v>クイックカース+</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -6966,17 +6966,17 @@
         <v>3</v>
       </c>
       <c r="B14">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="C14" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B14,[1]TextData!A:A))</f>
-        <v>シャープエッジ</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E14">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -6990,17 +6990,17 @@
         <v>3</v>
       </c>
       <c r="B15">
-        <v>15030</v>
+        <v>12020</v>
       </c>
       <c r="C15" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B15,[1]TextData!A:A))</f>
-        <v>バイタリティ</v>
+        <v>ファストファクション</v>
       </c>
       <c r="D15">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -7014,17 +7014,17 @@
         <v>3</v>
       </c>
       <c r="B16">
-        <v>412020</v>
+        <v>2020</v>
       </c>
       <c r="C16" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B16,[1]TextData!A:A))</f>
-        <v>ヘブンリーラック+</v>
+        <v>シャープエッジ</v>
       </c>
       <c r="D16">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -7035,20 +7035,20 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17">
-        <v>1010</v>
+        <v>12030</v>
       </c>
       <c r="C17" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B17,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>クイックムーブ</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E17">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -7059,23 +7059,23 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18">
-        <v>1020</v>
+        <v>15030</v>
       </c>
       <c r="C18" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B18,[1]TextData!A:A))</f>
-        <v>フレイムクラッシュ</v>
+        <v>バイタリティ</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E18">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="F18">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -7083,23 +7083,23 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19">
-        <v>1110</v>
+        <v>412020</v>
       </c>
       <c r="C19" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B19,[1]TextData!A:A))</f>
-        <v>バーンストーム</v>
+        <v>ヘブンリーラック+</v>
       </c>
       <c r="D19">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>5121</v>
+        <v>0</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -7110,17 +7110,17 @@
         <v>4</v>
       </c>
       <c r="B20">
-        <v>11020</v>
+        <v>1010</v>
       </c>
       <c r="C20" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B20,[1]TextData!A:A))</f>
-        <v>イーグルアイ</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D20">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -7134,20 +7134,20 @@
         <v>4</v>
       </c>
       <c r="B21">
-        <v>401060</v>
+        <v>1020</v>
       </c>
       <c r="C21" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B21,[1]TextData!A:A))</f>
-        <v>イクスティンクション+</v>
+        <v>フレイムクラッシュ</v>
       </c>
       <c r="D21">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -7155,23 +7155,23 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B22">
-        <v>2010</v>
+        <v>1110</v>
       </c>
       <c r="C22" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B22,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>バーンストーム</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E22">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>5121</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -7179,17 +7179,17 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B23">
-        <v>12040</v>
+        <v>11040</v>
       </c>
       <c r="C23" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B23,[1]TextData!A:A))</f>
-        <v>ヘブンリーラック</v>
+        <v>ウルフソウル</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -7203,17 +7203,17 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24">
-        <v>12010</v>
+        <v>11020</v>
       </c>
       <c r="C24" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B24,[1]TextData!A:A))</f>
-        <v>クロースエッジ</v>
+        <v>イーグルアイ</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -7227,17 +7227,17 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B25">
-        <v>12140</v>
+        <v>401060</v>
       </c>
       <c r="C25" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B25,[1]TextData!A:A))</f>
-        <v>ウィンドライズ</v>
+        <v>イクスティンクション+</v>
       </c>
       <c r="D25">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -7254,17 +7254,17 @@
         <v>5</v>
       </c>
       <c r="B26">
-        <v>402030</v>
+        <v>2010</v>
       </c>
       <c r="C26" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B26,[1]TextData!A:A))</f>
-        <v>ショックインパルス+</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D26">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -7275,20 +7275,20 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B27">
-        <v>1010</v>
+        <v>12040</v>
       </c>
       <c r="C27" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B27,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>ヘブンリーラック</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -7299,17 +7299,17 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B28">
-        <v>11010</v>
+        <v>12010</v>
       </c>
       <c r="C28" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B28,[1]TextData!A:A))</f>
-        <v>フレイムセイバー</v>
+        <v>クロースエッジ</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -7323,17 +7323,17 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B29">
-        <v>13030</v>
+        <v>14040</v>
       </c>
       <c r="C29" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B29,[1]TextData!A:A))</f>
-        <v>カウンターマジック</v>
+        <v>ホープフルアイリス</v>
       </c>
       <c r="D29">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -7347,17 +7347,17 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B30">
-        <v>14010</v>
+        <v>12140</v>
       </c>
       <c r="C30" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B30,[1]TextData!A:A))</f>
-        <v>ファーストエイド</v>
+        <v>ウィンドライズ</v>
       </c>
       <c r="D30">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -7371,14 +7371,14 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B31">
-        <v>402060</v>
+        <v>402030</v>
       </c>
       <c r="C31" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B31,[1]TextData!A:A))</f>
-        <v>アーテニーストライク+</v>
+        <v>ショックインパルス+</v>
       </c>
       <c r="D31">
         <v>31</v>
@@ -7395,20 +7395,20 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B32">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B32,[1]TextData!A:A))</f>
-        <v>セイントレーザー</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="E32">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -7419,23 +7419,23 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B33">
-        <v>14030</v>
+        <v>11010</v>
       </c>
       <c r="C33" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B33,[1]TextData!A:A))</f>
-        <v>ガードバインド</v>
+        <v>フレイムセイバー</v>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
       <c r="E33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -7443,20 +7443,20 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B34">
-        <v>4130</v>
+        <v>13030</v>
       </c>
       <c r="C34" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B34,[1]TextData!A:A))</f>
-        <v>チャクラ</v>
+        <v>カウンターマジック</v>
       </c>
       <c r="D34">
         <v>10</v>
       </c>
       <c r="E34">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -7467,20 +7467,20 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B35">
-        <v>14120</v>
+        <v>11030</v>
       </c>
       <c r="C35" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B35,[1]TextData!A:A))</f>
-        <v>ファストメディック</v>
+        <v>ウォークライ</v>
       </c>
       <c r="D35">
         <v>15</v>
       </c>
       <c r="E35">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -7491,17 +7491,17 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B36">
-        <v>403070</v>
+        <v>14010</v>
       </c>
       <c r="C36" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B36,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>ファーストエイド</v>
       </c>
       <c r="D36">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -7515,20 +7515,20 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B37">
-        <v>3010</v>
+        <v>402060</v>
       </c>
       <c r="C37" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B37,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>アーテニーストライク+</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E37">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -7539,20 +7539,20 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B38">
-        <v>3030</v>
+        <v>4010</v>
       </c>
       <c r="C38" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B38,[1]TextData!A:A))</f>
-        <v>フレンジー</v>
+        <v>セイントレーザー</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -7563,23 +7563,23 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B39">
-        <v>13110</v>
+        <v>14030</v>
       </c>
       <c r="C39" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B39,[1]TextData!A:A))</f>
-        <v>ガーディアン</v>
+        <v>ガードバインド</v>
       </c>
       <c r="D39">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -7587,20 +7587,20 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B40">
-        <v>13130</v>
+        <v>4130</v>
       </c>
       <c r="C40" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B40,[1]TextData!A:A))</f>
-        <v>ライフスティール</v>
+        <v>チャクラ</v>
       </c>
       <c r="D40">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -7611,17 +7611,17 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B41">
-        <v>403020</v>
+        <v>14020</v>
       </c>
       <c r="C41" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B41,[1]TextData!A:A))</f>
-        <v>カウンターオーラ+</v>
+        <v>クイックヒール</v>
       </c>
       <c r="D41">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -7635,20 +7635,20 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B42">
-        <v>3010</v>
+        <v>14120</v>
       </c>
       <c r="C42" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B42,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>ファストメディック</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E42">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -7659,17 +7659,17 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B43">
-        <v>13020</v>
+        <v>403070</v>
       </c>
       <c r="C43" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B43,[1]TextData!A:A))</f>
-        <v>アイシクルエッジ</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -7683,20 +7683,20 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B44">
-        <v>15110</v>
+        <v>3010</v>
       </c>
       <c r="C44" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B44,[1]TextData!A:A))</f>
-        <v>フォーカサイト</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D44">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -7707,17 +7707,17 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B45">
-        <v>15030</v>
+        <v>3030</v>
       </c>
       <c r="C45" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B45,[1]TextData!A:A))</f>
-        <v>バイタリティ</v>
+        <v>フレンジー</v>
       </c>
       <c r="D45">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -7731,17 +7731,17 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B46">
-        <v>401040</v>
+        <v>13110</v>
       </c>
       <c r="C46" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B46,[1]TextData!A:A))</f>
-        <v>ソードアダプト+</v>
+        <v>ガーディアン</v>
       </c>
       <c r="D46">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -7755,20 +7755,20 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B47">
-        <v>2010</v>
+        <v>13040</v>
       </c>
       <c r="C47" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B47,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>アーマーコード</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E47">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -7779,20 +7779,20 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B48">
-        <v>2030</v>
+        <v>13130</v>
       </c>
       <c r="C48" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B48,[1]TextData!A:A))</f>
-        <v>ロングスラスト</v>
+        <v>ライフスティール</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E48">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -7803,17 +7803,17 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B49">
-        <v>12040</v>
+        <v>403020</v>
       </c>
       <c r="C49" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B49,[1]TextData!A:A))</f>
-        <v>ヘブンリーラック</v>
+        <v>カウンターオーラ+</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -7827,20 +7827,20 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B50">
-        <v>12030</v>
+        <v>3010</v>
       </c>
       <c r="C50" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B50,[1]TextData!A:A))</f>
-        <v>クイックムーブ</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D50">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -7851,17 +7851,17 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B51">
-        <v>412070</v>
+        <v>13020</v>
       </c>
       <c r="C51" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B51,[1]TextData!A:A))</f>
-        <v>ソーサリーコネクト+</v>
+        <v>アイシクルエッジ</v>
       </c>
       <c r="D51">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -7875,20 +7875,20 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B52">
-        <v>4010</v>
+        <v>15110</v>
       </c>
       <c r="C52" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B52,[1]TextData!A:A))</f>
-        <v>セイントレーザー</v>
+        <v>フォーカサイト</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E52">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -7899,23 +7899,23 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B53">
-        <v>4020</v>
+        <v>15030</v>
       </c>
       <c r="C53" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B53,[1]TextData!A:A))</f>
-        <v>ペネトレイト</v>
+        <v>バイタリティ</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E53">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>14213</v>
+        <v>0</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -7923,17 +7923,17 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B54">
-        <v>4110</v>
+        <v>15120</v>
       </c>
       <c r="C54" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B54,[1]TextData!A:A))</f>
-        <v>ダブルレーザー</v>
+        <v>ガードハント</v>
       </c>
       <c r="D54">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -7947,17 +7947,17 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B55">
-        <v>12050</v>
+        <v>401040</v>
       </c>
       <c r="C55" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B55,[1]TextData!A:A))</f>
-        <v>キュアスタン</v>
+        <v>ソードアダプト+</v>
       </c>
       <c r="D55">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -7971,20 +7971,20 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B56">
-        <v>403030</v>
+        <v>2010</v>
       </c>
       <c r="C56" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B56,[1]TextData!A:A))</f>
-        <v>ラインプロテクト+</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D56">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E56">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -7995,20 +7995,20 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B57">
-        <v>5010</v>
+        <v>2030</v>
       </c>
       <c r="C57" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B57,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>ロングスラスト</v>
       </c>
       <c r="D57">
         <v>1</v>
       </c>
       <c r="E57">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -8019,20 +8019,20 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B58">
-        <v>5020</v>
+        <v>12040</v>
       </c>
       <c r="C58" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B58,[1]TextData!A:A))</f>
-        <v>カウントジャグラー</v>
+        <v>ヘブンリーラック</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E58">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -8043,17 +8043,17 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B59">
-        <v>15020</v>
+        <v>12010</v>
       </c>
       <c r="C59" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B59,[1]TextData!A:A))</f>
-        <v>クイックカース</v>
+        <v>クロースエッジ</v>
       </c>
       <c r="D59">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -8067,17 +8067,17 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B60">
-        <v>15110</v>
+        <v>12030</v>
       </c>
       <c r="C60" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B60,[1]TextData!A:A))</f>
-        <v>フォーカサイト</v>
+        <v>クイックムーブ</v>
       </c>
       <c r="D60">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -8091,14 +8091,14 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B61">
-        <v>415010</v>
+        <v>412070</v>
       </c>
       <c r="C61" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B61,[1]TextData!A:A))</f>
-        <v>イーグルアイ+</v>
+        <v>ソーサリーコネクト+</v>
       </c>
       <c r="D61">
         <v>31</v>
@@ -8115,7 +8115,7 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B62">
         <v>4010</v>
@@ -8128,7 +8128,7 @@
         <v>1</v>
       </c>
       <c r="E62">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -8139,14 +8139,14 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B63">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="C63" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B63,[1]TextData!A:A))</f>
-        <v>ヒーリング</v>
+        <v>ペネトレイト</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -8155,7 +8155,7 @@
         <v>100</v>
       </c>
       <c r="F63">
-        <v>1033</v>
+        <v>14213</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -8163,14 +8163,14 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B64">
-        <v>13120</v>
+        <v>4110</v>
       </c>
       <c r="C64" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B64,[1]TextData!A:A))</f>
-        <v>ライフセーブ</v>
+        <v>ダブルレーザー</v>
       </c>
       <c r="D64">
         <v>10</v>
@@ -8187,14 +8187,14 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B65">
-        <v>14080</v>
+        <v>14030</v>
       </c>
       <c r="C65" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B65,[1]TextData!A:A))</f>
-        <v>ホーミングクルセイド</v>
+        <v>ガードバインド</v>
       </c>
       <c r="D65">
         <v>15</v>
@@ -8203,7 +8203,7 @@
         <v>0</v>
       </c>
       <c r="F65">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -8211,17 +8211,17 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B66">
-        <v>404030</v>
+        <v>12050</v>
       </c>
       <c r="C66" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B66,[1]TextData!A:A))</f>
-        <v>ヒーリング+</v>
+        <v>キュアスタン</v>
       </c>
       <c r="D66">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -8235,20 +8235,20 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B67">
-        <v>5010</v>
+        <v>403030</v>
       </c>
       <c r="C67" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B67,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>ラインプロテクト+</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E67">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -8259,20 +8259,20 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B68">
-        <v>5120</v>
+        <v>5010</v>
       </c>
       <c r="C68" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B68,[1]TextData!A:A))</f>
-        <v>ユーサネイジア</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D68">
         <v>1</v>
       </c>
       <c r="E68">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -8283,47 +8283,47 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B69">
-        <v>15040</v>
+        <v>5020</v>
       </c>
       <c r="C69" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B69,[1]TextData!A:A))</f>
-        <v>ネガティブドレイン</v>
+        <v>カウントジャグラー</v>
       </c>
       <c r="D69">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F69">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G69">
-        <v>1033</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B70">
-        <v>15120</v>
+        <v>15020</v>
       </c>
       <c r="C70" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B70,[1]TextData!A:A))</f>
-        <v>ガードハント</v>
+        <v>クイックカース</v>
       </c>
       <c r="D70">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E70">
         <v>0</v>
       </c>
       <c r="F70">
-        <v>1032</v>
+        <v>0</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -8331,17 +8331,17 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B71">
-        <v>401010</v>
+        <v>15040</v>
       </c>
       <c r="C71" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B71,[1]TextData!A:A))</f>
-        <v>ファイアボール+</v>
+        <v>ネガティブドレイン</v>
       </c>
       <c r="D71">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -8355,20 +8355,20 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B72">
-        <v>1010</v>
+        <v>15110</v>
       </c>
       <c r="C72" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B72,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>フォーカサイト</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E72">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -8379,17 +8379,17 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B73">
-        <v>11030</v>
+        <v>415010</v>
       </c>
       <c r="C73" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B73,[1]TextData!A:A))</f>
-        <v>ウォークライ</v>
+        <v>イーグルアイ+</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -8403,23 +8403,23 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B74">
-        <v>1120</v>
+        <v>4010</v>
       </c>
       <c r="C74" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B74,[1]TextData!A:A))</f>
-        <v>イクスティンクション</v>
+        <v>セイントレーザー</v>
       </c>
       <c r="D74">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E74">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F74">
-        <v>9031</v>
+        <v>0</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -8427,23 +8427,23 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B75">
-        <v>11110</v>
+        <v>4030</v>
       </c>
       <c r="C75" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B75,[1]TextData!A:A))</f>
-        <v>レイジカウンター</v>
+        <v>ヒーリング</v>
       </c>
       <c r="D75">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -8451,17 +8451,17 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B76">
-        <v>401050</v>
+        <v>13120</v>
       </c>
       <c r="C76" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B76,[1]TextData!A:A))</f>
-        <v>フレイムレイン+</v>
+        <v>ライフセーブ</v>
       </c>
       <c r="D76">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -8475,20 +8475,20 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="B77">
-        <v>1010</v>
+        <v>14010</v>
       </c>
       <c r="C77" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B77,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>ファーストエイド</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E77">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -8499,23 +8499,23 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="B78">
-        <v>1110</v>
+        <v>14080</v>
       </c>
       <c r="C78" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B78,[1]TextData!A:A))</f>
-        <v>バーンストーム</v>
+        <v>ホーミングクルセイド</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E78">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -8523,17 +8523,17 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="B79">
-        <v>11130</v>
+        <v>404030</v>
       </c>
       <c r="C79" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B79,[1]TextData!A:A))</f>
-        <v>ワイドカウンター</v>
+        <v>ヒーリング+</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -8547,20 +8547,20 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="B80">
-        <v>2010</v>
+        <v>5010</v>
       </c>
       <c r="C80" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B80,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D80">
         <v>1</v>
       </c>
       <c r="E80">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -8571,20 +8571,20 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="B81">
-        <v>2030</v>
+        <v>5120</v>
       </c>
       <c r="C81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B81,[1]TextData!A:A))</f>
-        <v>ロングスラスト</v>
+        <v>ユーサネイジア</v>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="E81">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -8595,41 +8595,41 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="B82">
-        <v>4020</v>
+        <v>15040</v>
       </c>
       <c r="C82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B82,[1]TextData!A:A))</f>
-        <v>ペネトレイト</v>
+        <v>ネガティブドレイン</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E82">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G82">
-        <v>0</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="B83">
-        <v>12130</v>
+        <v>15030</v>
       </c>
       <c r="C83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B83,[1]TextData!A:A))</f>
-        <v>チェイスマジック</v>
+        <v>バイタリティ</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -8643,23 +8643,23 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="B84">
-        <v>14030</v>
+        <v>15120</v>
       </c>
       <c r="C84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B84,[1]TextData!A:A))</f>
-        <v>ガードバインド</v>
+        <v>ガードハント</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E84">
         <v>0</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8667,17 +8667,17 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="B85">
-        <v>200110</v>
+        <v>401010</v>
       </c>
       <c r="C85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B85,[1]TextData!A:A))</f>
-        <v>ティアーズスクリプト</v>
+        <v>ファイアボール+</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -8691,20 +8691,20 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="B86">
-        <v>200120</v>
+        <v>1010</v>
       </c>
       <c r="C86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B86,[1]TextData!A:A))</f>
-        <v>アングリークライ</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
       <c r="E86">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -8715,20 +8715,20 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="B87">
-        <v>5010</v>
+        <v>11030</v>
       </c>
       <c r="C87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B87,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>ウォークライ</v>
       </c>
       <c r="D87">
         <v>1</v>
       </c>
       <c r="E87">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -8739,23 +8739,23 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="B88">
-        <v>5020</v>
+        <v>1120</v>
       </c>
       <c r="C88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B88,[1]TextData!A:A))</f>
-        <v>カウントジャグラー</v>
+        <v>イクスティンクション</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E88">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F88">
-        <v>1013</v>
+        <v>9031</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8763,17 +8763,17 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="B89">
-        <v>15050</v>
+        <v>15040</v>
       </c>
       <c r="C89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B89,[1]TextData!A:A))</f>
-        <v>キュアシェイド</v>
+        <v>ネガティブドレイン</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -8787,17 +8787,17 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="B90">
-        <v>200210</v>
+        <v>11110</v>
       </c>
       <c r="C90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B90,[1]TextData!A:A))</f>
-        <v>マイトレインフォース</v>
+        <v>レイジカウンター</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -8811,20 +8811,20 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="B91">
-        <v>200220</v>
+        <v>401050</v>
       </c>
       <c r="C91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B91,[1]TextData!A:A))</f>
-        <v>カタストロフィ</v>
+        <v>フレイムレイン+</v>
       </c>
       <c r="D91">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="E91">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -8835,20 +8835,20 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="B92">
-        <v>200230</v>
+        <v>1010</v>
       </c>
       <c r="C92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B92,[1]TextData!A:A))</f>
-        <v>悪魔(ベリト)</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D92">
         <v>1</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -8859,20 +8859,20 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="B93">
-        <v>4010</v>
+        <v>1110</v>
       </c>
       <c r="C93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B93,[1]TextData!A:A))</f>
-        <v>セイントレーザー</v>
+        <v>バーンストーム</v>
       </c>
       <c r="D93">
         <v>1</v>
       </c>
       <c r="E93">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -8883,23 +8883,23 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="B94">
-        <v>4030</v>
+        <v>11130</v>
       </c>
       <c r="C94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B94,[1]TextData!A:A))</f>
-        <v>ヒーリング</v>
+        <v>ワイドカウンター</v>
       </c>
       <c r="D94">
         <v>1</v>
       </c>
       <c r="E94">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F94">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8907,23 +8907,23 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B95">
-        <v>14080</v>
+        <v>2010</v>
       </c>
       <c r="C95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B95,[1]TextData!A:A))</f>
-        <v>ホーミングクルセイド</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D95">
         <v>1</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F95">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -8931,20 +8931,20 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B96">
-        <v>200310</v>
+        <v>2030</v>
       </c>
       <c r="C96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B96,[1]TextData!A:A))</f>
-        <v>プルガシオン</v>
+        <v>ロングスラスト</v>
       </c>
       <c r="D96">
         <v>1</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -8955,20 +8955,20 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B97">
-        <v>200320</v>
+        <v>4020</v>
       </c>
       <c r="C97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B97,[1]TextData!A:A))</f>
-        <v>プリエステス</v>
+        <v>ペネトレイト</v>
       </c>
       <c r="D97">
         <v>1</v>
       </c>
       <c r="E97">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -8979,14 +8979,14 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B98">
-        <v>200330</v>
+        <v>12130</v>
       </c>
       <c r="C98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B98,[1]TextData!A:A))</f>
-        <v>悪魔(パイモン)</v>
+        <v>チェイスマジック</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -9003,20 +9003,20 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B99">
-        <v>2010</v>
+        <v>14030</v>
       </c>
       <c r="C99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B99,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>ガードバインド</v>
       </c>
       <c r="D99">
         <v>1</v>
       </c>
       <c r="E99">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F99">
         <v>0</v>
@@ -9027,14 +9027,14 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B100">
-        <v>200410</v>
+        <v>200110</v>
       </c>
       <c r="C100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B100,[1]TextData!A:A))</f>
-        <v>コウソクテンショウ</v>
+        <v>ティアーズスクリプト</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -9051,23 +9051,23 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B101">
-        <v>200420</v>
+        <v>200120</v>
       </c>
       <c r="C101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B101,[1]TextData!A:A))</f>
-        <v>アンチバフ</v>
+        <v>アングリークライ</v>
       </c>
       <c r="D101">
         <v>1</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F101">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -9075,20 +9075,20 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B102">
-        <v>200430</v>
+        <v>5010</v>
       </c>
       <c r="C102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B102,[1]TextData!A:A))</f>
-        <v>悪魔(アンドラス)</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D102">
         <v>1</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -9099,23 +9099,23 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B103">
-        <v>3010</v>
+        <v>5020</v>
       </c>
       <c r="C103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B103,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>カウントジャグラー</v>
       </c>
       <c r="D103">
         <v>1</v>
       </c>
       <c r="E103">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F103">
-        <v>0</v>
+        <v>1013</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -9123,20 +9123,20 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B104">
-        <v>3070</v>
+        <v>15050</v>
       </c>
       <c r="C104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B104,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>キュアシェイド</v>
       </c>
       <c r="D104">
         <v>1</v>
       </c>
       <c r="E104">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -9147,14 +9147,14 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B105">
-        <v>200510</v>
+        <v>200210</v>
       </c>
       <c r="C105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B105,[1]TextData!A:A))</f>
-        <v>カウントダウン</v>
+        <v>マイトレインフォース</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -9171,20 +9171,20 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B106">
-        <v>200520</v>
+        <v>200220</v>
       </c>
       <c r="C106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B106,[1]TextData!A:A))</f>
-        <v>グラウンドゼロ</v>
+        <v>カタストロフィ</v>
       </c>
       <c r="D106">
         <v>1</v>
       </c>
       <c r="E106">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -9195,14 +9195,14 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B107">
-        <v>200530</v>
+        <v>200230</v>
       </c>
       <c r="C107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B107,[1]TextData!A:A))</f>
-        <v>悪魔(ビフロンス)</v>
+        <v>悪魔(ベリト)</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -9219,20 +9219,20 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B108">
-        <v>403070</v>
+        <v>4010</v>
       </c>
       <c r="C108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B108,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>セイントレーザー</v>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -9243,23 +9243,23 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109">
-        <v>201</v>
+        <v>103</v>
       </c>
       <c r="B109">
-        <v>4010</v>
+        <v>4030</v>
       </c>
       <c r="C109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B109,[1]TextData!A:A))</f>
-        <v>セイントレーザー</v>
+        <v>ヒーリング</v>
       </c>
       <c r="D109">
         <v>1</v>
       </c>
       <c r="E109">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -9267,23 +9267,23 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110">
-        <v>1001</v>
+        <v>103</v>
       </c>
       <c r="B110">
-        <v>1010</v>
+        <v>14080</v>
       </c>
       <c r="C110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B110,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>ホーミングクルセイド</v>
       </c>
       <c r="D110">
         <v>1</v>
       </c>
       <c r="E110">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F110">
-        <v>5061</v>
+        <v>1033</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -9291,23 +9291,23 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111">
-        <v>1001</v>
+        <v>103</v>
       </c>
       <c r="B111">
-        <v>1060</v>
+        <v>200310</v>
       </c>
       <c r="C111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B111,[1]TextData!A:A))</f>
-        <v>フレイムレイン</v>
+        <v>プルガシオン</v>
       </c>
       <c r="D111">
         <v>1</v>
       </c>
       <c r="E111">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F111">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -9315,20 +9315,20 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112">
-        <v>1001</v>
+        <v>103</v>
       </c>
       <c r="B112">
-        <v>100110</v>
+        <v>200320</v>
       </c>
       <c r="C112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B112,[1]TextData!A:A))</f>
-        <v>ソーイングアームド</v>
+        <v>プリエステス</v>
       </c>
       <c r="D112">
         <v>1</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -9339,20 +9339,20 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113">
-        <v>1001</v>
+        <v>103</v>
       </c>
       <c r="B113">
-        <v>100120</v>
+        <v>200330</v>
       </c>
       <c r="C113" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B113,[1]TextData!A:A))</f>
-        <v>エターナルロンド</v>
+        <v>悪魔(パイモン)</v>
       </c>
       <c r="D113">
         <v>1</v>
       </c>
       <c r="E113">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -9363,20 +9363,20 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114">
-        <v>1001</v>
+        <v>104</v>
       </c>
       <c r="B114">
-        <v>11060</v>
+        <v>2010</v>
       </c>
       <c r="C114" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B114,[1]TextData!A:A))</f>
-        <v>キュアファイア</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D114">
         <v>1</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -9387,14 +9387,14 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115">
-        <v>1001</v>
+        <v>104</v>
       </c>
       <c r="B115">
-        <v>14010</v>
+        <v>200410</v>
       </c>
       <c r="C115" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B115,[1]TextData!A:A))</f>
-        <v>ファーストエイド</v>
+        <v>コウソクテンショウ</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -9411,14 +9411,14 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116">
-        <v>1001</v>
+        <v>104</v>
       </c>
       <c r="B116">
-        <v>12010</v>
+        <v>200420</v>
       </c>
       <c r="C116" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B116,[1]TextData!A:A))</f>
-        <v>クロースエッジ</v>
+        <v>アンチバフ</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -9427,7 +9427,7 @@
         <v>0</v>
       </c>
       <c r="F116">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -9435,14 +9435,14 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117">
-        <v>1001</v>
+        <v>104</v>
       </c>
       <c r="B117">
-        <v>12060</v>
+        <v>200430</v>
       </c>
       <c r="C117" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B117,[1]TextData!A:A))</f>
-        <v>キュアスタン</v>
+        <v>悪魔(アンドラス)</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -9459,23 +9459,23 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118">
-        <v>1002</v>
+        <v>105</v>
       </c>
       <c r="B118">
-        <v>2010</v>
+        <v>3010</v>
       </c>
       <c r="C118" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B118,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D118">
         <v>1</v>
       </c>
       <c r="E118">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F118">
-        <v>5060</v>
+        <v>0</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -9483,20 +9483,20 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119">
-        <v>1002</v>
+        <v>105</v>
       </c>
       <c r="B119">
-        <v>2070</v>
+        <v>3070</v>
       </c>
       <c r="C119" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B119,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D119">
         <v>1</v>
       </c>
       <c r="E119">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="F119">
         <v>0</v>
@@ -9507,14 +9507,14 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120">
-        <v>1002</v>
+        <v>105</v>
       </c>
       <c r="B120">
-        <v>100210</v>
+        <v>200510</v>
       </c>
       <c r="C120" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B120,[1]TextData!A:A))</f>
-        <v>ピースメーカー</v>
+        <v>カウントダウン</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -9531,38 +9531,38 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121">
-        <v>1002</v>
+        <v>105</v>
       </c>
       <c r="B121">
-        <v>100220</v>
+        <v>200520</v>
       </c>
       <c r="C121" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B121,[1]TextData!A:A))</f>
-        <v>レヴェリー</v>
+        <v>グラウンドゼロ</v>
       </c>
       <c r="D121">
         <v>1</v>
       </c>
       <c r="E121">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F121">
-        <v>14211</v>
+        <v>0</v>
       </c>
       <c r="G121">
-        <v>5060</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122">
-        <v>1002</v>
+        <v>105</v>
       </c>
       <c r="B122">
-        <v>402070</v>
+        <v>200530</v>
       </c>
       <c r="C122" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B122,[1]TextData!A:A))</f>
-        <v>コンセントレイト+</v>
+        <v>悪魔(ビフロンス)</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -9579,14 +9579,14 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123">
-        <v>1002</v>
+        <v>105</v>
       </c>
       <c r="B123">
-        <v>12080</v>
+        <v>403070</v>
       </c>
       <c r="C123" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B123,[1]TextData!A:A))</f>
-        <v>ソーサリーコネクト</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -9603,20 +9603,20 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124">
-        <v>1002</v>
+        <v>201</v>
       </c>
       <c r="B124">
-        <v>12040</v>
+        <v>4010</v>
       </c>
       <c r="C124" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B124,[1]TextData!A:A))</f>
-        <v>ヘブンリーラック</v>
+        <v>セイントレーザー</v>
       </c>
       <c r="D124">
         <v>1</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F124">
         <v>0</v>
@@ -9627,23 +9627,23 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B125">
-        <v>12050</v>
+        <v>1010</v>
       </c>
       <c r="C125" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B125,[1]TextData!A:A))</f>
-        <v>キュアスタン</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D125">
         <v>1</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -9651,23 +9651,23 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B126">
-        <v>12010</v>
+        <v>1060</v>
       </c>
       <c r="C126" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B126,[1]TextData!A:A))</f>
-        <v>クロースエッジ</v>
+        <v>フレイムレイン</v>
       </c>
       <c r="D126">
         <v>1</v>
       </c>
       <c r="E126">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -9675,20 +9675,20 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B127">
-        <v>3010</v>
+        <v>100110</v>
       </c>
       <c r="C127" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B127,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>ソーイングアームド</v>
       </c>
       <c r="D127">
         <v>1</v>
       </c>
       <c r="E127">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -9699,23 +9699,23 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B128">
-        <v>3020</v>
+        <v>100120</v>
       </c>
       <c r="C128" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B128,[1]TextData!A:A))</f>
-        <v>シールドバッシュ</v>
+        <v>エターナルロンド</v>
       </c>
       <c r="D128">
         <v>1</v>
       </c>
       <c r="E128">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F128">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G128">
         <v>0</v>
@@ -9723,14 +9723,14 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B129">
-        <v>100310</v>
+        <v>11060</v>
       </c>
       <c r="C129" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B129,[1]TextData!A:A))</f>
-        <v>セイクリッドバリア</v>
+        <v>キュアファイア</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -9747,23 +9747,23 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B130">
-        <v>100320</v>
+        <v>14010</v>
       </c>
       <c r="C130" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B130,[1]TextData!A:A))</f>
-        <v>リベンジニードル</v>
+        <v>ファーストエイド</v>
       </c>
       <c r="D130">
         <v>1</v>
       </c>
       <c r="E130">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F130">
-        <v>14214</v>
+        <v>0</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -9771,14 +9771,14 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B131">
-        <v>403020</v>
+        <v>12010</v>
       </c>
       <c r="C131" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B131,[1]TextData!A:A))</f>
-        <v>カウンターオーラ+</v>
+        <v>クロースエッジ</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -9795,14 +9795,14 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B132">
-        <v>403010</v>
+        <v>12060</v>
       </c>
       <c r="C132" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B132,[1]TextData!A:A))</f>
-        <v>アイスブレイド+</v>
+        <v>キュアスタン</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -9819,23 +9819,23 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B133">
-        <v>13020</v>
+        <v>2010</v>
       </c>
       <c r="C133" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B133,[1]TextData!A:A))</f>
-        <v>アイシクルエッジ</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D133">
         <v>1</v>
       </c>
       <c r="E133">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F133">
-        <v>0</v>
+        <v>5060</v>
       </c>
       <c r="G133">
         <v>0</v>
@@ -9843,20 +9843,20 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B134">
-        <v>13080</v>
+        <v>2070</v>
       </c>
       <c r="C134" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B134,[1]TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D134">
         <v>1</v>
       </c>
       <c r="E134">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -9867,14 +9867,14 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B135">
-        <v>14050</v>
+        <v>100210</v>
       </c>
       <c r="C135" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B135,[1]TextData!A:A))</f>
-        <v>キュアパッシブ</v>
+        <v>ピースメーカー</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -9891,47 +9891,47 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B136">
-        <v>4010</v>
+        <v>100220</v>
       </c>
       <c r="C136" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B136,[1]TextData!A:A))</f>
-        <v>セイントレーザー</v>
+        <v>レヴェリー</v>
       </c>
       <c r="D136">
         <v>1</v>
       </c>
       <c r="E136">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F136">
-        <v>0</v>
+        <v>14211</v>
       </c>
       <c r="G136">
-        <v>0</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B137">
-        <v>4030</v>
+        <v>402070</v>
       </c>
       <c r="C137" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B137,[1]TextData!A:A))</f>
-        <v>ヒーリング</v>
+        <v>コンセントレイト+</v>
       </c>
       <c r="D137">
         <v>1</v>
       </c>
       <c r="E137">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F137">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G137">
         <v>0</v>
@@ -9939,14 +9939,14 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B138">
-        <v>100410</v>
+        <v>12080</v>
       </c>
       <c r="C138" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B138,[1]TextData!A:A))</f>
-        <v>アバンデンス</v>
+        <v>ソーサリーコネクト</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -9963,20 +9963,20 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B139">
-        <v>100420</v>
+        <v>12040</v>
       </c>
       <c r="C139" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B139,[1]TextData!A:A))</f>
-        <v>ハーヴェスト</v>
+        <v>ヘブンリーラック</v>
       </c>
       <c r="D139">
         <v>1</v>
       </c>
       <c r="E139">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -9987,14 +9987,14 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B140">
-        <v>404030</v>
+        <v>12050</v>
       </c>
       <c r="C140" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B140,[1]TextData!A:A))</f>
-        <v>ヒーリング+</v>
+        <v>キュアスタン</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -10011,14 +10011,14 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B141">
-        <v>14080</v>
+        <v>12010</v>
       </c>
       <c r="C141" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B141,[1]TextData!A:A))</f>
-        <v>ホーミングクルセイド</v>
+        <v>クロースエッジ</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -10035,23 +10035,23 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B142">
-        <v>14010</v>
+        <v>3010</v>
       </c>
       <c r="C142" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B142,[1]TextData!A:A))</f>
-        <v>ファーストエイド</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D142">
         <v>1</v>
       </c>
       <c r="E142">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F142">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G142">
         <v>0</v>
@@ -10059,23 +10059,23 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B143">
-        <v>14040</v>
+        <v>3020</v>
       </c>
       <c r="C143" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B143,[1]TextData!A:A))</f>
-        <v>ホープフルアイリス</v>
+        <v>シールドバッシュ</v>
       </c>
       <c r="D143">
         <v>1</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G143">
         <v>0</v>
@@ -10083,14 +10083,14 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B144">
-        <v>14090</v>
+        <v>100310</v>
       </c>
       <c r="C144" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B144,[1]TextData!A:A))</f>
-        <v>リレイズ</v>
+        <v>セイクリッドバリア</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -10107,23 +10107,23 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B145">
-        <v>5010</v>
+        <v>100320</v>
       </c>
       <c r="C145" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B145,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>リベンジニードル</v>
       </c>
       <c r="D145">
         <v>1</v>
       </c>
       <c r="E145">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>14214</v>
       </c>
       <c r="G145">
         <v>0</v>
@@ -10131,23 +10131,23 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B146">
-        <v>5070</v>
+        <v>403020</v>
       </c>
       <c r="C146" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B146,[1]TextData!A:A))</f>
-        <v>ダークネス</v>
+        <v>カウンターオーラ+</v>
       </c>
       <c r="D146">
         <v>1</v>
       </c>
       <c r="E146">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F146">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G146">
         <v>0</v>
@@ -10155,14 +10155,14 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B147">
-        <v>100510</v>
+        <v>403010</v>
       </c>
       <c r="C147" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B147,[1]TextData!A:A))</f>
-        <v>カースドブレイク</v>
+        <v>アイスブレイド+</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -10179,20 +10179,20 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B148">
-        <v>100520</v>
+        <v>13020</v>
       </c>
       <c r="C148" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B148,[1]TextData!A:A))</f>
-        <v>ムーンライトレイ</v>
+        <v>アイシクルエッジ</v>
       </c>
       <c r="D148">
         <v>1</v>
       </c>
       <c r="E148">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F148">
         <v>0</v>
@@ -10203,14 +10203,14 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B149">
-        <v>15090</v>
+        <v>13080</v>
       </c>
       <c r="C149" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B149,[1]TextData!A:A))</f>
-        <v>ヒールハント</v>
+        <v>アシッドラッシュ</v>
       </c>
       <c r="D149">
         <v>1</v>
@@ -10227,14 +10227,14 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B150">
-        <v>405070</v>
+        <v>14050</v>
       </c>
       <c r="C150" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B150,[1]TextData!A:A))</f>
-        <v>シェイディークラウド+</v>
+        <v>キュアパッシブ</v>
       </c>
       <c r="D150">
         <v>1</v>
@@ -10251,20 +10251,20 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B151">
-        <v>15080</v>
+        <v>4010</v>
       </c>
       <c r="C151" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B151,[1]TextData!A:A))</f>
-        <v>ヒールハント</v>
+        <v>セイントレーザー</v>
       </c>
       <c r="D151">
         <v>1</v>
       </c>
       <c r="E151">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F151">
         <v>0</v>
@@ -10275,23 +10275,23 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B152">
-        <v>405010</v>
+        <v>4030</v>
       </c>
       <c r="C152" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B152,[1]TextData!A:A))</f>
-        <v>ダークプリズン+</v>
+        <v>ヒーリング</v>
       </c>
       <c r="D152">
         <v>1</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F152">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -10299,14 +10299,14 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B153">
-        <v>415090</v>
+        <v>100410</v>
       </c>
       <c r="C153" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B153,[1]TextData!A:A))</f>
-        <v>クイックカース+</v>
+        <v>アバンデンス</v>
       </c>
       <c r="D153">
         <v>1</v>
@@ -10323,20 +10323,20 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B154">
-        <v>1010</v>
+        <v>100420</v>
       </c>
       <c r="C154" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B154,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>ハーヴェスト</v>
       </c>
       <c r="D154">
         <v>1</v>
       </c>
       <c r="E154">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -10347,47 +10347,47 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B155">
-        <v>1030</v>
+        <v>404030</v>
       </c>
       <c r="C155" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B155,[1]TextData!A:A))</f>
-        <v>ブレイクウォール</v>
+        <v>ヒーリング+</v>
       </c>
       <c r="D155">
         <v>1</v>
       </c>
       <c r="E155">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F155">
-        <v>9120</v>
+        <v>0</v>
       </c>
       <c r="G155">
-        <v>1023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B156">
-        <v>1070</v>
+        <v>14080</v>
       </c>
       <c r="C156" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B156,[1]TextData!A:A))</f>
-        <v>バーニングソウル</v>
+        <v>ホーミングクルセイド</v>
       </c>
       <c r="D156">
         <v>1</v>
       </c>
       <c r="E156">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F156">
-        <v>6322</v>
+        <v>0</v>
       </c>
       <c r="G156">
         <v>0</v>
@@ -10395,14 +10395,14 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B157">
-        <v>100610</v>
+        <v>14010</v>
       </c>
       <c r="C157" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B157,[1]TextData!A:A))</f>
-        <v>サンフレイム</v>
+        <v>ファーストエイド</v>
       </c>
       <c r="D157">
         <v>1</v>
@@ -10411,7 +10411,7 @@
         <v>0</v>
       </c>
       <c r="F157">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G157">
         <v>0</v>
@@ -10419,20 +10419,20 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B158">
-        <v>100620</v>
+        <v>14040</v>
       </c>
       <c r="C158" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B158,[1]TextData!A:A))</f>
-        <v>フレイムタン</v>
+        <v>ホープフルアイリス</v>
       </c>
       <c r="D158">
         <v>1</v>
       </c>
       <c r="E158">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -10443,14 +10443,14 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B159">
-        <v>11040</v>
+        <v>14090</v>
       </c>
       <c r="C159" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B159,[1]TextData!A:A))</f>
-        <v>ウルフソウル</v>
+        <v>リレイズ</v>
       </c>
       <c r="D159">
         <v>1</v>
@@ -10459,7 +10459,7 @@
         <v>0</v>
       </c>
       <c r="F159">
-        <v>5042</v>
+        <v>0</v>
       </c>
       <c r="G159">
         <v>0</v>
@@ -10467,20 +10467,20 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B160">
-        <v>401030</v>
+        <v>5010</v>
       </c>
       <c r="C160" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B160,[1]TextData!A:A))</f>
-        <v>ヒートスタンプ+</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D160">
         <v>1</v>
       </c>
       <c r="E160">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -10491,23 +10491,23 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B161">
-        <v>411040</v>
+        <v>5070</v>
       </c>
       <c r="C161" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B161,[1]TextData!A:A))</f>
-        <v>アクティブギフト+</v>
+        <v>ダークネス</v>
       </c>
       <c r="D161">
         <v>1</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F161">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G161">
         <v>0</v>
@@ -10515,14 +10515,14 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B162">
-        <v>13040</v>
+        <v>100510</v>
       </c>
       <c r="C162" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B162,[1]TextData!A:A))</f>
-        <v>アーマーコード</v>
+        <v>カースドブレイク</v>
       </c>
       <c r="D162">
         <v>1</v>
@@ -10539,20 +10539,20 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B163">
-        <v>2010</v>
+        <v>100520</v>
       </c>
       <c r="C163" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B163,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>ムーンライトレイ</v>
       </c>
       <c r="D163">
         <v>1</v>
       </c>
       <c r="E163">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F163">
         <v>0</v>
@@ -10563,23 +10563,23 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B164">
-        <v>2040</v>
+        <v>15090</v>
       </c>
       <c r="C164" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B164,[1]TextData!A:A))</f>
-        <v>トラストチェイン</v>
+        <v>ヒールハント</v>
       </c>
       <c r="D164">
         <v>1</v>
       </c>
       <c r="E164">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F164">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G164">
         <v>0</v>
@@ -10587,14 +10587,14 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B165">
-        <v>100710</v>
+        <v>405070</v>
       </c>
       <c r="C165" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B165,[1]TextData!A:A))</f>
-        <v>ライズザフラッグ</v>
+        <v>シェイディークラウド+</v>
       </c>
       <c r="D165">
         <v>1</v>
@@ -10611,20 +10611,20 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B166">
-        <v>100720</v>
+        <v>15080</v>
       </c>
       <c r="C166" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B166,[1]TextData!A:A))</f>
-        <v>オーバーリミット</v>
+        <v>ヒールハント</v>
       </c>
       <c r="D166">
         <v>1</v>
       </c>
       <c r="E166">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F166">
         <v>0</v>
@@ -10635,14 +10635,14 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B167">
-        <v>12090</v>
+        <v>405010</v>
       </c>
       <c r="C167" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B167,[1]TextData!A:A))</f>
-        <v>アウトオブオーダー</v>
+        <v>ダークプリズン+</v>
       </c>
       <c r="D167">
         <v>1</v>
@@ -10651,7 +10651,7 @@
         <v>0</v>
       </c>
       <c r="F167">
-        <v>5042</v>
+        <v>0</v>
       </c>
       <c r="G167">
         <v>0</v>
@@ -10659,14 +10659,14 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B168">
-        <v>412090</v>
+        <v>415090</v>
       </c>
       <c r="C168" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B168,[1]TextData!A:A))</f>
-        <v>アウトオブオーダー+</v>
+        <v>クイックカース+</v>
       </c>
       <c r="D168">
         <v>1</v>
@@ -10683,20 +10683,20 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B169">
-        <v>12050</v>
+        <v>1010</v>
       </c>
       <c r="C169" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B169,[1]TextData!A:A))</f>
-        <v>キュアスタン</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D169">
         <v>1</v>
       </c>
       <c r="E169">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F169">
         <v>0</v>
@@ -10707,47 +10707,47 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B170">
-        <v>12070</v>
+        <v>1030</v>
       </c>
       <c r="C170" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B170,[1]TextData!A:A))</f>
-        <v>ソーサリーコネクト</v>
+        <v>ブレイクウォール</v>
       </c>
       <c r="D170">
         <v>1</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F170">
-        <v>0</v>
+        <v>9120</v>
       </c>
       <c r="G170">
-        <v>0</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="171" spans="1:7">
       <c r="A171">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B171">
-        <v>14030</v>
+        <v>1070</v>
       </c>
       <c r="C171" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B171,[1]TextData!A:A))</f>
-        <v>ガードバインド</v>
+        <v>バーニングソウル</v>
       </c>
       <c r="D171">
         <v>1</v>
       </c>
       <c r="E171">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F171">
-        <v>0</v>
+        <v>6322</v>
       </c>
       <c r="G171">
         <v>0</v>
@@ -10755,20 +10755,20 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B172">
-        <v>3010</v>
+        <v>100610</v>
       </c>
       <c r="C172" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B172,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>サンフレイム</v>
       </c>
       <c r="D172">
         <v>1</v>
       </c>
       <c r="E172">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F172">
         <v>0</v>
@@ -10779,20 +10779,20 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B173">
-        <v>3070</v>
+        <v>100620</v>
       </c>
       <c r="C173" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B173,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>フレイムタン</v>
       </c>
       <c r="D173">
         <v>1</v>
       </c>
       <c r="E173">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F173">
         <v>0</v>
@@ -10803,14 +10803,14 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B174">
-        <v>100810</v>
+        <v>11040</v>
       </c>
       <c r="C174" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B174,[1]TextData!A:A))</f>
-        <v>テンパランス</v>
+        <v>ウルフソウル</v>
       </c>
       <c r="D174">
         <v>1</v>
@@ -10819,7 +10819,7 @@
         <v>0</v>
       </c>
       <c r="F174">
-        <v>0</v>
+        <v>5042</v>
       </c>
       <c r="G174">
         <v>0</v>
@@ -10827,20 +10827,20 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B175">
-        <v>100820</v>
+        <v>401030</v>
       </c>
       <c r="C175" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B175,[1]TextData!A:A))</f>
-        <v>シエルクルセイダー</v>
+        <v>ヒートスタンプ+</v>
       </c>
       <c r="D175">
         <v>1</v>
       </c>
       <c r="E175">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -10851,14 +10851,14 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B176">
-        <v>13060</v>
+        <v>411040</v>
       </c>
       <c r="C176" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B176,[1]TextData!A:A))</f>
-        <v>キュアフリーズ</v>
+        <v>アクティブギフト+</v>
       </c>
       <c r="D176">
         <v>1</v>
@@ -10867,7 +10867,7 @@
         <v>0</v>
       </c>
       <c r="F176">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G176">
         <v>0</v>
@@ -10875,14 +10875,14 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B177">
-        <v>403070</v>
+        <v>13040</v>
       </c>
       <c r="C177" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B177,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>アーマーコード</v>
       </c>
       <c r="D177">
         <v>1</v>
@@ -10899,20 +10899,20 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B178">
-        <v>13010</v>
+        <v>2010</v>
       </c>
       <c r="C178" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B178,[1]TextData!A:A))</f>
-        <v>ヘビィカバー</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D178">
         <v>1</v>
       </c>
       <c r="E178">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F178">
         <v>0</v>
@@ -10923,23 +10923,23 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B179">
-        <v>13020</v>
+        <v>2040</v>
       </c>
       <c r="C179" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B179,[1]TextData!A:A))</f>
-        <v>アイシクルエッジ</v>
+        <v>トラストチェイン</v>
       </c>
       <c r="D179">
         <v>1</v>
       </c>
       <c r="E179">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F179">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G179">
         <v>0</v>
@@ -10947,14 +10947,14 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B180">
-        <v>13040</v>
+        <v>100710</v>
       </c>
       <c r="C180" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B180,[1]TextData!A:A))</f>
-        <v>アーマーコード</v>
+        <v>ライズザフラッグ</v>
       </c>
       <c r="D180">
         <v>1</v>
@@ -10971,20 +10971,20 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B181">
-        <v>1010</v>
+        <v>100720</v>
       </c>
       <c r="C181" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B181,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>オーバーリミット</v>
       </c>
       <c r="D181">
         <v>1</v>
       </c>
       <c r="E181">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F181">
         <v>0</v>
@@ -10995,23 +10995,23 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B182">
-        <v>1050</v>
+        <v>12090</v>
       </c>
       <c r="C182" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B182,[1]TextData!A:A))</f>
-        <v>フレイムレイン</v>
+        <v>アウトオブオーダー</v>
       </c>
       <c r="D182">
         <v>1</v>
       </c>
       <c r="E182">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F182">
-        <v>1151</v>
+        <v>5042</v>
       </c>
       <c r="G182">
         <v>0</v>
@@ -11019,14 +11019,14 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B183">
-        <v>100910</v>
+        <v>412090</v>
       </c>
       <c r="C183" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B183,[1]TextData!A:A))</f>
-        <v>バーニングカウンター</v>
+        <v>アウトオブオーダー+</v>
       </c>
       <c r="D183">
         <v>1</v>
@@ -11043,20 +11043,20 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B184">
-        <v>100920</v>
+        <v>12050</v>
       </c>
       <c r="C184" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B184,[1]TextData!A:A))</f>
-        <v>プロミネンス</v>
+        <v>キュアスタン</v>
       </c>
       <c r="D184">
         <v>1</v>
       </c>
       <c r="E184">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F184">
         <v>0</v>
@@ -11067,14 +11067,14 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B185">
-        <v>11070</v>
+        <v>12070</v>
       </c>
       <c r="C185" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B185,[1]TextData!A:A))</f>
-        <v>ルージュバック</v>
+        <v>ソーサリーコネクト</v>
       </c>
       <c r="D185">
         <v>1</v>
@@ -11091,14 +11091,14 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B186">
-        <v>401050</v>
+        <v>14030</v>
       </c>
       <c r="C186" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B186,[1]TextData!A:A))</f>
-        <v>フレイムレイン+</v>
+        <v>ガードバインド</v>
       </c>
       <c r="D186">
         <v>1</v>
@@ -11115,20 +11115,20 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B187">
-        <v>11030</v>
+        <v>3010</v>
       </c>
       <c r="C187" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B187,[1]TextData!A:A))</f>
-        <v>ウォークライ</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D187">
         <v>1</v>
       </c>
       <c r="E187">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F187">
         <v>0</v>
@@ -11139,20 +11139,20 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B188">
-        <v>11020</v>
+        <v>3070</v>
       </c>
       <c r="C188" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B188,[1]TextData!A:A))</f>
-        <v>イーグルアイ</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D188">
         <v>1</v>
       </c>
       <c r="E188">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F188">
         <v>0</v>
@@ -11163,14 +11163,14 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B189">
-        <v>15040</v>
+        <v>100810</v>
       </c>
       <c r="C189" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B189,[1]TextData!A:A))</f>
-        <v>ネガティブドレイン</v>
+        <v>テンパランス</v>
       </c>
       <c r="D189">
         <v>1</v>
@@ -11187,20 +11187,20 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B190">
-        <v>2010</v>
+        <v>100820</v>
       </c>
       <c r="C190" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B190,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>シエルクルセイダー</v>
       </c>
       <c r="D190">
         <v>1</v>
       </c>
       <c r="E190">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F190">
         <v>0</v>
@@ -11211,23 +11211,23 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B191">
-        <v>2030</v>
+        <v>13060</v>
       </c>
       <c r="C191" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B191,[1]TextData!A:A))</f>
-        <v>ロングスラスト</v>
+        <v>キュアフリーズ</v>
       </c>
       <c r="D191">
         <v>1</v>
       </c>
       <c r="E191">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F191">
-        <v>14215</v>
+        <v>1023</v>
       </c>
       <c r="G191">
         <v>0</v>
@@ -11235,14 +11235,14 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B192">
-        <v>101010</v>
+        <v>403070</v>
       </c>
       <c r="C192" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B192,[1]TextData!A:A))</f>
-        <v>エウロス</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D192">
         <v>1</v>
@@ -11259,20 +11259,20 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B193">
-        <v>101020</v>
+        <v>13010</v>
       </c>
       <c r="C193" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B193,[1]TextData!A:A))</f>
-        <v>ボレアス</v>
+        <v>ヘビィカバー</v>
       </c>
       <c r="D193">
         <v>1</v>
       </c>
       <c r="E193">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -11283,14 +11283,14 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B194">
-        <v>12010</v>
+        <v>13020</v>
       </c>
       <c r="C194" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B194,[1]TextData!A:A))</f>
-        <v>クロースエッジ</v>
+        <v>アイシクルエッジ</v>
       </c>
       <c r="D194">
         <v>1</v>
@@ -11307,14 +11307,14 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B195">
-        <v>402030</v>
+        <v>13040</v>
       </c>
       <c r="C195" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B195,[1]TextData!A:A))</f>
-        <v>ショックインパルス+</v>
+        <v>アーマーコード</v>
       </c>
       <c r="D195">
         <v>1</v>
@@ -11331,20 +11331,20 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196">
+        <v>1009</v>
+      </c>
+      <c r="B196">
         <v>1010</v>
-      </c>
-      <c r="B196">
-        <v>12020</v>
       </c>
       <c r="C196" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B196,[1]TextData!A:A))</f>
-        <v>ファストファクション</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D196">
         <v>1</v>
       </c>
       <c r="E196">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F196">
         <v>0</v>
@@ -11355,23 +11355,23 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B197">
-        <v>12030</v>
+        <v>1050</v>
       </c>
       <c r="C197" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B197,[1]TextData!A:A))</f>
-        <v>クイックムーブ</v>
+        <v>フレイムレイン</v>
       </c>
       <c r="D197">
         <v>1</v>
       </c>
       <c r="E197">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F197">
-        <v>0</v>
+        <v>1151</v>
       </c>
       <c r="G197">
         <v>0</v>
@@ -11379,14 +11379,14 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B198">
-        <v>15070</v>
+        <v>100910</v>
       </c>
       <c r="C198" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B198,[1]TextData!A:A))</f>
-        <v>ジャックポッド</v>
+        <v>バーニングカウンター</v>
       </c>
       <c r="D198">
         <v>1</v>
@@ -11403,20 +11403,20 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B199">
-        <v>3010</v>
+        <v>100920</v>
       </c>
       <c r="C199" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B199,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>プロミネンス</v>
       </c>
       <c r="D199">
         <v>1</v>
       </c>
       <c r="E199">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F199">
         <v>0</v>
@@ -11427,20 +11427,20 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B200">
-        <v>3050</v>
+        <v>11070</v>
       </c>
       <c r="C200" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B200,[1]TextData!A:A))</f>
-        <v>ディープフリーズ</v>
+        <v>ルージュバック</v>
       </c>
       <c r="D200">
         <v>1</v>
       </c>
       <c r="E200">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F200">
         <v>0</v>
@@ -11451,14 +11451,14 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B201">
-        <v>101110</v>
+        <v>401050</v>
       </c>
       <c r="C201" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B201,[1]TextData!A:A))</f>
-        <v>アバランシュ</v>
+        <v>フレイムレイン+</v>
       </c>
       <c r="D201">
         <v>1</v>
@@ -11475,20 +11475,20 @@
     </row>
     <row r="202" spans="1:7">
       <c r="A202">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B202">
-        <v>101120</v>
+        <v>11030</v>
       </c>
       <c r="C202" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B202,[1]TextData!A:A))</f>
-        <v>ブリザードコフィン</v>
+        <v>ウォークライ</v>
       </c>
       <c r="D202">
         <v>1</v>
       </c>
       <c r="E202">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F202">
         <v>0</v>
@@ -11499,14 +11499,14 @@
     </row>
     <row r="203" spans="1:7">
       <c r="A203">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B203">
-        <v>13090</v>
+        <v>11020</v>
       </c>
       <c r="C203" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B203,[1]TextData!A:A))</f>
-        <v>アイスセイバー</v>
+        <v>イーグルアイ</v>
       </c>
       <c r="D203">
         <v>1</v>
@@ -11523,14 +11523,14 @@
     </row>
     <row r="204" spans="1:7">
       <c r="A204">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B204">
-        <v>403050</v>
+        <v>15040</v>
       </c>
       <c r="C204" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B204,[1]TextData!A:A))</f>
-        <v>ディープフリーズ+</v>
+        <v>ネガティブドレイン</v>
       </c>
       <c r="D204">
         <v>1</v>
@@ -11547,20 +11547,20 @@
     </row>
     <row r="205" spans="1:7">
       <c r="A205">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B205">
-        <v>13050</v>
+        <v>2010</v>
       </c>
       <c r="C205" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B205,[1]TextData!A:A))</f>
-        <v>キュアフリーズ</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D205">
         <v>1</v>
       </c>
       <c r="E205">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F205">
         <v>0</v>
@@ -11571,23 +11571,23 @@
     </row>
     <row r="206" spans="1:7">
       <c r="A206">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B206">
-        <v>13070</v>
+        <v>2030</v>
       </c>
       <c r="C206" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B206,[1]TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
+        <v>ロングスラスト</v>
       </c>
       <c r="D206">
         <v>1</v>
       </c>
       <c r="E206">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F206">
-        <v>0</v>
+        <v>14215</v>
       </c>
       <c r="G206">
         <v>0</v>
@@ -11595,14 +11595,14 @@
     </row>
     <row r="207" spans="1:7">
       <c r="A207">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B207">
-        <v>14070</v>
+        <v>101010</v>
       </c>
       <c r="C207" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B207,[1]TextData!A:A))</f>
-        <v>ホーミングクルセイド</v>
+        <v>エウロス</v>
       </c>
       <c r="D207">
         <v>1</v>
@@ -11619,20 +11619,20 @@
     </row>
     <row r="208" spans="1:7">
       <c r="A208">
-        <v>1101</v>
+        <v>1010</v>
       </c>
       <c r="B208">
-        <v>3010</v>
+        <v>101020</v>
       </c>
       <c r="C208" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B208,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>ボレアス</v>
       </c>
       <c r="D208">
         <v>1</v>
       </c>
       <c r="E208">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F208">
         <v>0</v>
@@ -11643,20 +11643,20 @@
     </row>
     <row r="209" spans="1:7">
       <c r="A209">
-        <v>1101</v>
+        <v>1010</v>
       </c>
       <c r="B209">
-        <v>3070</v>
+        <v>12010</v>
       </c>
       <c r="C209" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B209,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>クロースエッジ</v>
       </c>
       <c r="D209">
         <v>1</v>
       </c>
       <c r="E209">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F209">
         <v>0</v>
@@ -11667,14 +11667,14 @@
     </row>
     <row r="210" spans="1:7">
       <c r="A210">
-        <v>1101</v>
+        <v>1010</v>
       </c>
       <c r="B210">
-        <v>110110</v>
+        <v>402030</v>
       </c>
       <c r="C210" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B210,[1]TextData!A:A))</f>
-        <v>ウィビングヒストリー</v>
+        <v>ショックインパルス+</v>
       </c>
       <c r="D210">
         <v>1</v>
@@ -11691,20 +11691,20 @@
     </row>
     <row r="211" spans="1:7">
       <c r="A211">
-        <v>1101</v>
+        <v>1010</v>
       </c>
       <c r="B211">
-        <v>110120</v>
+        <v>12020</v>
       </c>
       <c r="C211" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B211,[1]TextData!A:A))</f>
-        <v>アンライバルド</v>
+        <v>ファストファクション</v>
       </c>
       <c r="D211">
         <v>1</v>
       </c>
       <c r="E211">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F211">
         <v>0</v>
@@ -11715,14 +11715,14 @@
     </row>
     <row r="212" spans="1:7">
       <c r="A212">
-        <v>1101</v>
+        <v>1010</v>
       </c>
       <c r="B212">
-        <v>13100</v>
+        <v>12030</v>
       </c>
       <c r="C212" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B212,[1]TextData!A:A))</f>
-        <v>アイスセイバー</v>
+        <v>クイックムーブ</v>
       </c>
       <c r="D212">
         <v>1</v>
@@ -11739,14 +11739,14 @@
     </row>
     <row r="213" spans="1:7">
       <c r="A213">
-        <v>1101</v>
+        <v>1010</v>
       </c>
       <c r="B213">
-        <v>403050</v>
+        <v>15070</v>
       </c>
       <c r="C213" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B213,[1]TextData!A:A))</f>
-        <v>ディープフリーズ+</v>
+        <v>ジャックポッド</v>
       </c>
       <c r="D213">
         <v>1</v>
@@ -11763,20 +11763,20 @@
     </row>
     <row r="214" spans="1:7">
       <c r="A214">
-        <v>1101</v>
+        <v>1011</v>
       </c>
       <c r="B214">
-        <v>13050</v>
+        <v>3010</v>
       </c>
       <c r="C214" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B214,[1]TextData!A:A))</f>
-        <v>キュアフリーズ</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D214">
         <v>1</v>
       </c>
       <c r="E214">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F214">
         <v>0</v>
@@ -11787,20 +11787,20 @@
     </row>
     <row r="215" spans="1:7">
       <c r="A215">
-        <v>1101</v>
+        <v>1011</v>
       </c>
       <c r="B215">
-        <v>13070</v>
+        <v>3050</v>
       </c>
       <c r="C215" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B215,[1]TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
+        <v>ディープフリーズ</v>
       </c>
       <c r="D215">
         <v>1</v>
       </c>
       <c r="E215">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F215">
         <v>0</v>
@@ -11811,25 +11811,385 @@
     </row>
     <row r="216" spans="1:7">
       <c r="A216">
-        <v>1101</v>
+        <v>1011</v>
       </c>
       <c r="B216">
-        <v>14070</v>
+        <v>101110</v>
       </c>
       <c r="C216" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B216,[1]TextData!A:A))</f>
+        <v>アバランシュ</v>
+      </c>
+      <c r="D216">
+        <v>1</v>
+      </c>
+      <c r="E216">
+        <v>0</v>
+      </c>
+      <c r="F216">
+        <v>0</v>
+      </c>
+      <c r="G216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7">
+      <c r="A217">
+        <v>1011</v>
+      </c>
+      <c r="B217">
+        <v>101120</v>
+      </c>
+      <c r="C217" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B217,[1]TextData!A:A))</f>
+        <v>ブリザードコフィン</v>
+      </c>
+      <c r="D217">
+        <v>1</v>
+      </c>
+      <c r="E217">
+        <v>200</v>
+      </c>
+      <c r="F217">
+        <v>0</v>
+      </c>
+      <c r="G217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7">
+      <c r="A218">
+        <v>1011</v>
+      </c>
+      <c r="B218">
+        <v>13090</v>
+      </c>
+      <c r="C218" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B218,[1]TextData!A:A))</f>
+        <v>アイスセイバー</v>
+      </c>
+      <c r="D218">
+        <v>1</v>
+      </c>
+      <c r="E218">
+        <v>0</v>
+      </c>
+      <c r="F218">
+        <v>0</v>
+      </c>
+      <c r="G218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7">
+      <c r="A219">
+        <v>1011</v>
+      </c>
+      <c r="B219">
+        <v>403050</v>
+      </c>
+      <c r="C219" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B219,[1]TextData!A:A))</f>
+        <v>ディープフリーズ+</v>
+      </c>
+      <c r="D219">
+        <v>1</v>
+      </c>
+      <c r="E219">
+        <v>0</v>
+      </c>
+      <c r="F219">
+        <v>0</v>
+      </c>
+      <c r="G219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220">
+        <v>1011</v>
+      </c>
+      <c r="B220">
+        <v>13050</v>
+      </c>
+      <c r="C220" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B220,[1]TextData!A:A))</f>
+        <v>キュアフリーズ</v>
+      </c>
+      <c r="D220">
+        <v>1</v>
+      </c>
+      <c r="E220">
+        <v>0</v>
+      </c>
+      <c r="F220">
+        <v>0</v>
+      </c>
+      <c r="G220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="A221">
+        <v>1011</v>
+      </c>
+      <c r="B221">
+        <v>13070</v>
+      </c>
+      <c r="C221" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B221,[1]TextData!A:A))</f>
+        <v>アシッドラッシュ</v>
+      </c>
+      <c r="D221">
+        <v>1</v>
+      </c>
+      <c r="E221">
+        <v>0</v>
+      </c>
+      <c r="F221">
+        <v>0</v>
+      </c>
+      <c r="G221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7">
+      <c r="A222">
+        <v>1011</v>
+      </c>
+      <c r="B222">
+        <v>14070</v>
+      </c>
+      <c r="C222" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B222,[1]TextData!A:A))</f>
         <v>ホーミングクルセイド</v>
       </c>
-      <c r="D216">
-        <v>1</v>
-      </c>
-      <c r="E216">
-        <v>0</v>
-      </c>
-      <c r="F216">
-        <v>0</v>
-      </c>
-      <c r="G216">
+      <c r="D222">
+        <v>1</v>
+      </c>
+      <c r="E222">
+        <v>0</v>
+      </c>
+      <c r="F222">
+        <v>0</v>
+      </c>
+      <c r="G222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223">
+        <v>1101</v>
+      </c>
+      <c r="B223">
+        <v>3010</v>
+      </c>
+      <c r="C223" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B223,[1]TextData!A:A))</f>
+        <v>アイスブレイド</v>
+      </c>
+      <c r="D223">
+        <v>1</v>
+      </c>
+      <c r="E223">
+        <v>50</v>
+      </c>
+      <c r="F223">
+        <v>0</v>
+      </c>
+      <c r="G223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7">
+      <c r="A224">
+        <v>1101</v>
+      </c>
+      <c r="B224">
+        <v>3070</v>
+      </c>
+      <c r="C224" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B224,[1]TextData!A:A))</f>
+        <v>アクアミラージュ</v>
+      </c>
+      <c r="D224">
+        <v>1</v>
+      </c>
+      <c r="E224">
+        <v>100</v>
+      </c>
+      <c r="F224">
+        <v>0</v>
+      </c>
+      <c r="G224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225">
+        <v>1101</v>
+      </c>
+      <c r="B225">
+        <v>110110</v>
+      </c>
+      <c r="C225" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B225,[1]TextData!A:A))</f>
+        <v>ウィビングヒストリー</v>
+      </c>
+      <c r="D225">
+        <v>1</v>
+      </c>
+      <c r="E225">
+        <v>0</v>
+      </c>
+      <c r="F225">
+        <v>0</v>
+      </c>
+      <c r="G225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226">
+        <v>1101</v>
+      </c>
+      <c r="B226">
+        <v>110120</v>
+      </c>
+      <c r="C226" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B226,[1]TextData!A:A))</f>
+        <v>アンライバルド</v>
+      </c>
+      <c r="D226">
+        <v>1</v>
+      </c>
+      <c r="E226">
+        <v>200</v>
+      </c>
+      <c r="F226">
+        <v>0</v>
+      </c>
+      <c r="G226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7">
+      <c r="A227">
+        <v>1101</v>
+      </c>
+      <c r="B227">
+        <v>13100</v>
+      </c>
+      <c r="C227" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B227,[1]TextData!A:A))</f>
+        <v>アイスセイバー</v>
+      </c>
+      <c r="D227">
+        <v>1</v>
+      </c>
+      <c r="E227">
+        <v>0</v>
+      </c>
+      <c r="F227">
+        <v>0</v>
+      </c>
+      <c r="G227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228">
+        <v>1101</v>
+      </c>
+      <c r="B228">
+        <v>403050</v>
+      </c>
+      <c r="C228" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B228,[1]TextData!A:A))</f>
+        <v>ディープフリーズ+</v>
+      </c>
+      <c r="D228">
+        <v>1</v>
+      </c>
+      <c r="E228">
+        <v>0</v>
+      </c>
+      <c r="F228">
+        <v>0</v>
+      </c>
+      <c r="G228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229">
+        <v>1101</v>
+      </c>
+      <c r="B229">
+        <v>13050</v>
+      </c>
+      <c r="C229" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B229,[1]TextData!A:A))</f>
+        <v>キュアフリーズ</v>
+      </c>
+      <c r="D229">
+        <v>1</v>
+      </c>
+      <c r="E229">
+        <v>0</v>
+      </c>
+      <c r="F229">
+        <v>0</v>
+      </c>
+      <c r="G229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230">
+        <v>1101</v>
+      </c>
+      <c r="B230">
+        <v>13070</v>
+      </c>
+      <c r="C230" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B230,[1]TextData!A:A))</f>
+        <v>アシッドラッシュ</v>
+      </c>
+      <c r="D230">
+        <v>1</v>
+      </c>
+      <c r="E230">
+        <v>0</v>
+      </c>
+      <c r="F230">
+        <v>0</v>
+      </c>
+      <c r="G230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231">
+        <v>1101</v>
+      </c>
+      <c r="B231">
+        <v>14070</v>
+      </c>
+      <c r="C231" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B231,[1]TextData!A:A))</f>
+        <v>ホーミングクルセイド</v>
+      </c>
+      <c r="D231">
+        <v>1</v>
+      </c>
+      <c r="E231">
+        <v>0</v>
+      </c>
+      <c r="F231">
+        <v>0</v>
+      </c>
+      <c r="G231">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -188,7 +188,7 @@
     <t>Andras</t>
   </si>
   <si>
-    <t>Berith</t>
+    <t>unique enemy_011</t>
   </si>
   <si>
     <t>Paimon</t>
@@ -461,9 +461,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -489,7 +489,43 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -503,23 +539,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -534,15 +571,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -550,22 +579,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -579,15 +601,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -603,23 +619,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -634,7 +634,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -646,7 +694,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -658,73 +778,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -736,61 +802,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -802,19 +814,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -843,6 +843,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -860,17 +869,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
@@ -880,17 +878,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -907,6 +898,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -933,145 +933,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2720,7 +2720,7 @@
             <v>200210</v>
           </cell>
           <cell r="B195" t="str">
-            <v>マイトレインフォース</v>
+            <v>インフェルノ</v>
           </cell>
         </row>
         <row r="196">
@@ -2728,7 +2728,7 @@
             <v>200220</v>
           </cell>
           <cell r="B196" t="str">
-            <v>カタストロフィ</v>
+            <v>ハートアブレイズ</v>
           </cell>
         </row>
         <row r="197">
@@ -4096,7 +4096,7 @@
             <v>506011</v>
           </cell>
           <cell r="B367" t="str">
-            <v>ATK+1</v>
+            <v>DEF+1</v>
           </cell>
         </row>
         <row r="368">
@@ -4104,7 +4104,7 @@
             <v>506012</v>
           </cell>
           <cell r="B368" t="str">
-            <v>DEF+1</v>
+            <v>SPD+1</v>
           </cell>
         </row>
         <row r="369">
@@ -4112,7 +4112,7 @@
             <v>506013</v>
           </cell>
           <cell r="B369" t="str">
-            <v>SPD+1</v>
+            <v>EXP+20%</v>
           </cell>
         </row>
         <row r="370">
@@ -5557,7 +5557,7 @@
         <v>1</v>
       </c>
       <c r="L18">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -5598,7 +5598,7 @@
         <v>100</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19">
         <v>14</v>
@@ -5616,7 +5616,7 @@
         <v>3</v>
       </c>
       <c r="L19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -5637,7 +5637,7 @@
         <v>25</v>
       </c>
       <c r="S19" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -9078,11 +9078,11 @@
         <v>102</v>
       </c>
       <c r="B102">
-        <v>5010</v>
+        <v>1010</v>
       </c>
       <c r="C102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B102,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -9102,20 +9102,20 @@
         <v>102</v>
       </c>
       <c r="B103">
-        <v>5020</v>
+        <v>1110</v>
       </c>
       <c r="C103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B103,[1]TextData!A:A))</f>
-        <v>カウントジャグラー</v>
+        <v>バーンストーム</v>
       </c>
       <c r="D103">
         <v>1</v>
       </c>
       <c r="E103">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F103">
-        <v>1013</v>
+        <v>0</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -9126,11 +9126,11 @@
         <v>102</v>
       </c>
       <c r="B104">
-        <v>15050</v>
+        <v>11010</v>
       </c>
       <c r="C104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B104,[1]TextData!A:A))</f>
-        <v>キュアシェイド</v>
+        <v>フレイムセイバー</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="C105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B105,[1]TextData!A:A))</f>
-        <v>マイトレインフォース</v>
+        <v>インフェルノ</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="C106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B106,[1]TextData!A:A))</f>
-        <v>カタストロフィ</v>
+        <v>ハートアブレイズ</v>
       </c>
       <c r="D106">
         <v>1</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -194,7 +194,7 @@
     <t>Paimon</t>
   </si>
   <si>
-    <t>Ammon</t>
+    <t>guardian dragon_4</t>
   </si>
   <si>
     <t>Bifrons</t>
@@ -461,9 +461,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -481,6 +481,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -489,29 +512,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -525,7 +533,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -542,44 +550,6 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -602,14 +572,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -620,6 +582,44 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -640,7 +640,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -652,13 +700,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -670,49 +790,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -724,61 +802,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -790,31 +814,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -843,15 +843,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -872,17 +863,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -925,6 +905,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -933,22 +933,22 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -957,121 +957,121 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1256,7 +1256,7 @@
             <v>1040</v>
           </cell>
           <cell r="B12" t="str">
-            <v>ソードアダプト</v>
+            <v>フィニッシュスタブ</v>
           </cell>
         </row>
         <row r="13">
@@ -1309,2759 +1309,2759 @@
         </row>
         <row r="19">
           <cell r="A19">
-            <v>2010</v>
+            <v>1940</v>
           </cell>
           <cell r="B19" t="str">
-            <v>ディスチャージ</v>
+            <v>ソードアダプト</v>
           </cell>
         </row>
         <row r="20">
           <cell r="A20">
-            <v>2020</v>
+            <v>2010</v>
           </cell>
           <cell r="B20" t="str">
-            <v>シャープエッジ</v>
+            <v>ディスチャージ</v>
           </cell>
         </row>
         <row r="21">
           <cell r="A21">
-            <v>2030</v>
+            <v>2020</v>
           </cell>
           <cell r="B21" t="str">
-            <v>ロングスラスト</v>
+            <v>シャープエッジ</v>
           </cell>
         </row>
         <row r="22">
           <cell r="A22">
-            <v>2040</v>
+            <v>2030</v>
           </cell>
           <cell r="B22" t="str">
-            <v>トラストチェイン</v>
+            <v>ロングスラスト</v>
           </cell>
         </row>
         <row r="23">
           <cell r="A23">
-            <v>2050</v>
+            <v>2040</v>
           </cell>
           <cell r="B23" t="str">
-            <v>スペルバニシング</v>
+            <v>スパイラルソード</v>
           </cell>
         </row>
         <row r="24">
           <cell r="A24">
-            <v>2060</v>
+            <v>2050</v>
           </cell>
           <cell r="B24" t="str">
-            <v>アーテニーストライク</v>
+            <v>スペルバニシング</v>
           </cell>
         </row>
         <row r="25">
           <cell r="A25">
-            <v>2070</v>
+            <v>2060</v>
           </cell>
           <cell r="B25" t="str">
-            <v>コンセントレイト</v>
+            <v>アーテニーストライク</v>
           </cell>
         </row>
         <row r="26">
           <cell r="A26">
-            <v>2080</v>
+            <v>2070</v>
           </cell>
           <cell r="B26" t="str">
-            <v>ディレイマジック</v>
+            <v>コンセントレイト</v>
           </cell>
         </row>
         <row r="27">
           <cell r="A27">
-            <v>2110</v>
+            <v>2080</v>
           </cell>
           <cell r="B27" t="str">
-            <v>ショックインパルス</v>
+            <v>ディレイマジック</v>
           </cell>
         </row>
         <row r="28">
           <cell r="A28">
-            <v>2120</v>
+            <v>2110</v>
           </cell>
           <cell r="B28" t="str">
-            <v>インペイル</v>
+            <v>ショックインパルス</v>
           </cell>
         </row>
         <row r="29">
           <cell r="A29">
-            <v>2920</v>
+            <v>2120</v>
           </cell>
           <cell r="B29" t="str">
-            <v>イベイドコード</v>
+            <v>インペイル</v>
           </cell>
         </row>
         <row r="30">
           <cell r="A30">
-            <v>3010</v>
+            <v>2920</v>
           </cell>
           <cell r="B30" t="str">
-            <v>アイスブレイド</v>
+            <v>イベイドコード</v>
           </cell>
         </row>
         <row r="31">
           <cell r="A31">
-            <v>3020</v>
+            <v>2940</v>
           </cell>
           <cell r="B31" t="str">
-            <v>シールドバッシュ</v>
+            <v>トラストチェイン</v>
           </cell>
         </row>
         <row r="32">
           <cell r="A32">
-            <v>3030</v>
+            <v>3010</v>
           </cell>
           <cell r="B32" t="str">
-            <v>フレンジー</v>
+            <v>アイスブレイド</v>
           </cell>
         </row>
         <row r="33">
           <cell r="A33">
-            <v>3040</v>
+            <v>3020</v>
           </cell>
           <cell r="B33" t="str">
-            <v>エスコートソール</v>
+            <v>シールドバッシュ</v>
           </cell>
         </row>
         <row r="34">
           <cell r="A34">
-            <v>3050</v>
+            <v>3030</v>
           </cell>
           <cell r="B34" t="str">
-            <v>ディープフリーズ</v>
+            <v>フレンジー</v>
           </cell>
         </row>
         <row r="35">
           <cell r="A35">
-            <v>3060</v>
+            <v>3040</v>
           </cell>
           <cell r="B35" t="str">
-            <v>バブルブロウ</v>
+            <v>スカルブレイカー</v>
           </cell>
         </row>
         <row r="36">
           <cell r="A36">
-            <v>3070</v>
+            <v>3050</v>
           </cell>
           <cell r="B36" t="str">
-            <v>アクアミラージュ</v>
+            <v>ディープフリーズ</v>
           </cell>
         </row>
         <row r="37">
           <cell r="A37">
-            <v>3080</v>
+            <v>3060</v>
           </cell>
           <cell r="B37" t="str">
-            <v>フロストシールド</v>
+            <v>バブルブロウ</v>
           </cell>
         </row>
         <row r="38">
           <cell r="A38">
-            <v>3110</v>
+            <v>3070</v>
           </cell>
           <cell r="B38" t="str">
-            <v>ポイズン</v>
+            <v>アクアミラージュ</v>
           </cell>
         </row>
         <row r="39">
           <cell r="A39">
-            <v>3120</v>
+            <v>3080</v>
           </cell>
           <cell r="B39" t="str">
-            <v>カウンターオーラ</v>
+            <v>フロストシールド</v>
           </cell>
         </row>
         <row r="40">
           <cell r="A40">
-            <v>3130</v>
+            <v>3110</v>
           </cell>
           <cell r="B40" t="str">
-            <v>アクアウォール</v>
+            <v>ポイズン</v>
           </cell>
         </row>
         <row r="41">
           <cell r="A41">
-            <v>3930</v>
+            <v>3120</v>
           </cell>
           <cell r="B41" t="str">
-            <v>ラインプロテクト</v>
+            <v>カウンターオーラ</v>
           </cell>
         </row>
         <row r="42">
           <cell r="A42">
-            <v>4010</v>
+            <v>3130</v>
           </cell>
           <cell r="B42" t="str">
-            <v>セイントレーザー</v>
+            <v>アクアウォール</v>
           </cell>
         </row>
         <row r="43">
           <cell r="A43">
-            <v>4020</v>
+            <v>3930</v>
           </cell>
           <cell r="B43" t="str">
-            <v>ペネトレイト</v>
+            <v>ラインプロテクト</v>
           </cell>
         </row>
         <row r="44">
           <cell r="A44">
-            <v>4030</v>
+            <v>3940</v>
           </cell>
           <cell r="B44" t="str">
-            <v>ヒーリング</v>
+            <v>エスコートソール</v>
           </cell>
         </row>
         <row r="45">
           <cell r="A45">
-            <v>4050</v>
+            <v>4010</v>
           </cell>
           <cell r="B45" t="str">
-            <v>べネディクション</v>
+            <v>セイントレーザー</v>
           </cell>
         </row>
         <row r="46">
           <cell r="A46">
-            <v>4060</v>
+            <v>4020</v>
           </cell>
           <cell r="B46" t="str">
-            <v>ホーリーグレイス</v>
+            <v>ペネトレイト</v>
           </cell>
         </row>
         <row r="47">
           <cell r="A47">
-            <v>4070</v>
+            <v>4030</v>
           </cell>
           <cell r="B47" t="str">
-            <v>キュアエール</v>
+            <v>ヒーリング</v>
           </cell>
         </row>
         <row r="48">
           <cell r="A48">
-            <v>4080</v>
+            <v>4040</v>
           </cell>
           <cell r="B48" t="str">
-            <v>ラインバリア</v>
+            <v>ピアシングランス</v>
           </cell>
         </row>
         <row r="49">
           <cell r="A49">
-            <v>4110</v>
+            <v>4050</v>
           </cell>
           <cell r="B49" t="str">
-            <v>ダブルレーザー</v>
+            <v>べネディクション</v>
           </cell>
         </row>
         <row r="50">
           <cell r="A50">
-            <v>4120</v>
+            <v>4060</v>
           </cell>
           <cell r="B50" t="str">
-            <v>リザイアフォトン</v>
+            <v>ホーリーグレイス</v>
           </cell>
         </row>
         <row r="51">
           <cell r="A51">
-            <v>4130</v>
+            <v>4070</v>
           </cell>
           <cell r="B51" t="str">
-            <v>チャクラ</v>
+            <v>キュアエール</v>
           </cell>
         </row>
         <row r="52">
           <cell r="A52">
-            <v>5010</v>
+            <v>4080</v>
           </cell>
           <cell r="B52" t="str">
-            <v>ダークプリズン</v>
+            <v>ラインバリア</v>
           </cell>
         </row>
         <row r="53">
           <cell r="A53">
-            <v>5020</v>
+            <v>4110</v>
           </cell>
           <cell r="B53" t="str">
-            <v>カウントジャグラー</v>
+            <v>ダブルレーザー</v>
           </cell>
         </row>
         <row r="54">
           <cell r="A54">
-            <v>5030</v>
+            <v>4120</v>
           </cell>
           <cell r="B54" t="str">
-            <v>パッシブカース</v>
+            <v>リザイアフォトン</v>
           </cell>
         </row>
         <row r="55">
           <cell r="A55">
-            <v>5040</v>
+            <v>4130</v>
           </cell>
           <cell r="B55" t="str">
-            <v>アビサルデスペア</v>
+            <v>チャクラ</v>
           </cell>
         </row>
         <row r="56">
           <cell r="A56">
-            <v>5050</v>
+            <v>5010</v>
           </cell>
           <cell r="B56" t="str">
-            <v>ディプラヴィティ</v>
+            <v>ダークプリズン</v>
           </cell>
         </row>
         <row r="57">
           <cell r="A57">
-            <v>5060</v>
+            <v>5020</v>
           </cell>
           <cell r="B57" t="str">
-            <v>ダークネス</v>
+            <v>カウントジャグラー</v>
           </cell>
         </row>
         <row r="58">
           <cell r="A58">
-            <v>5080</v>
+            <v>5030</v>
           </cell>
           <cell r="B58" t="str">
-            <v>ポイズンブロウ</v>
+            <v>パッシブカース</v>
           </cell>
         </row>
         <row r="59">
           <cell r="A59">
-            <v>5110</v>
+            <v>5040</v>
           </cell>
           <cell r="B59" t="str">
-            <v>ドレインヒール</v>
+            <v>ディレイショット</v>
           </cell>
         </row>
         <row r="60">
           <cell r="A60">
-            <v>5120</v>
+            <v>5050</v>
           </cell>
           <cell r="B60" t="str">
-            <v>ユーサネイジア</v>
+            <v>ディプラヴィティ</v>
           </cell>
         </row>
         <row r="61">
           <cell r="A61">
-            <v>5130</v>
+            <v>5060</v>
           </cell>
           <cell r="B61" t="str">
-            <v>シェイディークラウド</v>
+            <v>ダークネス</v>
           </cell>
         </row>
         <row r="62">
           <cell r="A62">
-            <v>6010</v>
+            <v>5080</v>
           </cell>
           <cell r="B62" t="str">
-            <v>何もしない</v>
+            <v>ポイズンブロウ</v>
           </cell>
         </row>
         <row r="63">
           <cell r="A63">
-            <v>6020</v>
+            <v>5110</v>
           </cell>
           <cell r="B63" t="str">
-            <v>交代</v>
+            <v>ドレインヒール</v>
           </cell>
         </row>
         <row r="64">
           <cell r="A64">
-            <v>10010</v>
+            <v>5120</v>
           </cell>
           <cell r="B64" t="str">
-            <v>アンデッド</v>
+            <v>ユーサネイジア</v>
           </cell>
         </row>
         <row r="65">
           <cell r="A65">
-            <v>10020</v>
+            <v>5130</v>
           </cell>
           <cell r="B65" t="str">
-            <v>エアリアル</v>
+            <v>シェイディークラウド</v>
           </cell>
         </row>
         <row r="66">
           <cell r="A66">
-            <v>10030</v>
+            <v>5940</v>
           </cell>
           <cell r="B66" t="str">
-            <v>悪魔</v>
+            <v>アビサルデスペア</v>
           </cell>
         </row>
         <row r="67">
           <cell r="A67">
-            <v>10040</v>
+            <v>6010</v>
           </cell>
           <cell r="B67" t="str">
-            <v>クリーチャー</v>
+            <v>何もしない</v>
           </cell>
         </row>
         <row r="68">
           <cell r="A68">
-            <v>10050</v>
+            <v>6020</v>
           </cell>
           <cell r="B68" t="str">
-            <v>野生の記憶</v>
+            <v>交代</v>
           </cell>
         </row>
         <row r="69">
           <cell r="A69">
-            <v>10060</v>
+            <v>10010</v>
           </cell>
           <cell r="B69" t="str">
-            <v>変異生物</v>
+            <v>アンデッド</v>
           </cell>
         </row>
         <row r="70">
           <cell r="A70">
-            <v>10110</v>
+            <v>10020</v>
           </cell>
           <cell r="B70" t="str">
-            <v>先天属性・炎</v>
+            <v>エアリアル</v>
           </cell>
         </row>
         <row r="71">
           <cell r="A71">
-            <v>10120</v>
+            <v>10030</v>
           </cell>
           <cell r="B71" t="str">
-            <v>先天属性・雷</v>
+            <v>悪魔</v>
           </cell>
         </row>
         <row r="72">
           <cell r="A72">
-            <v>10130</v>
+            <v>10040</v>
           </cell>
           <cell r="B72" t="str">
-            <v>先天属性・氷</v>
+            <v>クリーチャー</v>
           </cell>
         </row>
         <row r="73">
           <cell r="A73">
-            <v>10140</v>
+            <v>10050</v>
           </cell>
           <cell r="B73" t="str">
-            <v>先天属性・光</v>
+            <v>野生の記憶</v>
           </cell>
         </row>
         <row r="74">
           <cell r="A74">
-            <v>10150</v>
+            <v>10060</v>
           </cell>
           <cell r="B74" t="str">
-            <v>先天属性・闇</v>
+            <v>変異生物</v>
           </cell>
         </row>
         <row r="75">
           <cell r="A75">
-            <v>10210</v>
+            <v>10110</v>
           </cell>
           <cell r="B75" t="str">
-            <v>装備スロット数+1</v>
+            <v>先天属性・炎</v>
           </cell>
         </row>
         <row r="76">
           <cell r="A76">
-            <v>11010</v>
+            <v>10120</v>
           </cell>
           <cell r="B76" t="str">
-            <v>フレイムセイバー</v>
+            <v>先天属性・雷</v>
           </cell>
         </row>
         <row r="77">
           <cell r="A77">
-            <v>11020</v>
+            <v>10130</v>
           </cell>
           <cell r="B77" t="str">
-            <v>イーグルアイ</v>
+            <v>先天属性・氷</v>
           </cell>
         </row>
         <row r="78">
           <cell r="A78">
-            <v>11030</v>
+            <v>10140</v>
           </cell>
           <cell r="B78" t="str">
-            <v>ウォークライ</v>
+            <v>先天属性・光</v>
           </cell>
         </row>
         <row r="79">
           <cell r="A79">
-            <v>11040</v>
+            <v>10150</v>
           </cell>
           <cell r="B79" t="str">
-            <v>ウルフソウル</v>
+            <v>先天属性・闇</v>
           </cell>
         </row>
         <row r="80">
           <cell r="A80">
-            <v>11050</v>
+            <v>10210</v>
           </cell>
           <cell r="B80" t="str">
-            <v>キュアファイア</v>
+            <v>装備スロット数+1</v>
           </cell>
         </row>
         <row r="81">
           <cell r="A81">
-            <v>11070</v>
+            <v>11010</v>
           </cell>
           <cell r="B81" t="str">
-            <v>ルージュバック</v>
+            <v>フレイムセイバー</v>
           </cell>
         </row>
         <row r="82">
           <cell r="A82">
-            <v>11090</v>
+            <v>11020</v>
           </cell>
           <cell r="B82" t="str">
-            <v>スレイプニル</v>
+            <v>イーグルアイ</v>
           </cell>
         </row>
         <row r="83">
           <cell r="A83">
-            <v>11100</v>
+            <v>11030</v>
           </cell>
           <cell r="B83" t="str">
-            <v>レストア</v>
+            <v>ウォークライ</v>
           </cell>
         </row>
         <row r="84">
           <cell r="A84">
-            <v>11110</v>
+            <v>11040</v>
           </cell>
           <cell r="B84" t="str">
-            <v>レイジカウンター</v>
+            <v>ウルフソウル</v>
           </cell>
         </row>
         <row r="85">
           <cell r="A85">
-            <v>11120</v>
+            <v>11050</v>
           </cell>
           <cell r="B85" t="str">
-            <v>パワーエール</v>
+            <v>キュアファイア</v>
           </cell>
         </row>
         <row r="86">
           <cell r="A86">
-            <v>11130</v>
+            <v>11070</v>
           </cell>
           <cell r="B86" t="str">
-            <v>ワイドカウンター</v>
+            <v>ルージュバック</v>
           </cell>
         </row>
         <row r="87">
           <cell r="A87">
-            <v>11140</v>
+            <v>11090</v>
           </cell>
           <cell r="B87" t="str">
-            <v>ライジングファイア</v>
+            <v>スレイプニル</v>
           </cell>
         </row>
         <row r="88">
           <cell r="A88">
-            <v>11920</v>
+            <v>11100</v>
           </cell>
           <cell r="B88" t="str">
-            <v>プリディカメント</v>
+            <v>レストア</v>
           </cell>
         </row>
         <row r="89">
           <cell r="A89">
-            <v>11930</v>
+            <v>11110</v>
           </cell>
           <cell r="B89" t="str">
-            <v>アサルトシフト</v>
+            <v>レイジカウンター</v>
           </cell>
         </row>
         <row r="90">
           <cell r="A90">
-            <v>11940</v>
+            <v>11120</v>
           </cell>
           <cell r="B90" t="str">
-            <v>アクティブギフト</v>
+            <v>パワーエール</v>
           </cell>
         </row>
         <row r="91">
           <cell r="A91">
-            <v>11950</v>
+            <v>11130</v>
           </cell>
           <cell r="B91" t="str">
-            <v>イグナイテッド</v>
+            <v>ワイドカウンター</v>
           </cell>
         </row>
         <row r="92">
           <cell r="A92">
-            <v>12010</v>
+            <v>11140</v>
           </cell>
           <cell r="B92" t="str">
-            <v>クロースエッジ</v>
+            <v>ライジングファイア</v>
           </cell>
         </row>
         <row r="93">
           <cell r="A93">
-            <v>12020</v>
+            <v>11920</v>
           </cell>
           <cell r="B93" t="str">
-            <v>ファストファクション</v>
+            <v>プリディカメント</v>
           </cell>
         </row>
         <row r="94">
           <cell r="A94">
-            <v>12030</v>
+            <v>11930</v>
           </cell>
           <cell r="B94" t="str">
-            <v>クイックムーブ</v>
+            <v>アサルトシフト</v>
           </cell>
         </row>
         <row r="95">
           <cell r="A95">
-            <v>12040</v>
+            <v>11940</v>
           </cell>
           <cell r="B95" t="str">
-            <v>ヘブンリーラック</v>
+            <v>アクティブギフト</v>
           </cell>
         </row>
         <row r="96">
           <cell r="A96">
-            <v>12050</v>
+            <v>11950</v>
           </cell>
           <cell r="B96" t="str">
-            <v>キュアスタン</v>
+            <v>イグナイテッド</v>
           </cell>
         </row>
         <row r="97">
           <cell r="A97">
-            <v>12070</v>
+            <v>12010</v>
           </cell>
           <cell r="B97" t="str">
-            <v>ソーサリーコネクト</v>
+            <v>クロースエッジ</v>
           </cell>
         </row>
         <row r="98">
           <cell r="A98">
-            <v>12090</v>
+            <v>12020</v>
           </cell>
           <cell r="B98" t="str">
-            <v>アウトオブオーダー</v>
+            <v>ファストファクション</v>
           </cell>
         </row>
         <row r="99">
           <cell r="A99">
-            <v>12100</v>
+            <v>12030</v>
           </cell>
           <cell r="B99" t="str">
-            <v>ワンスパニッシュ</v>
+            <v>クイックムーブ</v>
           </cell>
         </row>
         <row r="100">
           <cell r="A100">
-            <v>12110</v>
+            <v>12040</v>
           </cell>
           <cell r="B100" t="str">
-            <v>コンセントレイト</v>
+            <v>ヘブンリーラック</v>
           </cell>
         </row>
         <row r="101">
           <cell r="A101">
-            <v>12120</v>
+            <v>12050</v>
           </cell>
           <cell r="B101" t="str">
-            <v>パリィ</v>
+            <v>キュアスタン</v>
           </cell>
         </row>
         <row r="102">
           <cell r="A102">
-            <v>12130</v>
+            <v>12090</v>
           </cell>
           <cell r="B102" t="str">
-            <v>チェイスマジック</v>
+            <v>アウトオブオーダー</v>
           </cell>
         </row>
         <row r="103">
           <cell r="A103">
-            <v>12140</v>
+            <v>12100</v>
           </cell>
           <cell r="B103" t="str">
-            <v>ウィンドライズ</v>
+            <v>ワンスパニッシュ</v>
           </cell>
         </row>
         <row r="104">
           <cell r="A104">
-            <v>12510</v>
+            <v>12110</v>
           </cell>
           <cell r="B104" t="str">
-            <v>アクトスタンス</v>
+            <v>コンセントレイト</v>
           </cell>
         </row>
         <row r="105">
           <cell r="A105">
-            <v>12910</v>
+            <v>12120</v>
           </cell>
           <cell r="B105" t="str">
-            <v>コンセントレイト</v>
+            <v>パリィ</v>
           </cell>
         </row>
         <row r="106">
           <cell r="A106">
-            <v>12930</v>
+            <v>12130</v>
           </cell>
           <cell r="B106" t="str">
-            <v>スウィフトカレント</v>
+            <v>チェイスマジック</v>
           </cell>
         </row>
         <row r="107">
           <cell r="A107">
-            <v>12940</v>
+            <v>12140</v>
           </cell>
           <cell r="B107" t="str">
-            <v>イヴェイドオール</v>
+            <v>ウィンドライズ</v>
           </cell>
         </row>
         <row r="108">
           <cell r="A108">
-            <v>13010</v>
+            <v>12510</v>
           </cell>
           <cell r="B108" t="str">
-            <v>ヘビィカバー</v>
+            <v>アクトスタンス</v>
           </cell>
         </row>
         <row r="109">
           <cell r="A109">
-            <v>13020</v>
+            <v>12910</v>
           </cell>
           <cell r="B109" t="str">
-            <v>アイシクルエッジ</v>
+            <v>コンセントレイト</v>
           </cell>
         </row>
         <row r="110">
           <cell r="A110">
-            <v>13030</v>
+            <v>12930</v>
           </cell>
           <cell r="B110" t="str">
-            <v>カウンターマジック</v>
+            <v>スウィフトカレント</v>
           </cell>
         </row>
         <row r="111">
           <cell r="A111">
-            <v>13040</v>
+            <v>12940</v>
           </cell>
           <cell r="B111" t="str">
-            <v>アーマーコード</v>
+            <v>イヴェイドオール</v>
           </cell>
         </row>
         <row r="112">
           <cell r="A112">
-            <v>13050</v>
+            <v>13010</v>
           </cell>
           <cell r="B112" t="str">
-            <v>キュアフリーズ</v>
+            <v>ヘビィカバー</v>
           </cell>
         </row>
         <row r="113">
           <cell r="A113">
-            <v>13070</v>
+            <v>13020</v>
           </cell>
           <cell r="B113" t="str">
-            <v>アシッドラッシュ</v>
+            <v>アイシクルエッジ</v>
           </cell>
         </row>
         <row r="114">
           <cell r="A114">
-            <v>13090</v>
+            <v>13030</v>
           </cell>
           <cell r="B114" t="str">
-            <v>アイスセイバー</v>
+            <v>カウンターマジック</v>
           </cell>
         </row>
         <row r="115">
           <cell r="A115">
-            <v>13110</v>
+            <v>13040</v>
           </cell>
           <cell r="B115" t="str">
-            <v>ガーディアン</v>
+            <v>アーマーコード</v>
           </cell>
         </row>
         <row r="116">
           <cell r="A116">
-            <v>13120</v>
+            <v>13050</v>
           </cell>
           <cell r="B116" t="str">
-            <v>ライフセーブ</v>
+            <v>キュアフリーズ</v>
           </cell>
         </row>
         <row r="117">
           <cell r="A117">
-            <v>13130</v>
+            <v>13070</v>
           </cell>
           <cell r="B117" t="str">
-            <v>ライフスティール</v>
+            <v>アシッドラッシュ</v>
           </cell>
         </row>
         <row r="118">
           <cell r="A118">
-            <v>13210</v>
+            <v>13090</v>
           </cell>
           <cell r="B118" t="str">
-            <v>ルミナスカバー</v>
+            <v>アイスセイバー</v>
           </cell>
         </row>
         <row r="119">
           <cell r="A119">
-            <v>13510</v>
+            <v>13110</v>
           </cell>
           <cell r="B119" t="str">
-            <v>デコイプラス</v>
+            <v>ガーディアン</v>
           </cell>
         </row>
         <row r="120">
           <cell r="A120">
-            <v>13511</v>
+            <v>13120</v>
           </cell>
           <cell r="B120" t="str">
-            <v>デコイプラス</v>
+            <v>ライフセーブ</v>
           </cell>
         </row>
         <row r="121">
           <cell r="A121">
-            <v>13520</v>
+            <v>13130</v>
           </cell>
           <cell r="B121" t="str">
-            <v>アフターシールド</v>
+            <v>ライフスティール</v>
           </cell>
         </row>
         <row r="122">
           <cell r="A122">
-            <v>13530</v>
+            <v>13140</v>
           </cell>
           <cell r="B122" t="str">
-            <v>カバープラス</v>
+            <v>クイックバリア</v>
           </cell>
         </row>
         <row r="123">
           <cell r="A123">
-            <v>13920</v>
+            <v>13210</v>
           </cell>
           <cell r="B123" t="str">
-            <v>クイックバリア</v>
+            <v>ルミナスカバー</v>
           </cell>
         </row>
         <row r="124">
           <cell r="A124">
-            <v>13930</v>
+            <v>13510</v>
           </cell>
           <cell r="B124" t="str">
-            <v>クイックキュア</v>
+            <v>デコイプラス</v>
           </cell>
         </row>
         <row r="125">
           <cell r="A125">
-            <v>13940</v>
+            <v>13511</v>
           </cell>
           <cell r="B125" t="str">
-            <v>セルフシールド</v>
+            <v>デコイプラス</v>
           </cell>
         </row>
         <row r="126">
           <cell r="A126">
-            <v>13950</v>
+            <v>13520</v>
           </cell>
           <cell r="B126" t="str">
-            <v>パッシブジャミング</v>
+            <v>アフターシールド</v>
           </cell>
         </row>
         <row r="127">
           <cell r="A127">
-            <v>14010</v>
+            <v>13530</v>
           </cell>
           <cell r="B127" t="str">
-            <v>ファーストエイド</v>
+            <v>カバープラス</v>
           </cell>
         </row>
         <row r="128">
           <cell r="A128">
-            <v>14020</v>
+            <v>13930</v>
           </cell>
           <cell r="B128" t="str">
-            <v>クイックヒール</v>
+            <v>クイックキュア</v>
           </cell>
         </row>
         <row r="129">
           <cell r="A129">
-            <v>14030</v>
+            <v>13940</v>
           </cell>
           <cell r="B129" t="str">
-            <v>ガードバインド</v>
+            <v>セルフシールド</v>
           </cell>
         </row>
         <row r="130">
           <cell r="A130">
-            <v>14040</v>
+            <v>13950</v>
           </cell>
           <cell r="B130" t="str">
-            <v>ホープフルアイリス</v>
+            <v>パッシブジャミング</v>
           </cell>
         </row>
         <row r="131">
           <cell r="A131">
-            <v>14050</v>
+            <v>14010</v>
           </cell>
           <cell r="B131" t="str">
-            <v>キュアパッシブ</v>
+            <v>ファーストエイド</v>
           </cell>
         </row>
         <row r="132">
           <cell r="A132">
-            <v>14060</v>
+            <v>14020</v>
           </cell>
           <cell r="B132" t="str">
-            <v>パッシブサプライ</v>
+            <v>クイックヒール</v>
           </cell>
         </row>
         <row r="133">
           <cell r="A133">
-            <v>14070</v>
+            <v>14030</v>
           </cell>
           <cell r="B133" t="str">
-            <v>ホーミングクルセイド</v>
+            <v>ガードバインド</v>
           </cell>
         </row>
         <row r="134">
           <cell r="A134">
-            <v>14090</v>
+            <v>14040</v>
           </cell>
           <cell r="B134" t="str">
-            <v>リレイズ</v>
+            <v>ホープフルアイリス</v>
           </cell>
         </row>
         <row r="135">
           <cell r="A135">
-            <v>14100</v>
+            <v>14050</v>
           </cell>
           <cell r="B135" t="str">
-            <v>ファストヒール</v>
+            <v>キュアパッシブ</v>
           </cell>
         </row>
         <row r="136">
           <cell r="A136">
-            <v>14110</v>
+            <v>14060</v>
           </cell>
           <cell r="B136" t="str">
-            <v>リフレッシュ</v>
+            <v>パッシブサプライ</v>
           </cell>
         </row>
         <row r="137">
           <cell r="A137">
-            <v>14120</v>
+            <v>14070</v>
           </cell>
           <cell r="B137" t="str">
-            <v>ファストメディック</v>
+            <v>ホーミングクルセイド</v>
           </cell>
         </row>
         <row r="138">
           <cell r="A138">
-            <v>14130</v>
+            <v>14090</v>
           </cell>
           <cell r="B138" t="str">
-            <v>ディバインシールド</v>
+            <v>リレイズ</v>
           </cell>
         </row>
         <row r="139">
           <cell r="A139">
-            <v>14920</v>
+            <v>14100</v>
           </cell>
           <cell r="B139" t="str">
-            <v>ライフディバイド</v>
+            <v>ファストヒール</v>
           </cell>
         </row>
         <row r="140">
           <cell r="A140">
-            <v>14930</v>
+            <v>14110</v>
           </cell>
           <cell r="B140" t="str">
-            <v>エイミングスコープ</v>
+            <v>リフレッシュ</v>
           </cell>
         </row>
         <row r="141">
           <cell r="A141">
-            <v>14940</v>
+            <v>14120</v>
           </cell>
           <cell r="B141" t="str">
-            <v>リジェネレーション</v>
+            <v>ファストメディック</v>
           </cell>
         </row>
         <row r="142">
           <cell r="A142">
-            <v>15010</v>
+            <v>14130</v>
           </cell>
           <cell r="B142" t="str">
-            <v>ワンスパニッシュ</v>
+            <v>ディバインシールド</v>
           </cell>
         </row>
         <row r="143">
           <cell r="A143">
-            <v>15020</v>
+            <v>14140</v>
           </cell>
           <cell r="B143" t="str">
-            <v>クイックカース</v>
+            <v>ライフディバイド</v>
           </cell>
         </row>
         <row r="144">
           <cell r="A144">
-            <v>15030</v>
+            <v>14930</v>
           </cell>
           <cell r="B144" t="str">
-            <v>バイタリティ</v>
+            <v>エイミングスコープ</v>
           </cell>
         </row>
         <row r="145">
           <cell r="A145">
-            <v>15040</v>
+            <v>14940</v>
           </cell>
           <cell r="B145" t="str">
-            <v>ネガティブドレイン</v>
+            <v>リジェネレーション</v>
           </cell>
         </row>
         <row r="146">
           <cell r="A146">
-            <v>15050</v>
+            <v>15010</v>
           </cell>
           <cell r="B146" t="str">
-            <v>キュアシェイド</v>
+            <v>ワンスパニッシュ</v>
           </cell>
         </row>
         <row r="147">
           <cell r="A147">
-            <v>15060</v>
+            <v>15020</v>
           </cell>
           <cell r="B147" t="str">
-            <v>アンデッドペイン</v>
+            <v>クイックカース</v>
           </cell>
         </row>
         <row r="148">
           <cell r="A148">
-            <v>15070</v>
+            <v>15030</v>
           </cell>
           <cell r="B148" t="str">
-            <v>ジャックポッド</v>
+            <v>バイタリティ</v>
           </cell>
         </row>
         <row r="149">
           <cell r="A149">
-            <v>15080</v>
+            <v>15040</v>
           </cell>
           <cell r="B149" t="str">
-            <v>ヒールハント</v>
+            <v>ネガティブドレイン</v>
           </cell>
         </row>
         <row r="150">
           <cell r="A150">
-            <v>15110</v>
+            <v>15050</v>
           </cell>
           <cell r="B150" t="str">
-            <v>フォーカサイト</v>
+            <v>キュアシェイド</v>
           </cell>
         </row>
         <row r="151">
           <cell r="A151">
-            <v>15120</v>
+            <v>15060</v>
           </cell>
           <cell r="B151" t="str">
-            <v>ガードハント</v>
+            <v>アンデッドペイン</v>
           </cell>
         </row>
         <row r="152">
           <cell r="A152">
-            <v>15130</v>
+            <v>15070</v>
           </cell>
           <cell r="B152" t="str">
-            <v>リヴェンジャー</v>
+            <v>ジャックポッド</v>
           </cell>
         </row>
         <row r="153">
           <cell r="A153">
-            <v>15510</v>
+            <v>15080</v>
           </cell>
           <cell r="B153" t="str">
-            <v>リープリアクト</v>
+            <v>ヒールハント</v>
           </cell>
         </row>
         <row r="154">
           <cell r="A154">
-            <v>15512</v>
+            <v>15110</v>
           </cell>
           <cell r="B154" t="str">
-            <v>リープリアクト</v>
+            <v>フォーカサイト</v>
           </cell>
         </row>
         <row r="155">
           <cell r="A155">
-            <v>15520</v>
+            <v>15120</v>
           </cell>
           <cell r="B155" t="str">
-            <v>ディレイドパッシブ</v>
+            <v>ガードハント</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156">
-            <v>15530</v>
+            <v>15130</v>
           </cell>
           <cell r="B156" t="str">
-            <v>シャドウケイプ</v>
+            <v>リヴェンジャー</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157">
-            <v>15910</v>
+            <v>15140</v>
           </cell>
           <cell r="B157" t="str">
-            <v>イーグルアイ</v>
+            <v>ソーサリーコネクト</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158">
-            <v>15920</v>
+            <v>15510</v>
           </cell>
           <cell r="B158" t="str">
-            <v>ネヴァーエンド</v>
+            <v>リープリアクト</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159">
-            <v>15930</v>
+            <v>15512</v>
           </cell>
           <cell r="B159" t="str">
-            <v>グレイブアクト</v>
+            <v>リープリアクト</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160">
-            <v>15940</v>
+            <v>15520</v>
           </cell>
           <cell r="B160" t="str">
-            <v>スカルグラッジ</v>
+            <v>ディレイドパッシブ</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161">
-            <v>20010</v>
+            <v>15530</v>
           </cell>
           <cell r="B161" t="str">
-            <v>ウェイトユニゾン</v>
+            <v>シャドウケイプ</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162">
-            <v>30010</v>
+            <v>15910</v>
           </cell>
           <cell r="B162" t="str">
-            <v>ラーニングピアス</v>
+            <v>イーグルアイ</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163">
-            <v>30020</v>
+            <v>15920</v>
           </cell>
           <cell r="B163" t="str">
-            <v>スティールヒール</v>
+            <v>ネヴァーエンド</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164">
-            <v>30030</v>
+            <v>15930</v>
           </cell>
           <cell r="B164" t="str">
-            <v>ガッツ</v>
+            <v>グレイブアクト</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165">
-            <v>100110</v>
+            <v>15940</v>
           </cell>
           <cell r="B165" t="str">
-            <v>ソーイングアームド</v>
+            <v>スカルグラッジ</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166">
-            <v>100120</v>
+            <v>20010</v>
           </cell>
           <cell r="B166" t="str">
-            <v>エターナルロンド</v>
+            <v>ウェイトユニゾン</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167">
-            <v>100210</v>
+            <v>30010</v>
           </cell>
           <cell r="B167" t="str">
-            <v>ピースメーカー</v>
+            <v>ラーニングピアス</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168">
-            <v>100220</v>
+            <v>30020</v>
           </cell>
           <cell r="B168" t="str">
-            <v>レヴェリー</v>
+            <v>スティールヒール</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169">
-            <v>100310</v>
+            <v>30030</v>
           </cell>
           <cell r="B169" t="str">
-            <v>セイクリッドバリア</v>
+            <v>ガッツ</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170">
-            <v>100320</v>
+            <v>100110</v>
           </cell>
           <cell r="B170" t="str">
-            <v>リベンジニードル</v>
+            <v>ソーイングアームド</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171">
-            <v>100410</v>
+            <v>100120</v>
           </cell>
           <cell r="B171" t="str">
-            <v>アバンデンス</v>
+            <v>エターナルロンド</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172">
-            <v>100420</v>
+            <v>100210</v>
           </cell>
           <cell r="B172" t="str">
-            <v>ハーヴェスト</v>
+            <v>ピースメーカー</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173">
-            <v>100510</v>
+            <v>100220</v>
           </cell>
           <cell r="B173" t="str">
-            <v>カースドブレイク</v>
+            <v>レヴェリー</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174">
-            <v>100520</v>
+            <v>100310</v>
           </cell>
           <cell r="B174" t="str">
-            <v>ムーンライトレイ</v>
+            <v>セイクリッドバリア</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175">
-            <v>100610</v>
+            <v>100320</v>
           </cell>
           <cell r="B175" t="str">
-            <v>サンフレイム</v>
+            <v>リベンジニードル</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176">
-            <v>100620</v>
+            <v>100410</v>
           </cell>
           <cell r="B176" t="str">
-            <v>フレイムタン</v>
+            <v>アバンデンス</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177">
-            <v>100710</v>
+            <v>100420</v>
           </cell>
           <cell r="B177" t="str">
-            <v>ライズザフラッグ</v>
+            <v>ハーヴェスト</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178">
-            <v>100720</v>
+            <v>100510</v>
           </cell>
           <cell r="B178" t="str">
-            <v>オーバーリミット</v>
+            <v>カースドブレイク</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179">
-            <v>100810</v>
+            <v>100520</v>
           </cell>
           <cell r="B179" t="str">
-            <v>テンパランス</v>
+            <v>ムーンライトレイ</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180">
-            <v>100820</v>
+            <v>100610</v>
           </cell>
           <cell r="B180" t="str">
-            <v>シエルクルセイダー</v>
+            <v>サンフレイム</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181">
-            <v>100910</v>
+            <v>100620</v>
           </cell>
           <cell r="B181" t="str">
-            <v>バーニングカウンター</v>
+            <v>フレイムタン</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182">
-            <v>100911</v>
+            <v>100710</v>
           </cell>
           <cell r="B182" t="str">
-            <v>バーニングカウンター</v>
+            <v>ライズザフラッグ</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183">
-            <v>100920</v>
+            <v>100720</v>
           </cell>
           <cell r="B183" t="str">
-            <v>プロミネンス</v>
+            <v>オーバーリミット</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184">
-            <v>100921</v>
+            <v>100810</v>
           </cell>
           <cell r="B184" t="str">
-            <v>プロミネンス</v>
+            <v>テンパランス</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185">
-            <v>101010</v>
+            <v>100820</v>
           </cell>
           <cell r="B185" t="str">
-            <v>エウロス</v>
+            <v>シエルクルセイダー</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186">
-            <v>101020</v>
+            <v>100910</v>
           </cell>
           <cell r="B186" t="str">
-            <v>ボレアス</v>
+            <v>バーニングカウンター</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187">
-            <v>101110</v>
+            <v>100911</v>
           </cell>
           <cell r="B187" t="str">
-            <v>アバランシュ</v>
+            <v>バーニングカウンター</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188">
-            <v>101120</v>
+            <v>100920</v>
           </cell>
           <cell r="B188" t="str">
-            <v>ブリザードコフィン</v>
+            <v>プロミネンス</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189">
-            <v>110110</v>
+            <v>100921</v>
           </cell>
           <cell r="B189" t="str">
-            <v>ウィビングヒストリー</v>
+            <v>プロミネンス</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190">
-            <v>110120</v>
+            <v>101010</v>
           </cell>
           <cell r="B190" t="str">
-            <v>アンライバルド</v>
+            <v>エウロス</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191">
-            <v>110210</v>
+            <v>101020</v>
           </cell>
           <cell r="B191" t="str">
-            <v>リベリオンスピリッツ</v>
+            <v>ボレアス</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192">
-            <v>110220</v>
+            <v>101110</v>
           </cell>
           <cell r="B192" t="str">
-            <v>ファイナリティアビス</v>
+            <v>アバランシュ</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193">
-            <v>200110</v>
+            <v>101120</v>
           </cell>
           <cell r="B193" t="str">
-            <v>ティアーズスクリプト</v>
+            <v>ブリザードコフィン</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194">
-            <v>200120</v>
+            <v>110110</v>
           </cell>
           <cell r="B194" t="str">
-            <v>アングリークライ</v>
+            <v>ウィビングヒストリー</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195">
-            <v>200210</v>
+            <v>110120</v>
           </cell>
           <cell r="B195" t="str">
-            <v>インフェルノ</v>
+            <v>アンライバルド</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196">
-            <v>200220</v>
+            <v>110210</v>
           </cell>
           <cell r="B196" t="str">
-            <v>ハートアブレイズ</v>
+            <v>リベリオンスピリッツ</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197">
-            <v>200230</v>
+            <v>110220</v>
           </cell>
           <cell r="B197" t="str">
-            <v>悪魔(ベリト)</v>
+            <v>ファイナリティアビス</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198">
-            <v>200310</v>
+            <v>200110</v>
           </cell>
           <cell r="B198" t="str">
-            <v>プルガシオン</v>
+            <v>ティアーズスクリプト</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199">
-            <v>200320</v>
+            <v>200120</v>
           </cell>
           <cell r="B199" t="str">
-            <v>プリエステス</v>
+            <v>アングリークライ</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200">
-            <v>200330</v>
+            <v>200210</v>
           </cell>
           <cell r="B200" t="str">
-            <v>悪魔(パイモン)</v>
+            <v>インフェルノ</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201">
-            <v>200410</v>
+            <v>200220</v>
           </cell>
           <cell r="B201" t="str">
-            <v>コウソクテンショウ</v>
+            <v>ハートアブレイズ</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202">
-            <v>200411</v>
+            <v>200230</v>
           </cell>
           <cell r="B202" t="str">
-            <v>コウソクテンショウ</v>
+            <v>悪魔(ベリト)</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203">
-            <v>200420</v>
+            <v>200310</v>
           </cell>
           <cell r="B203" t="str">
-            <v>アンチバフ</v>
+            <v>ハードウォール</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204">
-            <v>200430</v>
+            <v>200320</v>
           </cell>
           <cell r="B204" t="str">
-            <v>悪魔(アンドラス)</v>
+            <v>リファクター</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205">
-            <v>200510</v>
+            <v>200330</v>
           </cell>
           <cell r="B205" t="str">
-            <v>カウントダウン</v>
+            <v>悪魔(アモン)</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206">
-            <v>200520</v>
+            <v>200410</v>
           </cell>
           <cell r="B206" t="str">
-            <v>グラウンドゼロ</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207">
-            <v>200530</v>
+            <v>200411</v>
           </cell>
           <cell r="B207" t="str">
-            <v>悪魔(ビフロンス)</v>
+            <v>コウソクテンショウ</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208">
-            <v>201010</v>
+            <v>200420</v>
           </cell>
           <cell r="B208" t="str">
-            <v>カオスペイン</v>
+            <v>アンチバフ</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209">
-            <v>201020</v>
+            <v>200430</v>
           </cell>
           <cell r="B209" t="str">
-            <v>フォールンワン</v>
+            <v>悪魔(アンドラス)</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210">
-            <v>201030</v>
+            <v>200510</v>
           </cell>
           <cell r="B210" t="str">
-            <v>アンリマユ</v>
+            <v>カウントダウン</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211">
-            <v>300010</v>
+            <v>200520</v>
           </cell>
           <cell r="B211" t="str">
-            <v>ライフブースト</v>
+            <v>グラウンドゼロ</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212">
-            <v>300020</v>
+            <v>200530</v>
           </cell>
           <cell r="B212" t="str">
-            <v>スピリットチャージ</v>
+            <v>悪魔(ビフロンス)</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213">
-            <v>300030</v>
+            <v>201010</v>
           </cell>
           <cell r="B213" t="str">
-            <v>フォースライズ</v>
+            <v>カオスペイン</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214">
-            <v>300040</v>
+            <v>201020</v>
           </cell>
           <cell r="B214" t="str">
-            <v>ディフェンスオーラ</v>
+            <v>フォールンワン</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215">
-            <v>300050</v>
+            <v>201030</v>
           </cell>
           <cell r="B215" t="str">
-            <v>ラピッドムーブ</v>
+            <v>アンリマユ</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216">
-            <v>300130</v>
+            <v>209310</v>
           </cell>
           <cell r="B216" t="str">
-            <v>アタックブレイク</v>
+            <v>プルガシオン</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217">
-            <v>300140</v>
+            <v>209320</v>
           </cell>
           <cell r="B217" t="str">
-            <v>シールドバニッシュ</v>
+            <v>プリエステス</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218">
-            <v>300210</v>
+            <v>209330</v>
           </cell>
           <cell r="B218" t="str">
-            <v>エーテルリチャージ</v>
+            <v>悪魔(パイモン)</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219">
-            <v>300220</v>
+            <v>300010</v>
           </cell>
           <cell r="B219" t="str">
-            <v>リカバリーエンハンス</v>
+            <v>ライフブースト</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220">
-            <v>300230</v>
+            <v>300020</v>
           </cell>
           <cell r="B220" t="str">
-            <v>ヴェンジェンス</v>
+            <v>スピリットチャージ</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221">
-            <v>301010</v>
+            <v>300030</v>
           </cell>
           <cell r="B221" t="str">
-            <v>ディケイドリセット</v>
+            <v>フォースライズ</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222">
-            <v>301020</v>
+            <v>300040</v>
           </cell>
           <cell r="B222" t="str">
-            <v>ウォーリアーブラッド</v>
+            <v>ディフェンスオーラ</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223">
-            <v>301030</v>
+            <v>300050</v>
           </cell>
           <cell r="B223" t="str">
-            <v>トライアングルガード</v>
+            <v>ラピッドムーブ</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224">
-            <v>301040</v>
+            <v>300130</v>
           </cell>
           <cell r="B224" t="str">
-            <v>セーフティバリア</v>
+            <v>アタックブレイク</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225">
-            <v>301050</v>
+            <v>300140</v>
           </cell>
           <cell r="B225" t="str">
-            <v>ヒロインズハイ</v>
+            <v>シールドバニッシュ</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226">
-            <v>301060</v>
+            <v>300210</v>
           </cell>
           <cell r="B226" t="str">
-            <v>セカンドステージ</v>
+            <v>エーテルリチャージ</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227">
-            <v>301070</v>
+            <v>300220</v>
           </cell>
           <cell r="B227" t="str">
-            <v>ハイヒットポイント</v>
+            <v>リカバリーエンハンス</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228">
-            <v>301080</v>
+            <v>300230</v>
           </cell>
           <cell r="B228" t="str">
-            <v>セプタブラスト</v>
+            <v>ヴェンジェンス</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229">
-            <v>301090</v>
+            <v>301010</v>
           </cell>
           <cell r="B229" t="str">
-            <v>イニシャルブロッカー</v>
+            <v>ディケイドリセット</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230">
-            <v>301100</v>
+            <v>301020</v>
           </cell>
           <cell r="B230" t="str">
-            <v>ファーストテイク</v>
+            <v>ウォーリアーブラッド</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231">
-            <v>310010</v>
+            <v>301030</v>
           </cell>
           <cell r="B231" t="str">
-            <v>妖精の祈り</v>
+            <v>トライアングルガード</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232">
-            <v>310020</v>
+            <v>301040</v>
           </cell>
           <cell r="B232" t="str">
-            <v>月のかけら</v>
+            <v>セーフティバリア</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233">
-            <v>310030</v>
+            <v>301050</v>
           </cell>
           <cell r="B233" t="str">
-            <v>商売の才覚書</v>
+            <v>ヒロインズハイ</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234">
-            <v>310040</v>
+            <v>301060</v>
           </cell>
           <cell r="B234" t="str">
-            <v>メビウスの砂時計</v>
+            <v>セカンドステージ</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235">
-            <v>310050</v>
+            <v>301070</v>
           </cell>
           <cell r="B235" t="str">
-            <v>先陣の心得</v>
+            <v>ハイヒットポイント</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236">
-            <v>310060</v>
+            <v>301080</v>
           </cell>
           <cell r="B236" t="str">
-            <v>ヒスイの勾玉</v>
+            <v>セプタブラスト</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237">
-            <v>310070</v>
+            <v>301090</v>
           </cell>
           <cell r="B237" t="str">
-            <v>英傑の盾</v>
+            <v>イニシャルブロッカー</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238">
-            <v>310080</v>
+            <v>301100</v>
           </cell>
           <cell r="B238" t="str">
-            <v>鷹の目</v>
+            <v>ファーストテイク</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239">
-            <v>310090</v>
+            <v>310010</v>
           </cell>
           <cell r="B239" t="str">
-            <v>ラーニングピアス</v>
+            <v>妖精の祈り</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240">
-            <v>310100</v>
+            <v>310020</v>
           </cell>
           <cell r="B240" t="str">
-            <v>セブンズストーン</v>
+            <v>月のかけら</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241">
-            <v>310130</v>
+            <v>310030</v>
           </cell>
           <cell r="B241" t="str">
-            <v>ヒールユニット</v>
+            <v>商売の才覚書</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242">
-            <v>320010</v>
+            <v>310040</v>
           </cell>
           <cell r="B242" t="str">
-            <v>訓練所Lv1</v>
+            <v>レイピッドブースト</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243">
-            <v>320011</v>
+            <v>310050</v>
           </cell>
           <cell r="B243" t="str">
-            <v>訓練所Lv2</v>
+            <v>黄金の守護精霊</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244">
-            <v>320012</v>
+            <v>310060</v>
           </cell>
           <cell r="B244" t="str">
-            <v>訓練所Lv3</v>
+            <v>ヒスイの勾玉</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245">
-            <v>320020</v>
+            <v>310070</v>
           </cell>
           <cell r="B245" t="str">
-            <v>研究施設Lv1</v>
+            <v>英傑の盾</v>
           </cell>
         </row>
         <row r="246">
           <cell r="A246">
-            <v>320021</v>
+            <v>310080</v>
           </cell>
           <cell r="B246" t="str">
-            <v>研究施設Lv2</v>
+            <v>鷹の目</v>
           </cell>
         </row>
         <row r="247">
           <cell r="A247">
-            <v>320022</v>
+            <v>310090</v>
           </cell>
           <cell r="B247" t="str">
-            <v>研究施設Lv3</v>
+            <v>ラーニングピアス</v>
           </cell>
         </row>
         <row r="248">
           <cell r="A248">
-            <v>320030</v>
+            <v>310100</v>
           </cell>
           <cell r="B248" t="str">
-            <v>資料館Lv1</v>
+            <v>セブンズストーン</v>
           </cell>
         </row>
         <row r="249">
           <cell r="A249">
-            <v>320031</v>
+            <v>310110</v>
           </cell>
           <cell r="B249" t="str">
-            <v>資料館Lv2</v>
+            <v>ファーストトリック</v>
           </cell>
         </row>
         <row r="250">
           <cell r="A250">
-            <v>320032</v>
+            <v>310130</v>
           </cell>
           <cell r="B250" t="str">
-            <v>資料館Lv3</v>
+            <v>ヒールユニット</v>
           </cell>
         </row>
         <row r="251">
           <cell r="A251">
-            <v>320040</v>
+            <v>320010</v>
           </cell>
           <cell r="B251" t="str">
-            <v>潜伏技術Lv1</v>
+            <v>訓練所Lv1</v>
           </cell>
         </row>
         <row r="252">
           <cell r="A252">
-            <v>321010</v>
+            <v>320011</v>
           </cell>
           <cell r="B252" t="str">
-            <v>炎の祭壇</v>
+            <v>訓練所Lv2</v>
           </cell>
         </row>
         <row r="253">
           <cell r="A253">
-            <v>321020</v>
+            <v>320012</v>
           </cell>
           <cell r="B253" t="str">
-            <v>稲妻の祭壇</v>
+            <v>訓練所Lv3</v>
           </cell>
         </row>
         <row r="254">
           <cell r="A254">
-            <v>321030</v>
+            <v>320020</v>
           </cell>
           <cell r="B254" t="str">
-            <v>蒼の祭壇</v>
+            <v>研究施設Lv1</v>
           </cell>
         </row>
         <row r="255">
           <cell r="A255">
-            <v>321040</v>
+            <v>320021</v>
           </cell>
           <cell r="B255" t="str">
-            <v>光の祭壇</v>
+            <v>研究施設Lv2</v>
           </cell>
         </row>
         <row r="256">
           <cell r="A256">
-            <v>321050</v>
+            <v>320022</v>
           </cell>
           <cell r="B256" t="str">
-            <v>月の祭壇</v>
+            <v>研究施設Lv3</v>
           </cell>
         </row>
         <row r="257">
           <cell r="A257">
-            <v>322010</v>
+            <v>320030</v>
           </cell>
           <cell r="B257" t="str">
-            <v>食糧庫Lv1</v>
+            <v>資料館Lv1</v>
           </cell>
         </row>
         <row r="258">
           <cell r="A258">
-            <v>322020</v>
+            <v>320031</v>
           </cell>
           <cell r="B258" t="str">
-            <v>攻撃技術Lv1</v>
+            <v>資料館Lv2</v>
           </cell>
         </row>
         <row r="259">
           <cell r="A259">
-            <v>322030</v>
+            <v>320032</v>
           </cell>
           <cell r="B259" t="str">
-            <v>防御技術Lv1</v>
+            <v>資料館Lv3</v>
           </cell>
         </row>
         <row r="260">
           <cell r="A260">
-            <v>322040</v>
+            <v>320040</v>
           </cell>
           <cell r="B260" t="str">
-            <v>詠唱技術Lv1</v>
+            <v>潜伏技術Lv1</v>
           </cell>
         </row>
         <row r="261">
           <cell r="A261">
-            <v>401010</v>
+            <v>321010</v>
           </cell>
           <cell r="B261" t="str">
-            <v>ファイアボール+</v>
+            <v>炎の祭壇</v>
           </cell>
         </row>
         <row r="262">
           <cell r="A262">
-            <v>401020</v>
+            <v>321020</v>
           </cell>
           <cell r="B262" t="str">
-            <v>バーンストーム+</v>
+            <v>稲妻の祭壇</v>
           </cell>
         </row>
         <row r="263">
           <cell r="A263">
-            <v>401030</v>
+            <v>321030</v>
           </cell>
           <cell r="B263" t="str">
-            <v>ヒートスタンプ+</v>
+            <v>蒼の祭壇</v>
           </cell>
         </row>
         <row r="264">
           <cell r="A264">
-            <v>401040</v>
+            <v>321040</v>
           </cell>
           <cell r="B264" t="str">
-            <v>ソードアダプト+</v>
+            <v>光の祭壇</v>
           </cell>
         </row>
         <row r="265">
           <cell r="A265">
-            <v>401050</v>
+            <v>321050</v>
           </cell>
           <cell r="B265" t="str">
-            <v>フレイムレイン+</v>
+            <v>月の祭壇</v>
           </cell>
         </row>
         <row r="266">
           <cell r="A266">
-            <v>401060</v>
+            <v>322010</v>
           </cell>
           <cell r="B266" t="str">
-            <v>イクスティンクション+</v>
+            <v>食糧庫Lv1</v>
           </cell>
         </row>
         <row r="267">
           <cell r="A267">
-            <v>401070</v>
+            <v>322020</v>
           </cell>
           <cell r="B267" t="str">
-            <v>バーニングソウル+</v>
+            <v>攻撃技術Lv1</v>
           </cell>
         </row>
         <row r="268">
           <cell r="A268">
-            <v>401080</v>
+            <v>322030</v>
           </cell>
           <cell r="B268" t="str">
-            <v>レイジングバウンサー+</v>
+            <v>防御技術Lv1</v>
           </cell>
         </row>
         <row r="269">
           <cell r="A269">
-            <v>402010</v>
+            <v>322040</v>
           </cell>
           <cell r="B269" t="str">
-            <v>ディスチャージ+</v>
+            <v>詠唱技術Lv1</v>
           </cell>
         </row>
         <row r="270">
           <cell r="A270">
-            <v>402020</v>
+            <v>401010</v>
           </cell>
           <cell r="B270" t="str">
-            <v>イベイドコード+</v>
+            <v>ファイアボール+</v>
           </cell>
         </row>
         <row r="271">
           <cell r="A271">
-            <v>402030</v>
+            <v>401020</v>
           </cell>
           <cell r="B271" t="str">
-            <v>ショックインパルス+</v>
+            <v>バーンストーム+</v>
           </cell>
         </row>
         <row r="272">
           <cell r="A272">
-            <v>402040</v>
+            <v>401030</v>
           </cell>
           <cell r="B272" t="str">
-            <v>トラストチェイン+</v>
+            <v>ヒートスタンプ+</v>
           </cell>
         </row>
         <row r="273">
           <cell r="A273">
-            <v>402050</v>
+            <v>401040</v>
           </cell>
           <cell r="B273" t="str">
-            <v>スペルバニシング+</v>
+            <v>ソードアダプト+</v>
           </cell>
         </row>
         <row r="274">
           <cell r="A274">
-            <v>402060</v>
+            <v>401050</v>
           </cell>
           <cell r="B274" t="str">
-            <v>アーテニーストライク+</v>
+            <v>フレイムレイン+</v>
           </cell>
         </row>
         <row r="275">
           <cell r="A275">
-            <v>402070</v>
+            <v>401060</v>
           </cell>
           <cell r="B275" t="str">
-            <v>コンセントレイト+</v>
+            <v>イクスティンクション+</v>
           </cell>
         </row>
         <row r="276">
           <cell r="A276">
-            <v>402080</v>
+            <v>401070</v>
           </cell>
           <cell r="B276" t="str">
-            <v>ディレイマジック+</v>
+            <v>バーニングソウル+</v>
           </cell>
         </row>
         <row r="277">
           <cell r="A277">
-            <v>403010</v>
+            <v>401080</v>
           </cell>
           <cell r="B277" t="str">
-            <v>アイスブレイド+</v>
+            <v>レイジングバウンサー+</v>
           </cell>
         </row>
         <row r="278">
           <cell r="A278">
-            <v>403020</v>
+            <v>402010</v>
           </cell>
           <cell r="B278" t="str">
-            <v>カウンターオーラ+</v>
+            <v>ディスチャージ+</v>
           </cell>
         </row>
         <row r="279">
           <cell r="A279">
-            <v>403030</v>
+            <v>402020</v>
           </cell>
           <cell r="B279" t="str">
-            <v>ラインプロテクト+</v>
+            <v>イベイドコード+</v>
           </cell>
         </row>
         <row r="280">
           <cell r="A280">
-            <v>403040</v>
+            <v>402030</v>
           </cell>
           <cell r="B280" t="str">
-            <v>エスコートソール+</v>
+            <v>ショックインパルス+</v>
           </cell>
         </row>
         <row r="281">
           <cell r="A281">
-            <v>403050</v>
+            <v>402040</v>
           </cell>
           <cell r="B281" t="str">
-            <v>ディープフリーズ+</v>
+            <v>トラストチェイン+</v>
           </cell>
         </row>
         <row r="282">
           <cell r="A282">
-            <v>403060</v>
+            <v>402050</v>
           </cell>
           <cell r="B282" t="str">
-            <v>バブルブロウ+</v>
+            <v>スペルバニシング+</v>
           </cell>
         </row>
         <row r="283">
           <cell r="A283">
-            <v>403070</v>
+            <v>402060</v>
           </cell>
           <cell r="B283" t="str">
-            <v>アクアミラージュ+</v>
+            <v>アーテニーストライク+</v>
           </cell>
         </row>
         <row r="284">
           <cell r="A284">
-            <v>403080</v>
+            <v>402070</v>
           </cell>
           <cell r="B284" t="str">
-            <v>フロストシールド+</v>
+            <v>コンセントレイト+</v>
           </cell>
         </row>
         <row r="285">
           <cell r="A285">
-            <v>404010</v>
+            <v>402080</v>
           </cell>
           <cell r="B285" t="str">
-            <v>セイントレーザー+</v>
+            <v>ディレイマジック+</v>
           </cell>
         </row>
         <row r="286">
           <cell r="A286">
-            <v>404020</v>
+            <v>403010</v>
           </cell>
           <cell r="B286" t="str">
-            <v>ペネトレイト+</v>
+            <v>アイスブレイド+</v>
           </cell>
         </row>
         <row r="287">
           <cell r="A287">
-            <v>404030</v>
+            <v>403020</v>
           </cell>
           <cell r="B287" t="str">
-            <v>ヒーリング+</v>
+            <v>カウンターオーラ+</v>
           </cell>
         </row>
         <row r="288">
           <cell r="A288">
-            <v>404040</v>
+            <v>403030</v>
           </cell>
           <cell r="B288" t="str">
-            <v>リザイアフォトン+</v>
+            <v>ラインプロテクト+</v>
           </cell>
         </row>
         <row r="289">
           <cell r="A289">
-            <v>404050</v>
+            <v>403040</v>
           </cell>
           <cell r="B289" t="str">
-            <v>べネディクション+</v>
+            <v>エスコートソール+</v>
           </cell>
         </row>
         <row r="290">
           <cell r="A290">
-            <v>404060</v>
+            <v>403050</v>
           </cell>
           <cell r="B290" t="str">
-            <v>ホーリーグレイス+</v>
+            <v>ディープフリーズ+</v>
           </cell>
         </row>
         <row r="291">
           <cell r="A291">
-            <v>404070</v>
+            <v>403060</v>
           </cell>
           <cell r="B291" t="str">
-            <v>キュアエール+</v>
+            <v>バブルブロウ+</v>
           </cell>
         </row>
         <row r="292">
           <cell r="A292">
-            <v>404080</v>
+            <v>403070</v>
           </cell>
           <cell r="B292" t="str">
-            <v>ラインバリア+</v>
+            <v>アクアミラージュ+</v>
           </cell>
         </row>
         <row r="293">
           <cell r="A293">
-            <v>405010</v>
+            <v>403080</v>
           </cell>
           <cell r="B293" t="str">
-            <v>ダークプリズン+</v>
+            <v>フロストシールド+</v>
           </cell>
         </row>
         <row r="294">
           <cell r="A294">
-            <v>405020</v>
+            <v>404010</v>
           </cell>
           <cell r="B294" t="str">
-            <v>ユーサネイジア+</v>
+            <v>セイントレーザー+</v>
           </cell>
         </row>
         <row r="295">
           <cell r="A295">
-            <v>405030</v>
+            <v>404020</v>
           </cell>
           <cell r="B295" t="str">
-            <v>ドレインヒール+</v>
+            <v>ペネトレイト+</v>
           </cell>
         </row>
         <row r="296">
           <cell r="A296">
-            <v>405040</v>
+            <v>404030</v>
           </cell>
           <cell r="B296" t="str">
-            <v>アビサルデスペア+</v>
+            <v>ヒーリング+</v>
           </cell>
         </row>
         <row r="297">
           <cell r="A297">
-            <v>405050</v>
+            <v>404040</v>
           </cell>
           <cell r="B297" t="str">
-            <v>ディプラヴィティ+</v>
+            <v>リザイアフォトン+</v>
           </cell>
         </row>
         <row r="298">
           <cell r="A298">
-            <v>405060</v>
+            <v>404050</v>
           </cell>
           <cell r="B298" t="str">
-            <v>ダークネス+</v>
+            <v>べネディクション+</v>
           </cell>
         </row>
         <row r="299">
           <cell r="A299">
-            <v>405070</v>
+            <v>404060</v>
           </cell>
           <cell r="B299" t="str">
-            <v>シェイディークラウド+</v>
+            <v>ホーリーグレイス+</v>
           </cell>
         </row>
         <row r="300">
           <cell r="A300">
-            <v>405080</v>
+            <v>404070</v>
           </cell>
           <cell r="B300" t="str">
-            <v>ポイズンブロウ+</v>
+            <v>キュアエール+</v>
           </cell>
         </row>
         <row r="301">
           <cell r="A301">
-            <v>411010</v>
+            <v>404080</v>
           </cell>
           <cell r="B301" t="str">
-            <v>ウルフソウル+</v>
+            <v>ラインバリア+</v>
           </cell>
         </row>
         <row r="302">
           <cell r="A302">
-            <v>411020</v>
+            <v>405010</v>
           </cell>
           <cell r="B302" t="str">
-            <v>プリディカメント+</v>
+            <v>ダークプリズン+</v>
           </cell>
         </row>
         <row r="303">
           <cell r="A303">
-            <v>411030</v>
+            <v>405020</v>
           </cell>
           <cell r="B303" t="str">
-            <v>アサルトシフト+</v>
+            <v>ユーサネイジア+</v>
           </cell>
         </row>
         <row r="304">
           <cell r="A304">
-            <v>411040</v>
+            <v>405030</v>
           </cell>
           <cell r="B304" t="str">
-            <v>アクティブギフト+</v>
+            <v>ドレインヒール+</v>
           </cell>
         </row>
         <row r="305">
           <cell r="A305">
-            <v>411050</v>
+            <v>405040</v>
           </cell>
           <cell r="B305" t="str">
-            <v>イグナイテッド+</v>
+            <v>アビサルデスペア+</v>
           </cell>
         </row>
         <row r="306">
           <cell r="A306">
-            <v>411060</v>
+            <v>405050</v>
           </cell>
           <cell r="B306" t="str">
-            <v>ライジングファイア+</v>
+            <v>ディプラヴィティ+</v>
           </cell>
         </row>
         <row r="307">
           <cell r="A307">
-            <v>411070</v>
+            <v>405060</v>
           </cell>
           <cell r="B307" t="str">
-            <v>ルージュバック+</v>
+            <v>ダークネス+</v>
           </cell>
         </row>
         <row r="308">
           <cell r="A308">
-            <v>411080</v>
+            <v>405070</v>
           </cell>
           <cell r="B308" t="str">
-            <v>パワーエール+</v>
+            <v>シェイディークラウド+</v>
           </cell>
         </row>
         <row r="309">
           <cell r="A309">
-            <v>411090</v>
+            <v>405080</v>
           </cell>
           <cell r="B309" t="str">
-            <v>スレイプニル+</v>
+            <v>ポイズンブロウ+</v>
           </cell>
         </row>
         <row r="310">
           <cell r="A310">
-            <v>412010</v>
+            <v>411010</v>
           </cell>
           <cell r="B310" t="str">
-            <v>エクステンション+</v>
+            <v>ウルフソウル+</v>
           </cell>
         </row>
         <row r="311">
           <cell r="A311">
-            <v>412020</v>
+            <v>411020</v>
           </cell>
           <cell r="B311" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>プリディカメント+</v>
           </cell>
         </row>
         <row r="312">
           <cell r="A312">
-            <v>412030</v>
+            <v>411030</v>
           </cell>
           <cell r="B312" t="str">
-            <v>スウィフトカレント+</v>
+            <v>アサルトシフト+</v>
           </cell>
         </row>
         <row r="313">
           <cell r="A313">
-            <v>412040</v>
+            <v>411040</v>
           </cell>
           <cell r="B313" t="str">
-            <v>イヴェイドオール+</v>
+            <v>アクティブギフト+</v>
           </cell>
         </row>
         <row r="314">
           <cell r="A314">
-            <v>412050</v>
+            <v>411050</v>
           </cell>
           <cell r="B314" t="str">
-            <v>クイックムーブ+</v>
+            <v>イグナイテッド+</v>
           </cell>
         </row>
         <row r="315">
           <cell r="A315">
-            <v>412060</v>
+            <v>411060</v>
           </cell>
           <cell r="B315" t="str">
-            <v>チェイスマジック+</v>
+            <v>ライジングファイア+</v>
           </cell>
         </row>
         <row r="316">
           <cell r="A316">
-            <v>412070</v>
+            <v>411070</v>
           </cell>
           <cell r="B316" t="str">
-            <v>ソーサリーコネクト+</v>
+            <v>ルージュバック+</v>
           </cell>
         </row>
         <row r="317">
           <cell r="A317">
-            <v>412080</v>
+            <v>411080</v>
           </cell>
           <cell r="B317" t="str">
-            <v>ウィンドライズ+</v>
+            <v>パワーエール+</v>
           </cell>
         </row>
         <row r="318">
           <cell r="A318">
-            <v>412090</v>
+            <v>411090</v>
           </cell>
           <cell r="B318" t="str">
-            <v>アウトオブオーダー+</v>
+            <v>スレイプニル+</v>
           </cell>
         </row>
         <row r="319">
           <cell r="A319">
-            <v>413010</v>
+            <v>412010</v>
           </cell>
           <cell r="B319" t="str">
-            <v>アーマーコード+</v>
+            <v>エクステンション+</v>
           </cell>
         </row>
         <row r="320">
           <cell r="A320">
-            <v>413020</v>
+            <v>412020</v>
           </cell>
           <cell r="B320" t="str">
-            <v>クイックバリア+</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="321">
           <cell r="A321">
-            <v>413030</v>
+            <v>412030</v>
           </cell>
           <cell r="B321" t="str">
-            <v>クイックキュア+</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="322">
           <cell r="A322">
-            <v>413040</v>
+            <v>412040</v>
           </cell>
           <cell r="B322" t="str">
-            <v>セルフシールド+</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="323">
           <cell r="A323">
-            <v>413050</v>
+            <v>412050</v>
           </cell>
           <cell r="B323" t="str">
-            <v>パッシブジャミング+</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="324">
           <cell r="A324">
-            <v>413060</v>
+            <v>412060</v>
           </cell>
           <cell r="B324" t="str">
-            <v>サプライカバー+</v>
+            <v>チェイスマジック+</v>
           </cell>
         </row>
         <row r="325">
           <cell r="A325">
-            <v>413070</v>
+            <v>412070</v>
           </cell>
           <cell r="B325" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>ソーサリーコネクト+</v>
           </cell>
         </row>
         <row r="326">
           <cell r="A326">
-            <v>413080</v>
+            <v>412080</v>
           </cell>
           <cell r="B326" t="str">
-            <v>ライフスティール+</v>
+            <v>ウィンドライズ+</v>
           </cell>
         </row>
         <row r="327">
           <cell r="A327">
-            <v>413090</v>
+            <v>412090</v>
           </cell>
           <cell r="B327" t="str">
-            <v>アイスセイバー+</v>
+            <v>アウトオブオーダー+</v>
           </cell>
         </row>
         <row r="328">
           <cell r="A328">
-            <v>414010</v>
+            <v>413010</v>
           </cell>
           <cell r="B328" t="str">
-            <v>ディバインシールド+</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="329">
           <cell r="A329">
-            <v>414020</v>
+            <v>413020</v>
           </cell>
           <cell r="B329" t="str">
-            <v>ライフディバイド+</v>
+            <v>クイックバリア+</v>
           </cell>
         </row>
         <row r="330">
           <cell r="A330">
-            <v>414030</v>
+            <v>413030</v>
           </cell>
           <cell r="B330" t="str">
-            <v>エイミングスコープ+</v>
+            <v>クイックキュア+</v>
           </cell>
         </row>
         <row r="331">
           <cell r="A331">
-            <v>414040</v>
+            <v>413040</v>
           </cell>
           <cell r="B331" t="str">
-            <v>リジェネレーション+</v>
+            <v>セルフシールド+</v>
           </cell>
         </row>
         <row r="332">
           <cell r="A332">
-            <v>414050</v>
+            <v>413050</v>
           </cell>
           <cell r="B332" t="str">
-            <v>ホープフルアイリス+</v>
+            <v>パッシブジャミング+</v>
           </cell>
         </row>
         <row r="333">
           <cell r="A333">
-            <v>414060</v>
+            <v>413060</v>
           </cell>
           <cell r="B333" t="str">
-            <v>パッシブサプライ+</v>
+            <v>サプライカバー+</v>
           </cell>
         </row>
         <row r="334">
           <cell r="A334">
-            <v>414070</v>
+            <v>413070</v>
           </cell>
           <cell r="B334" t="str">
-            <v>ホーミングクルセイド+</v>
+            <v>アシッドラッシュ+</v>
           </cell>
         </row>
         <row r="335">
           <cell r="A335">
-            <v>414080</v>
+            <v>413080</v>
           </cell>
           <cell r="B335" t="str">
-            <v>クイックヒール+</v>
+            <v>ライフスティール+</v>
           </cell>
         </row>
         <row r="336">
           <cell r="A336">
-            <v>414090</v>
+            <v>413090</v>
           </cell>
           <cell r="B336" t="str">
-            <v>リレイズ+</v>
+            <v>アイスセイバー+</v>
           </cell>
         </row>
         <row r="337">
           <cell r="A337">
-            <v>415010</v>
+            <v>414010</v>
           </cell>
           <cell r="B337" t="str">
-            <v>イーグルアイ+</v>
+            <v>ディバインシールド+</v>
           </cell>
         </row>
         <row r="338">
           <cell r="A338">
-            <v>415020</v>
+            <v>414020</v>
           </cell>
           <cell r="B338" t="str">
-            <v>ネヴァーエンド+</v>
+            <v>ライフディバイド+</v>
           </cell>
         </row>
         <row r="339">
           <cell r="A339">
-            <v>415030</v>
+            <v>414030</v>
           </cell>
           <cell r="B339" t="str">
-            <v>グレイブアクト+</v>
+            <v>エイミングスコープ+</v>
           </cell>
         </row>
         <row r="340">
           <cell r="A340">
-            <v>415040</v>
+            <v>414040</v>
           </cell>
           <cell r="B340" t="str">
-            <v>スカルグラッジ+</v>
+            <v>リジェネレーション+</v>
           </cell>
         </row>
         <row r="341">
           <cell r="A341">
-            <v>415050</v>
+            <v>414050</v>
           </cell>
           <cell r="B341" t="str">
-            <v>ネガティブドレイン+</v>
+            <v>ホープフルアイリス+</v>
           </cell>
         </row>
         <row r="342">
           <cell r="A342">
-            <v>415060</v>
+            <v>414060</v>
           </cell>
           <cell r="B342" t="str">
-            <v>アンデッドペイン+</v>
+            <v>パッシブサプライ+</v>
           </cell>
         </row>
         <row r="343">
           <cell r="A343">
-            <v>415070</v>
+            <v>414070</v>
           </cell>
           <cell r="B343" t="str">
-            <v>ジャックポッド+</v>
+            <v>ホーミングクルセイド+</v>
           </cell>
         </row>
         <row r="344">
           <cell r="A344">
-            <v>415080</v>
+            <v>414080</v>
           </cell>
           <cell r="B344" t="str">
-            <v>ヒールハント+</v>
+            <v>クイックヒール+</v>
           </cell>
         </row>
         <row r="345">
           <cell r="A345">
-            <v>415090</v>
+            <v>414090</v>
           </cell>
           <cell r="B345" t="str">
-            <v>クイックカース+</v>
+            <v>リレイズ+</v>
           </cell>
         </row>
         <row r="346">
           <cell r="A346">
-            <v>501010</v>
+            <v>415010</v>
           </cell>
           <cell r="B346" t="str">
-            <v>火傷耐性+20%</v>
+            <v>イーグルアイ+</v>
           </cell>
         </row>
         <row r="347">
           <cell r="A347">
-            <v>501020</v>
+            <v>415020</v>
           </cell>
           <cell r="B347" t="str">
-            <v>命中率+5%</v>
+            <v>ネヴァーエンド+</v>
           </cell>
         </row>
         <row r="348">
           <cell r="A348">
-            <v>501030</v>
+            <v>415030</v>
           </cell>
           <cell r="B348" t="str">
-            <v>最大HP+2</v>
+            <v>グレイブアクト+</v>
           </cell>
         </row>
         <row r="349">
           <cell r="A349">
-            <v>501040</v>
+            <v>415040</v>
           </cell>
           <cell r="B349" t="str">
-            <v>ATK+2</v>
+            <v>スカルグラッジ+</v>
           </cell>
         </row>
         <row r="350">
           <cell r="A350">
-            <v>502010</v>
+            <v>415050</v>
           </cell>
           <cell r="B350" t="str">
-            <v>DEF+1</v>
+            <v>ネガティブドレイン+</v>
           </cell>
         </row>
         <row r="351">
           <cell r="A351">
-            <v>502020</v>
+            <v>415060</v>
           </cell>
           <cell r="B351" t="str">
-            <v>SPD+1</v>
+            <v>アンデッドペイン+</v>
           </cell>
         </row>
         <row r="352">
           <cell r="A352">
-            <v>502030</v>
+            <v>415070</v>
           </cell>
           <cell r="B352" t="str">
-            <v>SPD+1</v>
+            <v>ジャックポッド+</v>
           </cell>
         </row>
         <row r="353">
           <cell r="A353">
-            <v>502040</v>
+            <v>415080</v>
           </cell>
           <cell r="B353" t="str">
-            <v>回避率+5%</v>
+            <v>ヒールハント+</v>
           </cell>
         </row>
         <row r="354">
           <cell r="A354">
-            <v>503010</v>
+            <v>415090</v>
           </cell>
           <cell r="B354" t="str">
-            <v>DEF+1</v>
+            <v>クイックカース+</v>
           </cell>
         </row>
         <row r="355">
           <cell r="A355">
-            <v>503020</v>
+            <v>501010</v>
           </cell>
           <cell r="B355" t="str">
-            <v>凍結耐性+20%</v>
+            <v>火傷耐性+20%</v>
           </cell>
         </row>
         <row r="356">
           <cell r="A356">
-            <v>503030</v>
+            <v>501020</v>
           </cell>
           <cell r="B356" t="str">
-            <v>最大HP+2</v>
+            <v>命中率+5%</v>
           </cell>
         </row>
         <row r="357">
           <cell r="A357">
-            <v>503040</v>
+            <v>501030</v>
           </cell>
           <cell r="B357" t="str">
-            <v>DEF+2</v>
+            <v>最大HP+2</v>
           </cell>
         </row>
         <row r="358">
           <cell r="A358">
-            <v>504010</v>
+            <v>501040</v>
           </cell>
           <cell r="B358" t="str">
-            <v>Hp回復効果+2</v>
+            <v>ATK+2</v>
           </cell>
         </row>
         <row r="359">
           <cell r="A359">
-            <v>504020</v>
+            <v>501110</v>
           </cell>
           <cell r="B359" t="str">
-            <v>SPD+1</v>
+            <v>DEF+2</v>
           </cell>
         </row>
         <row r="360">
           <cell r="A360">
-            <v>504030</v>
+            <v>501120</v>
           </cell>
           <cell r="B360" t="str">
-            <v>命中率+5%</v>
+            <v>命中率+10%</v>
           </cell>
         </row>
         <row r="361">
           <cell r="A361">
-            <v>504040</v>
+            <v>501130</v>
           </cell>
           <cell r="B361" t="str">
-            <v>最大HP+2</v>
+            <v>SPD+2</v>
           </cell>
         </row>
         <row r="362">
           <cell r="A362">
-            <v>505010</v>
+            <v>502010</v>
           </cell>
           <cell r="B362" t="str">
-            <v>回避率+5%</v>
+            <v>DEF+1</v>
           </cell>
         </row>
         <row r="363">
           <cell r="A363">
-            <v>505020</v>
+            <v>502020</v>
           </cell>
           <cell r="B363" t="str">
             <v>SPD+1</v>
@@ -4069,105 +4069,321 @@
         </row>
         <row r="364">
           <cell r="A364">
-            <v>505030</v>
+            <v>502030</v>
           </cell>
           <cell r="B364" t="str">
-            <v>最大HP+2</v>
+            <v>SPD+1</v>
           </cell>
         </row>
         <row r="365">
           <cell r="A365">
-            <v>505040</v>
+            <v>502040</v>
           </cell>
           <cell r="B365" t="str">
-            <v>ATK+1</v>
+            <v>回避率+5%</v>
           </cell>
         </row>
         <row r="366">
           <cell r="A366">
-            <v>506010</v>
+            <v>502110</v>
           </cell>
           <cell r="B366" t="str">
-            <v>最大HP+3</v>
+            <v>会心ダメージ率+25%</v>
           </cell>
         </row>
         <row r="367">
           <cell r="A367">
-            <v>506011</v>
+            <v>502120</v>
           </cell>
           <cell r="B367" t="str">
-            <v>DEF+1</v>
+            <v>命中率+5%</v>
           </cell>
         </row>
         <row r="368">
           <cell r="A368">
-            <v>506012</v>
+            <v>502121</v>
           </cell>
           <cell r="B368" t="str">
-            <v>SPD+1</v>
+            <v>回避率+5%</v>
           </cell>
         </row>
         <row r="369">
           <cell r="A369">
-            <v>506013</v>
+            <v>502130</v>
           </cell>
           <cell r="B369" t="str">
-            <v>EXP+20%</v>
+            <v>SPD+2</v>
           </cell>
         </row>
         <row r="370">
           <cell r="A370">
-            <v>506020</v>
+            <v>503010</v>
           </cell>
           <cell r="B370" t="str">
-            <v>炎属性耐性+20%</v>
+            <v>DEF+1</v>
           </cell>
         </row>
         <row r="371">
           <cell r="A371">
-            <v>506030</v>
+            <v>503020</v>
           </cell>
           <cell r="B371" t="str">
-            <v>雷属性耐性+20%</v>
+            <v>凍結耐性+20%</v>
           </cell>
         </row>
         <row r="372">
           <cell r="A372">
-            <v>506040</v>
+            <v>503030</v>
           </cell>
           <cell r="B372" t="str">
-            <v>氷属性耐性+20%</v>
+            <v>最大HP+2</v>
           </cell>
         </row>
         <row r="373">
           <cell r="A373">
-            <v>506050</v>
+            <v>503040</v>
           </cell>
           <cell r="B373" t="str">
-            <v>光属性耐性+20%</v>
+            <v>DEF+2</v>
           </cell>
         </row>
         <row r="374">
           <cell r="A374">
-            <v>506060</v>
+            <v>503110</v>
           </cell>
           <cell r="B374" t="str">
-            <v>闇属性耐性+20%</v>
+            <v>DEF+2</v>
           </cell>
         </row>
         <row r="375">
           <cell r="A375">
-            <v>507010</v>
+            <v>503120</v>
           </cell>
           <cell r="B375" t="str">
-            <v>獲得Exp+30%</v>
+            <v>ATK+2</v>
           </cell>
         </row>
         <row r="376">
           <cell r="A376">
+            <v>503130</v>
+          </cell>
+          <cell r="B376" t="str">
+            <v>ダメージ軽減効果無視+10%</v>
+          </cell>
+        </row>
+        <row r="377">
+          <cell r="A377">
+            <v>504010</v>
+          </cell>
+          <cell r="B377" t="str">
+            <v>Hp回復効果+2</v>
+          </cell>
+        </row>
+        <row r="378">
+          <cell r="A378">
+            <v>504020</v>
+          </cell>
+          <cell r="B378" t="str">
+            <v>SPD+1</v>
+          </cell>
+        </row>
+        <row r="379">
+          <cell r="A379">
+            <v>504030</v>
+          </cell>
+          <cell r="B379" t="str">
+            <v>命中率+5%</v>
+          </cell>
+        </row>
+        <row r="380">
+          <cell r="A380">
+            <v>504040</v>
+          </cell>
+          <cell r="B380" t="str">
+            <v>最大HP+2</v>
+          </cell>
+        </row>
+        <row r="381">
+          <cell r="A381">
+            <v>504110</v>
+          </cell>
+          <cell r="B381" t="str">
+            <v>命中率+10%</v>
+          </cell>
+        </row>
+        <row r="382">
+          <cell r="A382">
+            <v>504120</v>
+          </cell>
+          <cell r="B382" t="str">
+            <v>最大HP+2</v>
+          </cell>
+        </row>
+        <row r="383">
+          <cell r="A383">
+            <v>504130</v>
+          </cell>
+          <cell r="B383" t="str">
+            <v>ダメージ軽減効果無視+10%</v>
+          </cell>
+        </row>
+        <row r="384">
+          <cell r="A384">
+            <v>505010</v>
+          </cell>
+          <cell r="B384" t="str">
+            <v>回避率+5%</v>
+          </cell>
+        </row>
+        <row r="385">
+          <cell r="A385">
+            <v>505020</v>
+          </cell>
+          <cell r="B385" t="str">
+            <v>SPD+1</v>
+          </cell>
+        </row>
+        <row r="386">
+          <cell r="A386">
+            <v>505030</v>
+          </cell>
+          <cell r="B386" t="str">
+            <v>最大HP+2</v>
+          </cell>
+        </row>
+        <row r="387">
+          <cell r="A387">
+            <v>505040</v>
+          </cell>
+          <cell r="B387" t="str">
+            <v>ATK+1</v>
+          </cell>
+        </row>
+        <row r="388">
+          <cell r="A388">
+            <v>505110</v>
+          </cell>
+          <cell r="B388" t="str">
+            <v>命中率+5%</v>
+          </cell>
+        </row>
+        <row r="389">
+          <cell r="A389">
+            <v>505111</v>
+          </cell>
+          <cell r="B389" t="str">
+            <v>回避率+5%</v>
+          </cell>
+        </row>
+        <row r="390">
+          <cell r="A390">
+            <v>505120</v>
+          </cell>
+          <cell r="B390" t="str">
+            <v>ATK+1</v>
+          </cell>
+        </row>
+        <row r="391">
+          <cell r="A391">
+            <v>505121</v>
+          </cell>
+          <cell r="B391" t="str">
+            <v>SPD+1</v>
+          </cell>
+        </row>
+        <row r="392">
+          <cell r="A392">
+            <v>505130</v>
+          </cell>
+          <cell r="B392" t="str">
+            <v>SPD+2</v>
+          </cell>
+        </row>
+        <row r="393">
+          <cell r="A393">
+            <v>506010</v>
+          </cell>
+          <cell r="B393" t="str">
+            <v>最大HP+3</v>
+          </cell>
+        </row>
+        <row r="394">
+          <cell r="A394">
+            <v>506011</v>
+          </cell>
+          <cell r="B394" t="str">
+            <v>DEF+1</v>
+          </cell>
+        </row>
+        <row r="395">
+          <cell r="A395">
+            <v>506012</v>
+          </cell>
+          <cell r="B395" t="str">
+            <v>SPD+1</v>
+          </cell>
+        </row>
+        <row r="396">
+          <cell r="A396">
+            <v>506013</v>
+          </cell>
+          <cell r="B396" t="str">
+            <v>EXP+20%</v>
+          </cell>
+        </row>
+        <row r="397">
+          <cell r="A397">
+            <v>506020</v>
+          </cell>
+          <cell r="B397" t="str">
+            <v>炎属性耐性+20%</v>
+          </cell>
+        </row>
+        <row r="398">
+          <cell r="A398">
+            <v>506030</v>
+          </cell>
+          <cell r="B398" t="str">
+            <v>雷属性耐性+20%</v>
+          </cell>
+        </row>
+        <row r="399">
+          <cell r="A399">
+            <v>506040</v>
+          </cell>
+          <cell r="B399" t="str">
+            <v>氷属性耐性+20%</v>
+          </cell>
+        </row>
+        <row r="400">
+          <cell r="A400">
+            <v>506050</v>
+          </cell>
+          <cell r="B400" t="str">
+            <v>光属性耐性+20%</v>
+          </cell>
+        </row>
+        <row r="401">
+          <cell r="A401">
+            <v>506060</v>
+          </cell>
+          <cell r="B401" t="str">
+            <v>闇属性耐性+20%</v>
+          </cell>
+        </row>
+        <row r="402">
+          <cell r="A402">
+            <v>507010</v>
+          </cell>
+          <cell r="B402" t="str">
+            <v>獲得Exp+30%</v>
+          </cell>
+        </row>
+        <row r="403">
+          <cell r="A403">
             <v>507020</v>
           </cell>
-          <cell r="B376" t="str">
+          <cell r="B403" t="str">
             <v>ATK⇔DEF交換</v>
           </cell>
         </row>
@@ -5716,22 +5932,22 @@
         <v>100</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H21">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I21">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="J21">
         <v>1</v>
       </c>
       <c r="K21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L21">
         <v>12</v>
@@ -5740,22 +5956,22 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="Q21">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="R21">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="S21" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -6644,7 +6860,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G231"/>
+  <dimension ref="A1:G235"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="16.7272727272727" customWidth="1"/>
@@ -8502,11 +8718,11 @@
         <v>13</v>
       </c>
       <c r="B78">
-        <v>14080</v>
+        <v>14040</v>
       </c>
       <c r="C78" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B78,[1]TextData!A:A))</f>
-        <v>ホーミングクルセイド</v>
+        <v>ホープフルアイリス</v>
       </c>
       <c r="D78">
         <v>20</v>
@@ -9298,7 +9514,7 @@
       </c>
       <c r="C111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B111,[1]TextData!A:A))</f>
-        <v>プルガシオン</v>
+        <v>ハードウォール</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -9322,7 +9538,7 @@
       </c>
       <c r="C112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B112,[1]TextData!A:A))</f>
-        <v>プリエステス</v>
+        <v>リファクター</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -9346,7 +9562,7 @@
       </c>
       <c r="C113" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B113,[1]TextData!A:A))</f>
-        <v>悪魔(パイモン)</v>
+        <v>悪魔(アモン)</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -9366,11 +9582,11 @@
         <v>104</v>
       </c>
       <c r="B114">
-        <v>2010</v>
+        <v>5010</v>
       </c>
       <c r="C114" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B114,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -9390,17 +9606,17 @@
         <v>104</v>
       </c>
       <c r="B115">
-        <v>200410</v>
+        <v>5120</v>
       </c>
       <c r="C115" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B115,[1]TextData!A:A))</f>
-        <v>コウソクテンショウ</v>
+        <v>ユーサネイジア</v>
       </c>
       <c r="D115">
         <v>1</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F115">
         <v>0</v>
@@ -9414,20 +9630,20 @@
         <v>104</v>
       </c>
       <c r="B116">
-        <v>200420</v>
+        <v>5110</v>
       </c>
       <c r="C116" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B116,[1]TextData!A:A))</f>
-        <v>アンチバフ</v>
+        <v>ドレインヒール</v>
       </c>
       <c r="D116">
         <v>1</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F116">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -9438,11 +9654,11 @@
         <v>104</v>
       </c>
       <c r="B117">
-        <v>200430</v>
+        <v>15040</v>
       </c>
       <c r="C117" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B117,[1]TextData!A:A))</f>
-        <v>悪魔(アンドラス)</v>
+        <v>ネガティブドレイン</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -9459,20 +9675,20 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B118">
-        <v>3010</v>
+        <v>15130</v>
       </c>
       <c r="C118" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B118,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>リヴェンジャー</v>
       </c>
       <c r="D118">
         <v>1</v>
       </c>
       <c r="E118">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -9483,20 +9699,20 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B119">
-        <v>3070</v>
+        <v>200310</v>
       </c>
       <c r="C119" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B119,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>ハードウォール</v>
       </c>
       <c r="D119">
         <v>1</v>
       </c>
       <c r="E119">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F119">
         <v>0</v>
@@ -9507,14 +9723,14 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B120">
-        <v>200510</v>
+        <v>200320</v>
       </c>
       <c r="C120" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B120,[1]TextData!A:A))</f>
-        <v>カウントダウン</v>
+        <v>リファクター</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -9531,20 +9747,20 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B121">
-        <v>200520</v>
+        <v>200330</v>
       </c>
       <c r="C121" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B121,[1]TextData!A:A))</f>
-        <v>グラウンドゼロ</v>
+        <v>悪魔(アモン)</v>
       </c>
       <c r="D121">
         <v>1</v>
       </c>
       <c r="E121">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F121">
         <v>0</v>
@@ -9558,17 +9774,17 @@
         <v>105</v>
       </c>
       <c r="B122">
-        <v>200530</v>
+        <v>3010</v>
       </c>
       <c r="C122" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B122,[1]TextData!A:A))</f>
-        <v>悪魔(ビフロンス)</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D122">
         <v>1</v>
       </c>
       <c r="E122">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F122">
         <v>0</v>
@@ -9582,17 +9798,17 @@
         <v>105</v>
       </c>
       <c r="B123">
-        <v>403070</v>
+        <v>3070</v>
       </c>
       <c r="C123" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B123,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D123">
         <v>1</v>
       </c>
       <c r="E123">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F123">
         <v>0</v>
@@ -9603,20 +9819,20 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="B124">
-        <v>4010</v>
+        <v>200510</v>
       </c>
       <c r="C124" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B124,[1]TextData!A:A))</f>
-        <v>セイントレーザー</v>
+        <v>カウントダウン</v>
       </c>
       <c r="D124">
         <v>1</v>
       </c>
       <c r="E124">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F124">
         <v>0</v>
@@ -9627,23 +9843,23 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125">
-        <v>1001</v>
+        <v>105</v>
       </c>
       <c r="B125">
-        <v>1010</v>
+        <v>200520</v>
       </c>
       <c r="C125" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B125,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>グラウンドゼロ</v>
       </c>
       <c r="D125">
         <v>1</v>
       </c>
       <c r="E125">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F125">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -9651,23 +9867,23 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126">
-        <v>1001</v>
+        <v>105</v>
       </c>
       <c r="B126">
-        <v>1060</v>
+        <v>200530</v>
       </c>
       <c r="C126" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B126,[1]TextData!A:A))</f>
-        <v>フレイムレイン</v>
+        <v>悪魔(ビフロンス)</v>
       </c>
       <c r="D126">
         <v>1</v>
       </c>
       <c r="E126">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F126">
-        <v>5061</v>
+        <v>0</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -9675,14 +9891,14 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127">
-        <v>1001</v>
+        <v>105</v>
       </c>
       <c r="B127">
-        <v>100110</v>
+        <v>403070</v>
       </c>
       <c r="C127" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B127,[1]TextData!A:A))</f>
-        <v>ソーイングアームド</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -9699,20 +9915,20 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="B128">
-        <v>100120</v>
+        <v>4010</v>
       </c>
       <c r="C128" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B128,[1]TextData!A:A))</f>
-        <v>エターナルロンド</v>
+        <v>セイントレーザー</v>
       </c>
       <c r="D128">
         <v>1</v>
       </c>
       <c r="E128">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F128">
         <v>0</v>
@@ -9726,20 +9942,20 @@
         <v>1001</v>
       </c>
       <c r="B129">
-        <v>11060</v>
+        <v>1010</v>
       </c>
       <c r="C129" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B129,[1]TextData!A:A))</f>
-        <v>キュアファイア</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D129">
         <v>1</v>
       </c>
       <c r="E129">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F129">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -9750,20 +9966,20 @@
         <v>1001</v>
       </c>
       <c r="B130">
-        <v>14010</v>
+        <v>1060</v>
       </c>
       <c r="C130" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B130,[1]TextData!A:A))</f>
-        <v>ファーストエイド</v>
+        <v>フレイムレイン</v>
       </c>
       <c r="D130">
         <v>1</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F130">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -9774,11 +9990,11 @@
         <v>1001</v>
       </c>
       <c r="B131">
-        <v>12010</v>
+        <v>100110</v>
       </c>
       <c r="C131" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B131,[1]TextData!A:A))</f>
-        <v>クロースエッジ</v>
+        <v>ソーイングアームド</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -9798,17 +10014,17 @@
         <v>1001</v>
       </c>
       <c r="B132">
-        <v>12060</v>
+        <v>100120</v>
       </c>
       <c r="C132" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B132,[1]TextData!A:A))</f>
-        <v>キュアスタン</v>
+        <v>エターナルロンド</v>
       </c>
       <c r="D132">
         <v>1</v>
       </c>
       <c r="E132">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F132">
         <v>0</v>
@@ -9819,23 +10035,23 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B133">
-        <v>2010</v>
+        <v>11060</v>
       </c>
       <c r="C133" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B133,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>キュアファイア</v>
       </c>
       <c r="D133">
         <v>1</v>
       </c>
       <c r="E133">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F133">
-        <v>5060</v>
+        <v>0</v>
       </c>
       <c r="G133">
         <v>0</v>
@@ -9843,20 +10059,20 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B134">
-        <v>2070</v>
+        <v>14010</v>
       </c>
       <c r="C134" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B134,[1]TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>ファーストエイド</v>
       </c>
       <c r="D134">
         <v>1</v>
       </c>
       <c r="E134">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -9867,14 +10083,14 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B135">
-        <v>100210</v>
+        <v>12010</v>
       </c>
       <c r="C135" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B135,[1]TextData!A:A))</f>
-        <v>ピースメーカー</v>
+        <v>クロースエッジ</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -9891,26 +10107,26 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B136">
-        <v>100220</v>
+        <v>12060</v>
       </c>
       <c r="C136" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B136,[1]TextData!A:A))</f>
-        <v>レヴェリー</v>
+        <v>キュアスタン</v>
       </c>
       <c r="D136">
         <v>1</v>
       </c>
       <c r="E136">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F136">
-        <v>14211</v>
+        <v>0</v>
       </c>
       <c r="G136">
-        <v>5060</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -9918,20 +10134,20 @@
         <v>1002</v>
       </c>
       <c r="B137">
-        <v>402070</v>
+        <v>2010</v>
       </c>
       <c r="C137" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B137,[1]TextData!A:A))</f>
-        <v>コンセントレイト+</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D137">
         <v>1</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F137">
-        <v>0</v>
+        <v>5060</v>
       </c>
       <c r="G137">
         <v>0</v>
@@ -9942,17 +10158,17 @@
         <v>1002</v>
       </c>
       <c r="B138">
-        <v>12080</v>
+        <v>2070</v>
       </c>
       <c r="C138" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B138,[1]TextData!A:A))</f>
-        <v>ソーサリーコネクト</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D138">
         <v>1</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -9966,11 +10182,11 @@
         <v>1002</v>
       </c>
       <c r="B139">
-        <v>12040</v>
+        <v>100210</v>
       </c>
       <c r="C139" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B139,[1]TextData!A:A))</f>
-        <v>ヘブンリーラック</v>
+        <v>ピースメーカー</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -9990,23 +10206,23 @@
         <v>1002</v>
       </c>
       <c r="B140">
-        <v>12050</v>
+        <v>100220</v>
       </c>
       <c r="C140" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B140,[1]TextData!A:A))</f>
-        <v>キュアスタン</v>
+        <v>レヴェリー</v>
       </c>
       <c r="D140">
         <v>1</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F140">
-        <v>0</v>
+        <v>14211</v>
       </c>
       <c r="G140">
-        <v>0</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -10014,11 +10230,11 @@
         <v>1002</v>
       </c>
       <c r="B141">
-        <v>12010</v>
+        <v>402070</v>
       </c>
       <c r="C141" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B141,[1]TextData!A:A))</f>
-        <v>クロースエッジ</v>
+        <v>コンセントレイト+</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -10035,20 +10251,20 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B142">
-        <v>3010</v>
+        <v>12080</v>
       </c>
       <c r="C142" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B142,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>キュアスタン</v>
       </c>
       <c r="D142">
         <v>1</v>
       </c>
       <c r="E142">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F142">
         <v>0</v>
@@ -10059,23 +10275,23 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B143">
-        <v>3020</v>
+        <v>12040</v>
       </c>
       <c r="C143" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B143,[1]TextData!A:A))</f>
-        <v>シールドバッシュ</v>
+        <v>ヘブンリーラック</v>
       </c>
       <c r="D143">
         <v>1</v>
       </c>
       <c r="E143">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F143">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G143">
         <v>0</v>
@@ -10083,14 +10299,14 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B144">
-        <v>100310</v>
+        <v>12050</v>
       </c>
       <c r="C144" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B144,[1]TextData!A:A))</f>
-        <v>セイクリッドバリア</v>
+        <v>キュアスタン</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -10107,23 +10323,23 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B145">
-        <v>100320</v>
+        <v>12010</v>
       </c>
       <c r="C145" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B145,[1]TextData!A:A))</f>
-        <v>リベンジニードル</v>
+        <v>クロースエッジ</v>
       </c>
       <c r="D145">
         <v>1</v>
       </c>
       <c r="E145">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F145">
-        <v>14214</v>
+        <v>0</v>
       </c>
       <c r="G145">
         <v>0</v>
@@ -10134,17 +10350,17 @@
         <v>1003</v>
       </c>
       <c r="B146">
-        <v>403020</v>
+        <v>3010</v>
       </c>
       <c r="C146" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B146,[1]TextData!A:A))</f>
-        <v>カウンターオーラ+</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D146">
         <v>1</v>
       </c>
       <c r="E146">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F146">
         <v>0</v>
@@ -10158,20 +10374,20 @@
         <v>1003</v>
       </c>
       <c r="B147">
-        <v>403010</v>
+        <v>3020</v>
       </c>
       <c r="C147" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B147,[1]TextData!A:A))</f>
-        <v>アイスブレイド+</v>
+        <v>シールドバッシュ</v>
       </c>
       <c r="D147">
         <v>1</v>
       </c>
       <c r="E147">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -10182,11 +10398,11 @@
         <v>1003</v>
       </c>
       <c r="B148">
-        <v>13020</v>
+        <v>100310</v>
       </c>
       <c r="C148" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B148,[1]TextData!A:A))</f>
-        <v>アイシクルエッジ</v>
+        <v>セイクリッドバリア</v>
       </c>
       <c r="D148">
         <v>1</v>
@@ -10206,20 +10422,20 @@
         <v>1003</v>
       </c>
       <c r="B149">
-        <v>13080</v>
+        <v>100320</v>
       </c>
       <c r="C149" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B149,[1]TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
+        <v>リベンジニードル</v>
       </c>
       <c r="D149">
         <v>1</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>14214</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -10230,11 +10446,11 @@
         <v>1003</v>
       </c>
       <c r="B150">
-        <v>14050</v>
+        <v>403020</v>
       </c>
       <c r="C150" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B150,[1]TextData!A:A))</f>
-        <v>キュアパッシブ</v>
+        <v>カウンターオーラ+</v>
       </c>
       <c r="D150">
         <v>1</v>
@@ -10251,20 +10467,20 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B151">
-        <v>4010</v>
+        <v>403010</v>
       </c>
       <c r="C151" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B151,[1]TextData!A:A))</f>
-        <v>セイントレーザー</v>
+        <v>アイスブレイド+</v>
       </c>
       <c r="D151">
         <v>1</v>
       </c>
       <c r="E151">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F151">
         <v>0</v>
@@ -10275,23 +10491,23 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B152">
-        <v>4030</v>
+        <v>13020</v>
       </c>
       <c r="C152" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B152,[1]TextData!A:A))</f>
-        <v>ヒーリング</v>
+        <v>アイシクルエッジ</v>
       </c>
       <c r="D152">
         <v>1</v>
       </c>
       <c r="E152">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F152">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -10299,14 +10515,14 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B153">
-        <v>100410</v>
+        <v>13080</v>
       </c>
       <c r="C153" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B153,[1]TextData!A:A))</f>
-        <v>アバンデンス</v>
+        <v>アシッドラッシュ</v>
       </c>
       <c r="D153">
         <v>1</v>
@@ -10323,20 +10539,20 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B154">
-        <v>100420</v>
+        <v>14050</v>
       </c>
       <c r="C154" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B154,[1]TextData!A:A))</f>
-        <v>ハーヴェスト</v>
+        <v>キュアパッシブ</v>
       </c>
       <c r="D154">
         <v>1</v>
       </c>
       <c r="E154">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -10350,17 +10566,17 @@
         <v>1004</v>
       </c>
       <c r="B155">
-        <v>404030</v>
+        <v>4010</v>
       </c>
       <c r="C155" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B155,[1]TextData!A:A))</f>
-        <v>ヒーリング+</v>
+        <v>セイントレーザー</v>
       </c>
       <c r="D155">
         <v>1</v>
       </c>
       <c r="E155">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F155">
         <v>0</v>
@@ -10374,20 +10590,20 @@
         <v>1004</v>
       </c>
       <c r="B156">
-        <v>14080</v>
+        <v>4030</v>
       </c>
       <c r="C156" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B156,[1]TextData!A:A))</f>
-        <v>ホーミングクルセイド</v>
+        <v>ヒーリング</v>
       </c>
       <c r="D156">
         <v>1</v>
       </c>
       <c r="E156">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="G156">
         <v>0</v>
@@ -10398,11 +10614,11 @@
         <v>1004</v>
       </c>
       <c r="B157">
-        <v>14010</v>
+        <v>100410</v>
       </c>
       <c r="C157" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B157,[1]TextData!A:A))</f>
-        <v>ファーストエイド</v>
+        <v>アバンデンス</v>
       </c>
       <c r="D157">
         <v>1</v>
@@ -10411,7 +10627,7 @@
         <v>0</v>
       </c>
       <c r="F157">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G157">
         <v>0</v>
@@ -10422,17 +10638,17 @@
         <v>1004</v>
       </c>
       <c r="B158">
-        <v>14040</v>
+        <v>100420</v>
       </c>
       <c r="C158" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B158,[1]TextData!A:A))</f>
-        <v>ホープフルアイリス</v>
+        <v>ハーヴェスト</v>
       </c>
       <c r="D158">
         <v>1</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -10446,11 +10662,11 @@
         <v>1004</v>
       </c>
       <c r="B159">
-        <v>14090</v>
+        <v>404030</v>
       </c>
       <c r="C159" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B159,[1]TextData!A:A))</f>
-        <v>リレイズ</v>
+        <v>ヒーリング+</v>
       </c>
       <c r="D159">
         <v>1</v>
@@ -10467,20 +10683,20 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B160">
-        <v>5010</v>
+        <v>14080</v>
       </c>
       <c r="C160" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B160,[1]TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>ホーミングクルセイド</v>
       </c>
       <c r="D160">
         <v>1</v>
       </c>
       <c r="E160">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -10491,23 +10707,23 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B161">
-        <v>5070</v>
+        <v>14010</v>
       </c>
       <c r="C161" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B161,[1]TextData!A:A))</f>
-        <v>ダークネス</v>
+        <v>ファーストエイド</v>
       </c>
       <c r="D161">
         <v>1</v>
       </c>
       <c r="E161">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F161">
-        <v>5061</v>
+        <v>1023</v>
       </c>
       <c r="G161">
         <v>0</v>
@@ -10515,14 +10731,14 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B162">
-        <v>100510</v>
+        <v>14040</v>
       </c>
       <c r="C162" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B162,[1]TextData!A:A))</f>
-        <v>カースドブレイク</v>
+        <v>ホープフルアイリス</v>
       </c>
       <c r="D162">
         <v>1</v>
@@ -10539,20 +10755,20 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B163">
-        <v>100520</v>
+        <v>14090</v>
       </c>
       <c r="C163" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B163,[1]TextData!A:A))</f>
-        <v>ムーンライトレイ</v>
+        <v>リレイズ</v>
       </c>
       <c r="D163">
         <v>1</v>
       </c>
       <c r="E163">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F163">
         <v>0</v>
@@ -10566,17 +10782,17 @@
         <v>1005</v>
       </c>
       <c r="B164">
-        <v>15090</v>
+        <v>5010</v>
       </c>
       <c r="C164" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B164,[1]TextData!A:A))</f>
-        <v>ヒールハント</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="D164">
         <v>1</v>
       </c>
       <c r="E164">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -10590,20 +10806,20 @@
         <v>1005</v>
       </c>
       <c r="B165">
-        <v>405070</v>
+        <v>5070</v>
       </c>
       <c r="C165" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B165,[1]TextData!A:A))</f>
-        <v>シェイディークラウド+</v>
+        <v>ダークネス</v>
       </c>
       <c r="D165">
         <v>1</v>
       </c>
       <c r="E165">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>5061</v>
       </c>
       <c r="G165">
         <v>0</v>
@@ -10614,11 +10830,11 @@
         <v>1005</v>
       </c>
       <c r="B166">
-        <v>15080</v>
+        <v>100510</v>
       </c>
       <c r="C166" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B166,[1]TextData!A:A))</f>
-        <v>ヒールハント</v>
+        <v>カースドブレイク</v>
       </c>
       <c r="D166">
         <v>1</v>
@@ -10638,17 +10854,17 @@
         <v>1005</v>
       </c>
       <c r="B167">
-        <v>405010</v>
+        <v>100520</v>
       </c>
       <c r="C167" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B167,[1]TextData!A:A))</f>
-        <v>ダークプリズン+</v>
+        <v>ムーンライトレイ</v>
       </c>
       <c r="D167">
         <v>1</v>
       </c>
       <c r="E167">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -10662,11 +10878,11 @@
         <v>1005</v>
       </c>
       <c r="B168">
-        <v>415090</v>
+        <v>15090</v>
       </c>
       <c r="C168" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B168,[1]TextData!A:A))</f>
-        <v>クイックカース+</v>
+        <v>ヒールハント</v>
       </c>
       <c r="D168">
         <v>1</v>
@@ -10683,20 +10899,20 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B169">
-        <v>1010</v>
+        <v>405070</v>
       </c>
       <c r="C169" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B169,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>シェイディークラウド+</v>
       </c>
       <c r="D169">
         <v>1</v>
       </c>
       <c r="E169">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F169">
         <v>0</v>
@@ -10707,47 +10923,47 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B170">
-        <v>1030</v>
+        <v>15080</v>
       </c>
       <c r="C170" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B170,[1]TextData!A:A))</f>
-        <v>ブレイクウォール</v>
+        <v>ヒールハント</v>
       </c>
       <c r="D170">
         <v>1</v>
       </c>
       <c r="E170">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F170">
-        <v>9120</v>
+        <v>0</v>
       </c>
       <c r="G170">
-        <v>1023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:7">
       <c r="A171">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B171">
-        <v>1070</v>
+        <v>405010</v>
       </c>
       <c r="C171" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B171,[1]TextData!A:A))</f>
-        <v>バーニングソウル</v>
+        <v>ダークプリズン+</v>
       </c>
       <c r="D171">
         <v>1</v>
       </c>
       <c r="E171">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F171">
-        <v>6322</v>
+        <v>0</v>
       </c>
       <c r="G171">
         <v>0</v>
@@ -10755,14 +10971,14 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B172">
-        <v>100610</v>
+        <v>415090</v>
       </c>
       <c r="C172" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B172,[1]TextData!A:A))</f>
-        <v>サンフレイム</v>
+        <v>クイックカース+</v>
       </c>
       <c r="D172">
         <v>1</v>
@@ -10782,17 +10998,17 @@
         <v>1006</v>
       </c>
       <c r="B173">
-        <v>100620</v>
+        <v>1010</v>
       </c>
       <c r="C173" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B173,[1]TextData!A:A))</f>
-        <v>フレイムタン</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D173">
         <v>1</v>
       </c>
       <c r="E173">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F173">
         <v>0</v>
@@ -10806,23 +11022,23 @@
         <v>1006</v>
       </c>
       <c r="B174">
-        <v>11040</v>
+        <v>1030</v>
       </c>
       <c r="C174" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B174,[1]TextData!A:A))</f>
-        <v>ウルフソウル</v>
+        <v>ブレイクウォール</v>
       </c>
       <c r="D174">
         <v>1</v>
       </c>
       <c r="E174">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F174">
-        <v>5042</v>
+        <v>9120</v>
       </c>
       <c r="G174">
-        <v>0</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -10830,20 +11046,20 @@
         <v>1006</v>
       </c>
       <c r="B175">
-        <v>401030</v>
+        <v>1070</v>
       </c>
       <c r="C175" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B175,[1]TextData!A:A))</f>
-        <v>ヒートスタンプ+</v>
+        <v>バーニングソウル</v>
       </c>
       <c r="D175">
         <v>1</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F175">
-        <v>0</v>
+        <v>6322</v>
       </c>
       <c r="G175">
         <v>0</v>
@@ -10854,11 +11070,11 @@
         <v>1006</v>
       </c>
       <c r="B176">
-        <v>411040</v>
+        <v>100610</v>
       </c>
       <c r="C176" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B176,[1]TextData!A:A))</f>
-        <v>アクティブギフト+</v>
+        <v>サンフレイム</v>
       </c>
       <c r="D176">
         <v>1</v>
@@ -10878,17 +11094,17 @@
         <v>1006</v>
       </c>
       <c r="B177">
-        <v>13040</v>
+        <v>100620</v>
       </c>
       <c r="C177" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B177,[1]TextData!A:A))</f>
-        <v>アーマーコード</v>
+        <v>フレイムタン</v>
       </c>
       <c r="D177">
         <v>1</v>
       </c>
       <c r="E177">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F177">
         <v>0</v>
@@ -10899,23 +11115,23 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B178">
-        <v>2010</v>
+        <v>11040</v>
       </c>
       <c r="C178" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B178,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>ウルフソウル</v>
       </c>
       <c r="D178">
         <v>1</v>
       </c>
       <c r="E178">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F178">
-        <v>0</v>
+        <v>5042</v>
       </c>
       <c r="G178">
         <v>0</v>
@@ -10923,23 +11139,23 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B179">
-        <v>2040</v>
+        <v>401030</v>
       </c>
       <c r="C179" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B179,[1]TextData!A:A))</f>
-        <v>トラストチェイン</v>
+        <v>ヒートスタンプ+</v>
       </c>
       <c r="D179">
         <v>1</v>
       </c>
       <c r="E179">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F179">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G179">
         <v>0</v>
@@ -10947,14 +11163,14 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B180">
-        <v>100710</v>
+        <v>411040</v>
       </c>
       <c r="C180" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B180,[1]TextData!A:A))</f>
-        <v>ライズザフラッグ</v>
+        <v>アクティブギフト+</v>
       </c>
       <c r="D180">
         <v>1</v>
@@ -10971,20 +11187,20 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B181">
-        <v>100720</v>
+        <v>13040</v>
       </c>
       <c r="C181" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B181,[1]TextData!A:A))</f>
-        <v>オーバーリミット</v>
+        <v>アーマーコード</v>
       </c>
       <c r="D181">
         <v>1</v>
       </c>
       <c r="E181">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F181">
         <v>0</v>
@@ -10998,20 +11214,20 @@
         <v>1007</v>
       </c>
       <c r="B182">
-        <v>12090</v>
+        <v>2010</v>
       </c>
       <c r="C182" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B182,[1]TextData!A:A))</f>
-        <v>アウトオブオーダー</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D182">
         <v>1</v>
       </c>
       <c r="E182">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F182">
-        <v>5042</v>
+        <v>0</v>
       </c>
       <c r="G182">
         <v>0</v>
@@ -11022,20 +11238,20 @@
         <v>1007</v>
       </c>
       <c r="B183">
-        <v>412090</v>
+        <v>2040</v>
       </c>
       <c r="C183" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B183,[1]TextData!A:A))</f>
-        <v>アウトオブオーダー+</v>
+        <v>スパイラルソード</v>
       </c>
       <c r="D183">
         <v>1</v>
       </c>
       <c r="E183">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F183">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G183">
         <v>0</v>
@@ -11046,11 +11262,11 @@
         <v>1007</v>
       </c>
       <c r="B184">
-        <v>12050</v>
+        <v>100710</v>
       </c>
       <c r="C184" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B184,[1]TextData!A:A))</f>
-        <v>キュアスタン</v>
+        <v>ライズザフラッグ</v>
       </c>
       <c r="D184">
         <v>1</v>
@@ -11070,17 +11286,17 @@
         <v>1007</v>
       </c>
       <c r="B185">
-        <v>12070</v>
+        <v>100720</v>
       </c>
       <c r="C185" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B185,[1]TextData!A:A))</f>
-        <v>ソーサリーコネクト</v>
+        <v>オーバーリミット</v>
       </c>
       <c r="D185">
         <v>1</v>
       </c>
       <c r="E185">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F185">
         <v>0</v>
@@ -11094,11 +11310,11 @@
         <v>1007</v>
       </c>
       <c r="B186">
-        <v>14030</v>
+        <v>12090</v>
       </c>
       <c r="C186" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B186,[1]TextData!A:A))</f>
-        <v>ガードバインド</v>
+        <v>アウトオブオーダー</v>
       </c>
       <c r="D186">
         <v>1</v>
@@ -11107,7 +11323,7 @@
         <v>0</v>
       </c>
       <c r="F186">
-        <v>0</v>
+        <v>5042</v>
       </c>
       <c r="G186">
         <v>0</v>
@@ -11115,20 +11331,20 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B187">
-        <v>3010</v>
+        <v>412090</v>
       </c>
       <c r="C187" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B187,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>アウトオブオーダー+</v>
       </c>
       <c r="D187">
         <v>1</v>
       </c>
       <c r="E187">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F187">
         <v>0</v>
@@ -11139,20 +11355,20 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B188">
-        <v>3070</v>
+        <v>12050</v>
       </c>
       <c r="C188" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B188,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>キュアスタン</v>
       </c>
       <c r="D188">
         <v>1</v>
       </c>
       <c r="E188">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F188">
         <v>0</v>
@@ -11163,14 +11379,14 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B189">
-        <v>100810</v>
+        <v>12070</v>
       </c>
       <c r="C189" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B189,[1]TextData!A:A))</f>
-        <v>テンパランス</v>
+        <v>キュアスタン</v>
       </c>
       <c r="D189">
         <v>1</v>
@@ -11187,20 +11403,20 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B190">
-        <v>100820</v>
+        <v>14030</v>
       </c>
       <c r="C190" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B190,[1]TextData!A:A))</f>
-        <v>シエルクルセイダー</v>
+        <v>ガードバインド</v>
       </c>
       <c r="D190">
         <v>1</v>
       </c>
       <c r="E190">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F190">
         <v>0</v>
@@ -11214,20 +11430,20 @@
         <v>1008</v>
       </c>
       <c r="B191">
-        <v>13060</v>
+        <v>3010</v>
       </c>
       <c r="C191" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B191,[1]TextData!A:A))</f>
-        <v>キュアフリーズ</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D191">
         <v>1</v>
       </c>
       <c r="E191">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F191">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="G191">
         <v>0</v>
@@ -11238,17 +11454,17 @@
         <v>1008</v>
       </c>
       <c r="B192">
-        <v>403070</v>
+        <v>3070</v>
       </c>
       <c r="C192" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B192,[1]TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D192">
         <v>1</v>
       </c>
       <c r="E192">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F192">
         <v>0</v>
@@ -11262,11 +11478,11 @@
         <v>1008</v>
       </c>
       <c r="B193">
-        <v>13010</v>
+        <v>100810</v>
       </c>
       <c r="C193" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B193,[1]TextData!A:A))</f>
-        <v>ヘビィカバー</v>
+        <v>テンパランス</v>
       </c>
       <c r="D193">
         <v>1</v>
@@ -11286,17 +11502,17 @@
         <v>1008</v>
       </c>
       <c r="B194">
-        <v>13020</v>
+        <v>100820</v>
       </c>
       <c r="C194" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B194,[1]TextData!A:A))</f>
-        <v>アイシクルエッジ</v>
+        <v>シエルクルセイダー</v>
       </c>
       <c r="D194">
         <v>1</v>
       </c>
       <c r="E194">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F194">
         <v>0</v>
@@ -11310,11 +11526,11 @@
         <v>1008</v>
       </c>
       <c r="B195">
-        <v>13040</v>
+        <v>13060</v>
       </c>
       <c r="C195" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B195,[1]TextData!A:A))</f>
-        <v>アーマーコード</v>
+        <v>キュアフリーズ</v>
       </c>
       <c r="D195">
         <v>1</v>
@@ -11323,7 +11539,7 @@
         <v>0</v>
       </c>
       <c r="F195">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="G195">
         <v>0</v>
@@ -11331,20 +11547,20 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B196">
-        <v>1010</v>
+        <v>403070</v>
       </c>
       <c r="C196" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B196,[1]TextData!A:A))</f>
-        <v>ファイアボール</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D196">
         <v>1</v>
       </c>
       <c r="E196">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F196">
         <v>0</v>
@@ -11355,23 +11571,23 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B197">
-        <v>1050</v>
+        <v>13010</v>
       </c>
       <c r="C197" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B197,[1]TextData!A:A))</f>
-        <v>フレイムレイン</v>
+        <v>ヘビィカバー</v>
       </c>
       <c r="D197">
         <v>1</v>
       </c>
       <c r="E197">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F197">
-        <v>1151</v>
+        <v>0</v>
       </c>
       <c r="G197">
         <v>0</v>
@@ -11379,14 +11595,14 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B198">
-        <v>100910</v>
+        <v>13020</v>
       </c>
       <c r="C198" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B198,[1]TextData!A:A))</f>
-        <v>バーニングカウンター</v>
+        <v>アイシクルエッジ</v>
       </c>
       <c r="D198">
         <v>1</v>
@@ -11403,20 +11619,20 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B199">
-        <v>100920</v>
+        <v>13040</v>
       </c>
       <c r="C199" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B199,[1]TextData!A:A))</f>
-        <v>プロミネンス</v>
+        <v>アーマーコード</v>
       </c>
       <c r="D199">
         <v>1</v>
       </c>
       <c r="E199">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F199">
         <v>0</v>
@@ -11430,17 +11646,17 @@
         <v>1009</v>
       </c>
       <c r="B200">
-        <v>11070</v>
+        <v>1010</v>
       </c>
       <c r="C200" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B200,[1]TextData!A:A))</f>
-        <v>ルージュバック</v>
+        <v>ファイアボール</v>
       </c>
       <c r="D200">
         <v>1</v>
       </c>
       <c r="E200">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F200">
         <v>0</v>
@@ -11454,20 +11670,20 @@
         <v>1009</v>
       </c>
       <c r="B201">
-        <v>401050</v>
+        <v>1050</v>
       </c>
       <c r="C201" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B201,[1]TextData!A:A))</f>
-        <v>フレイムレイン+</v>
+        <v>フレイムレイン</v>
       </c>
       <c r="D201">
         <v>1</v>
       </c>
       <c r="E201">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F201">
-        <v>0</v>
+        <v>1151</v>
       </c>
       <c r="G201">
         <v>0</v>
@@ -11478,11 +11694,11 @@
         <v>1009</v>
       </c>
       <c r="B202">
-        <v>11030</v>
+        <v>100910</v>
       </c>
       <c r="C202" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B202,[1]TextData!A:A))</f>
-        <v>ウォークライ</v>
+        <v>バーニングカウンター</v>
       </c>
       <c r="D202">
         <v>1</v>
@@ -11502,17 +11718,17 @@
         <v>1009</v>
       </c>
       <c r="B203">
-        <v>11020</v>
+        <v>100920</v>
       </c>
       <c r="C203" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B203,[1]TextData!A:A))</f>
-        <v>イーグルアイ</v>
+        <v>プロミネンス</v>
       </c>
       <c r="D203">
         <v>1</v>
       </c>
       <c r="E203">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F203">
         <v>0</v>
@@ -11526,11 +11742,11 @@
         <v>1009</v>
       </c>
       <c r="B204">
-        <v>15040</v>
+        <v>11070</v>
       </c>
       <c r="C204" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B204,[1]TextData!A:A))</f>
-        <v>ネガティブドレイン</v>
+        <v>ルージュバック</v>
       </c>
       <c r="D204">
         <v>1</v>
@@ -11547,20 +11763,20 @@
     </row>
     <row r="205" spans="1:7">
       <c r="A205">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B205">
-        <v>2010</v>
+        <v>401050</v>
       </c>
       <c r="C205" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B205,[1]TextData!A:A))</f>
-        <v>ディスチャージ</v>
+        <v>フレイムレイン+</v>
       </c>
       <c r="D205">
         <v>1</v>
       </c>
       <c r="E205">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F205">
         <v>0</v>
@@ -11571,23 +11787,23 @@
     </row>
     <row r="206" spans="1:7">
       <c r="A206">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B206">
-        <v>2030</v>
+        <v>11030</v>
       </c>
       <c r="C206" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B206,[1]TextData!A:A))</f>
-        <v>ロングスラスト</v>
+        <v>ウォークライ</v>
       </c>
       <c r="D206">
         <v>1</v>
       </c>
       <c r="E206">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F206">
-        <v>14215</v>
+        <v>0</v>
       </c>
       <c r="G206">
         <v>0</v>
@@ -11595,14 +11811,14 @@
     </row>
     <row r="207" spans="1:7">
       <c r="A207">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B207">
-        <v>101010</v>
+        <v>11020</v>
       </c>
       <c r="C207" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B207,[1]TextData!A:A))</f>
-        <v>エウロス</v>
+        <v>イーグルアイ</v>
       </c>
       <c r="D207">
         <v>1</v>
@@ -11619,20 +11835,20 @@
     </row>
     <row r="208" spans="1:7">
       <c r="A208">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B208">
-        <v>101020</v>
+        <v>15040</v>
       </c>
       <c r="C208" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B208,[1]TextData!A:A))</f>
-        <v>ボレアス</v>
+        <v>ネガティブドレイン</v>
       </c>
       <c r="D208">
         <v>1</v>
       </c>
       <c r="E208">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F208">
         <v>0</v>
@@ -11646,17 +11862,17 @@
         <v>1010</v>
       </c>
       <c r="B209">
-        <v>12010</v>
+        <v>2010</v>
       </c>
       <c r="C209" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B209,[1]TextData!A:A))</f>
-        <v>クロースエッジ</v>
+        <v>ディスチャージ</v>
       </c>
       <c r="D209">
         <v>1</v>
       </c>
       <c r="E209">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F209">
         <v>0</v>
@@ -11670,20 +11886,20 @@
         <v>1010</v>
       </c>
       <c r="B210">
-        <v>402030</v>
+        <v>2030</v>
       </c>
       <c r="C210" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B210,[1]TextData!A:A))</f>
-        <v>ショックインパルス+</v>
+        <v>ロングスラスト</v>
       </c>
       <c r="D210">
         <v>1</v>
       </c>
       <c r="E210">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F210">
-        <v>0</v>
+        <v>14215</v>
       </c>
       <c r="G210">
         <v>0</v>
@@ -11694,11 +11910,11 @@
         <v>1010</v>
       </c>
       <c r="B211">
-        <v>12020</v>
+        <v>101010</v>
       </c>
       <c r="C211" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B211,[1]TextData!A:A))</f>
-        <v>ファストファクション</v>
+        <v>エウロス</v>
       </c>
       <c r="D211">
         <v>1</v>
@@ -11718,17 +11934,17 @@
         <v>1010</v>
       </c>
       <c r="B212">
-        <v>12030</v>
+        <v>101020</v>
       </c>
       <c r="C212" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B212,[1]TextData!A:A))</f>
-        <v>クイックムーブ</v>
+        <v>ボレアス</v>
       </c>
       <c r="D212">
         <v>1</v>
       </c>
       <c r="E212">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F212">
         <v>0</v>
@@ -11742,11 +11958,11 @@
         <v>1010</v>
       </c>
       <c r="B213">
-        <v>15070</v>
+        <v>12010</v>
       </c>
       <c r="C213" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B213,[1]TextData!A:A))</f>
-        <v>ジャックポッド</v>
+        <v>クロースエッジ</v>
       </c>
       <c r="D213">
         <v>1</v>
@@ -11763,20 +11979,20 @@
     </row>
     <row r="214" spans="1:7">
       <c r="A214">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B214">
-        <v>3010</v>
+        <v>402030</v>
       </c>
       <c r="C214" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B214,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>ショックインパルス+</v>
       </c>
       <c r="D214">
         <v>1</v>
       </c>
       <c r="E214">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F214">
         <v>0</v>
@@ -11787,20 +12003,20 @@
     </row>
     <row r="215" spans="1:7">
       <c r="A215">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B215">
-        <v>3050</v>
+        <v>12020</v>
       </c>
       <c r="C215" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B215,[1]TextData!A:A))</f>
-        <v>ディープフリーズ</v>
+        <v>ファストファクション</v>
       </c>
       <c r="D215">
         <v>1</v>
       </c>
       <c r="E215">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F215">
         <v>0</v>
@@ -11811,14 +12027,14 @@
     </row>
     <row r="216" spans="1:7">
       <c r="A216">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B216">
-        <v>101110</v>
+        <v>12030</v>
       </c>
       <c r="C216" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B216,[1]TextData!A:A))</f>
-        <v>アバランシュ</v>
+        <v>クイックムーブ</v>
       </c>
       <c r="D216">
         <v>1</v>
@@ -11835,20 +12051,20 @@
     </row>
     <row r="217" spans="1:7">
       <c r="A217">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B217">
-        <v>101120</v>
+        <v>15070</v>
       </c>
       <c r="C217" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B217,[1]TextData!A:A))</f>
-        <v>ブリザードコフィン</v>
+        <v>ジャックポッド</v>
       </c>
       <c r="D217">
         <v>1</v>
       </c>
       <c r="E217">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F217">
         <v>0</v>
@@ -11862,17 +12078,17 @@
         <v>1011</v>
       </c>
       <c r="B218">
-        <v>13090</v>
+        <v>3010</v>
       </c>
       <c r="C218" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B218,[1]TextData!A:A))</f>
-        <v>アイスセイバー</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D218">
         <v>1</v>
       </c>
       <c r="E218">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F218">
         <v>0</v>
@@ -11886,17 +12102,17 @@
         <v>1011</v>
       </c>
       <c r="B219">
-        <v>403050</v>
+        <v>3050</v>
       </c>
       <c r="C219" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B219,[1]TextData!A:A))</f>
-        <v>ディープフリーズ+</v>
+        <v>ディープフリーズ</v>
       </c>
       <c r="D219">
         <v>1</v>
       </c>
       <c r="E219">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F219">
         <v>0</v>
@@ -11910,11 +12126,11 @@
         <v>1011</v>
       </c>
       <c r="B220">
-        <v>13050</v>
+        <v>101110</v>
       </c>
       <c r="C220" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B220,[1]TextData!A:A))</f>
-        <v>キュアフリーズ</v>
+        <v>アバランシュ</v>
       </c>
       <c r="D220">
         <v>1</v>
@@ -11934,17 +12150,17 @@
         <v>1011</v>
       </c>
       <c r="B221">
-        <v>13070</v>
+        <v>101120</v>
       </c>
       <c r="C221" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B221,[1]TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
+        <v>ブリザードコフィン</v>
       </c>
       <c r="D221">
         <v>1</v>
       </c>
       <c r="E221">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F221">
         <v>0</v>
@@ -11958,11 +12174,11 @@
         <v>1011</v>
       </c>
       <c r="B222">
-        <v>14070</v>
+        <v>13090</v>
       </c>
       <c r="C222" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B222,[1]TextData!A:A))</f>
-        <v>ホーミングクルセイド</v>
+        <v>アイスセイバー</v>
       </c>
       <c r="D222">
         <v>1</v>
@@ -11979,20 +12195,20 @@
     </row>
     <row r="223" spans="1:7">
       <c r="A223">
-        <v>1101</v>
+        <v>1011</v>
       </c>
       <c r="B223">
-        <v>3010</v>
+        <v>403050</v>
       </c>
       <c r="C223" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B223,[1]TextData!A:A))</f>
-        <v>アイスブレイド</v>
+        <v>ディープフリーズ+</v>
       </c>
       <c r="D223">
         <v>1</v>
       </c>
       <c r="E223">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F223">
         <v>0</v>
@@ -12003,20 +12219,20 @@
     </row>
     <row r="224" spans="1:7">
       <c r="A224">
-        <v>1101</v>
+        <v>1011</v>
       </c>
       <c r="B224">
-        <v>3070</v>
+        <v>13050</v>
       </c>
       <c r="C224" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B224,[1]TextData!A:A))</f>
-        <v>アクアミラージュ</v>
+        <v>キュアフリーズ</v>
       </c>
       <c r="D224">
         <v>1</v>
       </c>
       <c r="E224">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F224">
         <v>0</v>
@@ -12027,14 +12243,14 @@
     </row>
     <row r="225" spans="1:7">
       <c r="A225">
-        <v>1101</v>
+        <v>1011</v>
       </c>
       <c r="B225">
-        <v>110110</v>
+        <v>13070</v>
       </c>
       <c r="C225" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B225,[1]TextData!A:A))</f>
-        <v>ウィビングヒストリー</v>
+        <v>アシッドラッシュ</v>
       </c>
       <c r="D225">
         <v>1</v>
@@ -12051,20 +12267,20 @@
     </row>
     <row r="226" spans="1:7">
       <c r="A226">
-        <v>1101</v>
+        <v>1011</v>
       </c>
       <c r="B226">
-        <v>110120</v>
+        <v>14070</v>
       </c>
       <c r="C226" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B226,[1]TextData!A:A))</f>
-        <v>アンライバルド</v>
+        <v>ホーミングクルセイド</v>
       </c>
       <c r="D226">
         <v>1</v>
       </c>
       <c r="E226">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F226">
         <v>0</v>
@@ -12078,17 +12294,17 @@
         <v>1101</v>
       </c>
       <c r="B227">
-        <v>13100</v>
+        <v>3010</v>
       </c>
       <c r="C227" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B227,[1]TextData!A:A))</f>
-        <v>アイスセイバー</v>
+        <v>アイスブレイド</v>
       </c>
       <c r="D227">
         <v>1</v>
       </c>
       <c r="E227">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F227">
         <v>0</v>
@@ -12102,17 +12318,17 @@
         <v>1101</v>
       </c>
       <c r="B228">
-        <v>403050</v>
+        <v>3070</v>
       </c>
       <c r="C228" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B228,[1]TextData!A:A))</f>
-        <v>ディープフリーズ+</v>
+        <v>アクアミラージュ</v>
       </c>
       <c r="D228">
         <v>1</v>
       </c>
       <c r="E228">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F228">
         <v>0</v>
@@ -12126,11 +12342,11 @@
         <v>1101</v>
       </c>
       <c r="B229">
-        <v>13050</v>
+        <v>110110</v>
       </c>
       <c r="C229" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B229,[1]TextData!A:A))</f>
-        <v>キュアフリーズ</v>
+        <v>ウィビングヒストリー</v>
       </c>
       <c r="D229">
         <v>1</v>
@@ -12150,17 +12366,17 @@
         <v>1101</v>
       </c>
       <c r="B230">
-        <v>13070</v>
+        <v>110120</v>
       </c>
       <c r="C230" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B230,[1]TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
+        <v>アンライバルド</v>
       </c>
       <c r="D230">
         <v>1</v>
       </c>
       <c r="E230">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F230">
         <v>0</v>
@@ -12174,22 +12390,118 @@
         <v>1101</v>
       </c>
       <c r="B231">
-        <v>14070</v>
+        <v>13100</v>
       </c>
       <c r="C231" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B231,[1]TextData!A:A))</f>
+        <v>アイスセイバー</v>
+      </c>
+      <c r="D231">
+        <v>1</v>
+      </c>
+      <c r="E231">
+        <v>0</v>
+      </c>
+      <c r="F231">
+        <v>0</v>
+      </c>
+      <c r="G231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7">
+      <c r="A232">
+        <v>1101</v>
+      </c>
+      <c r="B232">
+        <v>403050</v>
+      </c>
+      <c r="C232" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B232,[1]TextData!A:A))</f>
+        <v>ディープフリーズ+</v>
+      </c>
+      <c r="D232">
+        <v>1</v>
+      </c>
+      <c r="E232">
+        <v>0</v>
+      </c>
+      <c r="F232">
+        <v>0</v>
+      </c>
+      <c r="G232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7">
+      <c r="A233">
+        <v>1101</v>
+      </c>
+      <c r="B233">
+        <v>13050</v>
+      </c>
+      <c r="C233" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B233,[1]TextData!A:A))</f>
+        <v>キュアフリーズ</v>
+      </c>
+      <c r="D233">
+        <v>1</v>
+      </c>
+      <c r="E233">
+        <v>0</v>
+      </c>
+      <c r="F233">
+        <v>0</v>
+      </c>
+      <c r="G233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7">
+      <c r="A234">
+        <v>1101</v>
+      </c>
+      <c r="B234">
+        <v>13070</v>
+      </c>
+      <c r="C234" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B234,[1]TextData!A:A))</f>
+        <v>アシッドラッシュ</v>
+      </c>
+      <c r="D234">
+        <v>1</v>
+      </c>
+      <c r="E234">
+        <v>0</v>
+      </c>
+      <c r="F234">
+        <v>0</v>
+      </c>
+      <c r="G234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235">
+        <v>1101</v>
+      </c>
+      <c r="B235">
+        <v>14070</v>
+      </c>
+      <c r="C235" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B235,[1]TextData!A:A))</f>
         <v>ホーミングクルセイド</v>
       </c>
-      <c r="D231">
-        <v>1</v>
-      </c>
-      <c r="E231">
-        <v>0</v>
-      </c>
-      <c r="F231">
-        <v>0</v>
-      </c>
-      <c r="G231">
+      <c r="D235">
+        <v>1</v>
+      </c>
+      <c r="E235">
+        <v>0</v>
+      </c>
+      <c r="F235">
+        <v>0</v>
+      </c>
+      <c r="G235">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Enemies" sheetId="1" r:id="rId1"/>
@@ -197,7 +197,7 @@
     <t>guardian dragon_4</t>
   </si>
   <si>
-    <t>Bifrons</t>
+    <t>machine enemy_003</t>
   </si>
   <si>
     <t>Dragon_Saint1</t>
@@ -461,8 +461,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -481,24 +481,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -511,15 +495,56 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -533,23 +558,37 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -563,11 +602,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -580,48 +618,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -634,25 +634,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -664,7 +688,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -682,7 +724,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -694,19 +790,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -718,85 +802,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -808,13 +814,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -825,6 +825,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -843,41 +858,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -909,8 +894,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -925,6 +910,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -933,145 +933,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1696,7 +1696,7 @@
             <v>6010</v>
           </cell>
           <cell r="B67" t="str">
-            <v>何もしない</v>
+            <v>待機</v>
           </cell>
         </row>
         <row r="68">
@@ -3157,919 +3157,919 @@
         </row>
         <row r="250">
           <cell r="A250">
-            <v>310130</v>
+            <v>310120</v>
           </cell>
           <cell r="B250" t="str">
-            <v>ヒールユニット</v>
+            <v>リカバリーエンハンス</v>
           </cell>
         </row>
         <row r="251">
           <cell r="A251">
-            <v>320010</v>
+            <v>310130</v>
           </cell>
           <cell r="B251" t="str">
-            <v>訓練所Lv1</v>
+            <v>ヒールユニット</v>
           </cell>
         </row>
         <row r="252">
           <cell r="A252">
-            <v>320011</v>
+            <v>320010</v>
           </cell>
           <cell r="B252" t="str">
-            <v>訓練所Lv2</v>
+            <v>訓練所Lv1</v>
           </cell>
         </row>
         <row r="253">
           <cell r="A253">
-            <v>320012</v>
+            <v>320011</v>
           </cell>
           <cell r="B253" t="str">
-            <v>訓練所Lv3</v>
+            <v>訓練所Lv2</v>
           </cell>
         </row>
         <row r="254">
           <cell r="A254">
-            <v>320020</v>
+            <v>320012</v>
           </cell>
           <cell r="B254" t="str">
-            <v>研究施設Lv1</v>
+            <v>訓練所Lv3</v>
           </cell>
         </row>
         <row r="255">
           <cell r="A255">
-            <v>320021</v>
+            <v>320020</v>
           </cell>
           <cell r="B255" t="str">
-            <v>研究施設Lv2</v>
+            <v>研究施設Lv1</v>
           </cell>
         </row>
         <row r="256">
           <cell r="A256">
-            <v>320022</v>
+            <v>320021</v>
           </cell>
           <cell r="B256" t="str">
-            <v>研究施設Lv3</v>
+            <v>研究施設Lv2</v>
           </cell>
         </row>
         <row r="257">
           <cell r="A257">
-            <v>320030</v>
+            <v>320022</v>
           </cell>
           <cell r="B257" t="str">
-            <v>資料館Lv1</v>
+            <v>研究施設Lv3</v>
           </cell>
         </row>
         <row r="258">
           <cell r="A258">
-            <v>320031</v>
+            <v>320030</v>
           </cell>
           <cell r="B258" t="str">
-            <v>資料館Lv2</v>
+            <v>資料館Lv1</v>
           </cell>
         </row>
         <row r="259">
           <cell r="A259">
-            <v>320032</v>
+            <v>320031</v>
           </cell>
           <cell r="B259" t="str">
-            <v>資料館Lv3</v>
+            <v>資料館Lv2</v>
           </cell>
         </row>
         <row r="260">
           <cell r="A260">
-            <v>320040</v>
+            <v>320032</v>
           </cell>
           <cell r="B260" t="str">
-            <v>潜伏技術Lv1</v>
+            <v>資料館Lv3</v>
           </cell>
         </row>
         <row r="261">
           <cell r="A261">
-            <v>321010</v>
+            <v>320040</v>
           </cell>
           <cell r="B261" t="str">
-            <v>炎の祭壇</v>
+            <v>潜伏技術Lv1</v>
           </cell>
         </row>
         <row r="262">
           <cell r="A262">
-            <v>321020</v>
+            <v>321010</v>
           </cell>
           <cell r="B262" t="str">
-            <v>稲妻の祭壇</v>
+            <v>炎の祭壇</v>
           </cell>
         </row>
         <row r="263">
           <cell r="A263">
-            <v>321030</v>
+            <v>321020</v>
           </cell>
           <cell r="B263" t="str">
-            <v>蒼の祭壇</v>
+            <v>稲妻の祭壇</v>
           </cell>
         </row>
         <row r="264">
           <cell r="A264">
-            <v>321040</v>
+            <v>321030</v>
           </cell>
           <cell r="B264" t="str">
-            <v>光の祭壇</v>
+            <v>蒼の祭壇</v>
           </cell>
         </row>
         <row r="265">
           <cell r="A265">
-            <v>321050</v>
+            <v>321040</v>
           </cell>
           <cell r="B265" t="str">
-            <v>月の祭壇</v>
+            <v>光の祭壇</v>
           </cell>
         </row>
         <row r="266">
           <cell r="A266">
-            <v>322010</v>
+            <v>321050</v>
           </cell>
           <cell r="B266" t="str">
-            <v>食糧庫Lv1</v>
+            <v>月の祭壇</v>
           </cell>
         </row>
         <row r="267">
           <cell r="A267">
-            <v>322020</v>
+            <v>322010</v>
           </cell>
           <cell r="B267" t="str">
-            <v>攻撃技術Lv1</v>
+            <v>食糧庫Lv1</v>
           </cell>
         </row>
         <row r="268">
           <cell r="A268">
-            <v>322030</v>
+            <v>322020</v>
           </cell>
           <cell r="B268" t="str">
-            <v>防御技術Lv1</v>
+            <v>攻撃技術Lv1</v>
           </cell>
         </row>
         <row r="269">
           <cell r="A269">
-            <v>322040</v>
+            <v>322030</v>
           </cell>
           <cell r="B269" t="str">
-            <v>詠唱技術Lv1</v>
+            <v>防御技術Lv1</v>
           </cell>
         </row>
         <row r="270">
           <cell r="A270">
-            <v>401010</v>
+            <v>322040</v>
           </cell>
           <cell r="B270" t="str">
-            <v>ファイアボール+</v>
+            <v>詠唱技術Lv1</v>
           </cell>
         </row>
         <row r="271">
           <cell r="A271">
-            <v>401020</v>
+            <v>401010</v>
           </cell>
           <cell r="B271" t="str">
-            <v>バーンストーム+</v>
+            <v>ファイアボール+</v>
           </cell>
         </row>
         <row r="272">
           <cell r="A272">
-            <v>401030</v>
+            <v>401020</v>
           </cell>
           <cell r="B272" t="str">
-            <v>ヒートスタンプ+</v>
+            <v>バーンストーム+</v>
           </cell>
         </row>
         <row r="273">
           <cell r="A273">
-            <v>401040</v>
+            <v>401030</v>
           </cell>
           <cell r="B273" t="str">
-            <v>ソードアダプト+</v>
+            <v>ヒートスタンプ+</v>
           </cell>
         </row>
         <row r="274">
           <cell r="A274">
-            <v>401050</v>
+            <v>401040</v>
           </cell>
           <cell r="B274" t="str">
-            <v>フレイムレイン+</v>
+            <v>ソードアダプト+</v>
           </cell>
         </row>
         <row r="275">
           <cell r="A275">
-            <v>401060</v>
+            <v>401050</v>
           </cell>
           <cell r="B275" t="str">
-            <v>イクスティンクション+</v>
+            <v>フレイムレイン+</v>
           </cell>
         </row>
         <row r="276">
           <cell r="A276">
-            <v>401070</v>
+            <v>401060</v>
           </cell>
           <cell r="B276" t="str">
-            <v>バーニングソウル+</v>
+            <v>イクスティンクション+</v>
           </cell>
         </row>
         <row r="277">
           <cell r="A277">
-            <v>401080</v>
+            <v>401070</v>
           </cell>
           <cell r="B277" t="str">
-            <v>レイジングバウンサー+</v>
+            <v>バーニングソウル+</v>
           </cell>
         </row>
         <row r="278">
           <cell r="A278">
-            <v>402010</v>
+            <v>401080</v>
           </cell>
           <cell r="B278" t="str">
-            <v>ディスチャージ+</v>
+            <v>レイジングバウンサー+</v>
           </cell>
         </row>
         <row r="279">
           <cell r="A279">
-            <v>402020</v>
+            <v>402010</v>
           </cell>
           <cell r="B279" t="str">
-            <v>イベイドコード+</v>
+            <v>ディスチャージ+</v>
           </cell>
         </row>
         <row r="280">
           <cell r="A280">
-            <v>402030</v>
+            <v>402020</v>
           </cell>
           <cell r="B280" t="str">
-            <v>ショックインパルス+</v>
+            <v>イベイドコード+</v>
           </cell>
         </row>
         <row r="281">
           <cell r="A281">
-            <v>402040</v>
+            <v>402030</v>
           </cell>
           <cell r="B281" t="str">
-            <v>トラストチェイン+</v>
+            <v>ショックインパルス+</v>
           </cell>
         </row>
         <row r="282">
           <cell r="A282">
-            <v>402050</v>
+            <v>402040</v>
           </cell>
           <cell r="B282" t="str">
-            <v>スペルバニシング+</v>
+            <v>トラストチェイン+</v>
           </cell>
         </row>
         <row r="283">
           <cell r="A283">
-            <v>402060</v>
+            <v>402050</v>
           </cell>
           <cell r="B283" t="str">
-            <v>アーテニーストライク+</v>
+            <v>スペルバニシング+</v>
           </cell>
         </row>
         <row r="284">
           <cell r="A284">
-            <v>402070</v>
+            <v>402060</v>
           </cell>
           <cell r="B284" t="str">
-            <v>コンセントレイト+</v>
+            <v>アーテニーストライク+</v>
           </cell>
         </row>
         <row r="285">
           <cell r="A285">
-            <v>402080</v>
+            <v>402070</v>
           </cell>
           <cell r="B285" t="str">
-            <v>ディレイマジック+</v>
+            <v>コンセントレイト+</v>
           </cell>
         </row>
         <row r="286">
           <cell r="A286">
-            <v>403010</v>
+            <v>402080</v>
           </cell>
           <cell r="B286" t="str">
-            <v>アイスブレイド+</v>
+            <v>ディレイマジック+</v>
           </cell>
         </row>
         <row r="287">
           <cell r="A287">
-            <v>403020</v>
+            <v>403010</v>
           </cell>
           <cell r="B287" t="str">
-            <v>カウンターオーラ+</v>
+            <v>アイスブレイド+</v>
           </cell>
         </row>
         <row r="288">
           <cell r="A288">
-            <v>403030</v>
+            <v>403020</v>
           </cell>
           <cell r="B288" t="str">
-            <v>ラインプロテクト+</v>
+            <v>カウンターオーラ+</v>
           </cell>
         </row>
         <row r="289">
           <cell r="A289">
-            <v>403040</v>
+            <v>403030</v>
           </cell>
           <cell r="B289" t="str">
-            <v>エスコートソール+</v>
+            <v>ラインプロテクト+</v>
           </cell>
         </row>
         <row r="290">
           <cell r="A290">
-            <v>403050</v>
+            <v>403040</v>
           </cell>
           <cell r="B290" t="str">
-            <v>ディープフリーズ+</v>
+            <v>エスコートソール+</v>
           </cell>
         </row>
         <row r="291">
           <cell r="A291">
-            <v>403060</v>
+            <v>403050</v>
           </cell>
           <cell r="B291" t="str">
-            <v>バブルブロウ+</v>
+            <v>ディープフリーズ+</v>
           </cell>
         </row>
         <row r="292">
           <cell r="A292">
-            <v>403070</v>
+            <v>403060</v>
           </cell>
           <cell r="B292" t="str">
-            <v>アクアミラージュ+</v>
+            <v>バブルブロウ+</v>
           </cell>
         </row>
         <row r="293">
           <cell r="A293">
-            <v>403080</v>
+            <v>403070</v>
           </cell>
           <cell r="B293" t="str">
-            <v>フロストシールド+</v>
+            <v>アクアミラージュ+</v>
           </cell>
         </row>
         <row r="294">
           <cell r="A294">
-            <v>404010</v>
+            <v>403080</v>
           </cell>
           <cell r="B294" t="str">
-            <v>セイントレーザー+</v>
+            <v>フロストシールド+</v>
           </cell>
         </row>
         <row r="295">
           <cell r="A295">
-            <v>404020</v>
+            <v>404010</v>
           </cell>
           <cell r="B295" t="str">
-            <v>ペネトレイト+</v>
+            <v>セイントレーザー+</v>
           </cell>
         </row>
         <row r="296">
           <cell r="A296">
-            <v>404030</v>
+            <v>404020</v>
           </cell>
           <cell r="B296" t="str">
-            <v>ヒーリング+</v>
+            <v>ペネトレイト+</v>
           </cell>
         </row>
         <row r="297">
           <cell r="A297">
-            <v>404040</v>
+            <v>404030</v>
           </cell>
           <cell r="B297" t="str">
-            <v>リザイアフォトン+</v>
+            <v>ヒーリング+</v>
           </cell>
         </row>
         <row r="298">
           <cell r="A298">
-            <v>404050</v>
+            <v>404040</v>
           </cell>
           <cell r="B298" t="str">
-            <v>べネディクション+</v>
+            <v>リザイアフォトン+</v>
           </cell>
         </row>
         <row r="299">
           <cell r="A299">
-            <v>404060</v>
+            <v>404050</v>
           </cell>
           <cell r="B299" t="str">
-            <v>ホーリーグレイス+</v>
+            <v>べネディクション+</v>
           </cell>
         </row>
         <row r="300">
           <cell r="A300">
-            <v>404070</v>
+            <v>404060</v>
           </cell>
           <cell r="B300" t="str">
-            <v>キュアエール+</v>
+            <v>ホーリーグレイス+</v>
           </cell>
         </row>
         <row r="301">
           <cell r="A301">
-            <v>404080</v>
+            <v>404070</v>
           </cell>
           <cell r="B301" t="str">
-            <v>ラインバリア+</v>
+            <v>キュアエール+</v>
           </cell>
         </row>
         <row r="302">
           <cell r="A302">
-            <v>405010</v>
+            <v>404080</v>
           </cell>
           <cell r="B302" t="str">
-            <v>ダークプリズン+</v>
+            <v>ラインバリア+</v>
           </cell>
         </row>
         <row r="303">
           <cell r="A303">
-            <v>405020</v>
+            <v>405010</v>
           </cell>
           <cell r="B303" t="str">
-            <v>ユーサネイジア+</v>
+            <v>ダークプリズン+</v>
           </cell>
         </row>
         <row r="304">
           <cell r="A304">
-            <v>405030</v>
+            <v>405020</v>
           </cell>
           <cell r="B304" t="str">
-            <v>ドレインヒール+</v>
+            <v>ユーサネイジア+</v>
           </cell>
         </row>
         <row r="305">
           <cell r="A305">
-            <v>405040</v>
+            <v>405030</v>
           </cell>
           <cell r="B305" t="str">
-            <v>アビサルデスペア+</v>
+            <v>ドレインヒール+</v>
           </cell>
         </row>
         <row r="306">
           <cell r="A306">
-            <v>405050</v>
+            <v>405040</v>
           </cell>
           <cell r="B306" t="str">
-            <v>ディプラヴィティ+</v>
+            <v>アビサルデスペア+</v>
           </cell>
         </row>
         <row r="307">
           <cell r="A307">
-            <v>405060</v>
+            <v>405050</v>
           </cell>
           <cell r="B307" t="str">
-            <v>ダークネス+</v>
+            <v>ディプラヴィティ+</v>
           </cell>
         </row>
         <row r="308">
           <cell r="A308">
-            <v>405070</v>
+            <v>405060</v>
           </cell>
           <cell r="B308" t="str">
-            <v>シェイディークラウド+</v>
+            <v>ダークネス+</v>
           </cell>
         </row>
         <row r="309">
           <cell r="A309">
-            <v>405080</v>
+            <v>405070</v>
           </cell>
           <cell r="B309" t="str">
-            <v>ポイズンブロウ+</v>
+            <v>シェイディークラウド+</v>
           </cell>
         </row>
         <row r="310">
           <cell r="A310">
-            <v>411010</v>
+            <v>405080</v>
           </cell>
           <cell r="B310" t="str">
-            <v>ウルフソウル+</v>
+            <v>ポイズンブロウ+</v>
           </cell>
         </row>
         <row r="311">
           <cell r="A311">
-            <v>411020</v>
+            <v>411010</v>
           </cell>
           <cell r="B311" t="str">
-            <v>プリディカメント+</v>
+            <v>ウルフソウル+</v>
           </cell>
         </row>
         <row r="312">
           <cell r="A312">
-            <v>411030</v>
+            <v>411020</v>
           </cell>
           <cell r="B312" t="str">
-            <v>アサルトシフト+</v>
+            <v>プリディカメント+</v>
           </cell>
         </row>
         <row r="313">
           <cell r="A313">
-            <v>411040</v>
+            <v>411030</v>
           </cell>
           <cell r="B313" t="str">
-            <v>アクティブギフト+</v>
+            <v>アサルトシフト+</v>
           </cell>
         </row>
         <row r="314">
           <cell r="A314">
-            <v>411050</v>
+            <v>411040</v>
           </cell>
           <cell r="B314" t="str">
-            <v>イグナイテッド+</v>
+            <v>アクティブギフト+</v>
           </cell>
         </row>
         <row r="315">
           <cell r="A315">
-            <v>411060</v>
+            <v>411050</v>
           </cell>
           <cell r="B315" t="str">
-            <v>ライジングファイア+</v>
+            <v>イグナイテッド+</v>
           </cell>
         </row>
         <row r="316">
           <cell r="A316">
-            <v>411070</v>
+            <v>411060</v>
           </cell>
           <cell r="B316" t="str">
-            <v>ルージュバック+</v>
+            <v>ライジングファイア+</v>
           </cell>
         </row>
         <row r="317">
           <cell r="A317">
-            <v>411080</v>
+            <v>411070</v>
           </cell>
           <cell r="B317" t="str">
-            <v>パワーエール+</v>
+            <v>ルージュバック+</v>
           </cell>
         </row>
         <row r="318">
           <cell r="A318">
-            <v>411090</v>
+            <v>411080</v>
           </cell>
           <cell r="B318" t="str">
-            <v>スレイプニル+</v>
+            <v>パワーエール+</v>
           </cell>
         </row>
         <row r="319">
           <cell r="A319">
-            <v>412010</v>
+            <v>411090</v>
           </cell>
           <cell r="B319" t="str">
-            <v>エクステンション+</v>
+            <v>スレイプニル+</v>
           </cell>
         </row>
         <row r="320">
           <cell r="A320">
-            <v>412020</v>
+            <v>412010</v>
           </cell>
           <cell r="B320" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>エクステンション+</v>
           </cell>
         </row>
         <row r="321">
           <cell r="A321">
-            <v>412030</v>
+            <v>412020</v>
           </cell>
           <cell r="B321" t="str">
-            <v>スウィフトカレント+</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="322">
           <cell r="A322">
-            <v>412040</v>
+            <v>412030</v>
           </cell>
           <cell r="B322" t="str">
-            <v>イヴェイドオール+</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="323">
           <cell r="A323">
-            <v>412050</v>
+            <v>412040</v>
           </cell>
           <cell r="B323" t="str">
-            <v>クイックムーブ+</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="324">
           <cell r="A324">
-            <v>412060</v>
+            <v>412050</v>
           </cell>
           <cell r="B324" t="str">
-            <v>チェイスマジック+</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="325">
           <cell r="A325">
-            <v>412070</v>
+            <v>412060</v>
           </cell>
           <cell r="B325" t="str">
-            <v>ソーサリーコネクト+</v>
+            <v>チェイスマジック+</v>
           </cell>
         </row>
         <row r="326">
           <cell r="A326">
-            <v>412080</v>
+            <v>412070</v>
           </cell>
           <cell r="B326" t="str">
-            <v>ウィンドライズ+</v>
+            <v>ソーサリーコネクト+</v>
           </cell>
         </row>
         <row r="327">
           <cell r="A327">
-            <v>412090</v>
+            <v>412080</v>
           </cell>
           <cell r="B327" t="str">
-            <v>アウトオブオーダー+</v>
+            <v>ウィンドライズ+</v>
           </cell>
         </row>
         <row r="328">
           <cell r="A328">
-            <v>413010</v>
+            <v>412090</v>
           </cell>
           <cell r="B328" t="str">
-            <v>アーマーコード+</v>
+            <v>アウトオブオーダー+</v>
           </cell>
         </row>
         <row r="329">
           <cell r="A329">
-            <v>413020</v>
+            <v>413010</v>
           </cell>
           <cell r="B329" t="str">
-            <v>クイックバリア+</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="330">
           <cell r="A330">
-            <v>413030</v>
+            <v>413020</v>
           </cell>
           <cell r="B330" t="str">
-            <v>クイックキュア+</v>
+            <v>クイックバリア+</v>
           </cell>
         </row>
         <row r="331">
           <cell r="A331">
-            <v>413040</v>
+            <v>413030</v>
           </cell>
           <cell r="B331" t="str">
-            <v>セルフシールド+</v>
+            <v>クイックキュア+</v>
           </cell>
         </row>
         <row r="332">
           <cell r="A332">
-            <v>413050</v>
+            <v>413040</v>
           </cell>
           <cell r="B332" t="str">
-            <v>パッシブジャミング+</v>
+            <v>セルフシールド+</v>
           </cell>
         </row>
         <row r="333">
           <cell r="A333">
-            <v>413060</v>
+            <v>413050</v>
           </cell>
           <cell r="B333" t="str">
-            <v>サプライカバー+</v>
+            <v>パッシブジャミング+</v>
           </cell>
         </row>
         <row r="334">
           <cell r="A334">
-            <v>413070</v>
+            <v>413060</v>
           </cell>
           <cell r="B334" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>サプライカバー+</v>
           </cell>
         </row>
         <row r="335">
           <cell r="A335">
-            <v>413080</v>
+            <v>413070</v>
           </cell>
           <cell r="B335" t="str">
-            <v>ライフスティール+</v>
+            <v>アシッドラッシュ+</v>
           </cell>
         </row>
         <row r="336">
           <cell r="A336">
-            <v>413090</v>
+            <v>413080</v>
           </cell>
           <cell r="B336" t="str">
-            <v>アイスセイバー+</v>
+            <v>ライフスティール+</v>
           </cell>
         </row>
         <row r="337">
           <cell r="A337">
-            <v>414010</v>
+            <v>413090</v>
           </cell>
           <cell r="B337" t="str">
-            <v>ディバインシールド+</v>
+            <v>アイスセイバー+</v>
           </cell>
         </row>
         <row r="338">
           <cell r="A338">
-            <v>414020</v>
+            <v>414010</v>
           </cell>
           <cell r="B338" t="str">
-            <v>ライフディバイド+</v>
+            <v>ディバインシールド+</v>
           </cell>
         </row>
         <row r="339">
           <cell r="A339">
-            <v>414030</v>
+            <v>414020</v>
           </cell>
           <cell r="B339" t="str">
-            <v>エイミングスコープ+</v>
+            <v>ライフディバイド+</v>
           </cell>
         </row>
         <row r="340">
           <cell r="A340">
-            <v>414040</v>
+            <v>414030</v>
           </cell>
           <cell r="B340" t="str">
-            <v>リジェネレーション+</v>
+            <v>エイミングスコープ+</v>
           </cell>
         </row>
         <row r="341">
           <cell r="A341">
-            <v>414050</v>
+            <v>414040</v>
           </cell>
           <cell r="B341" t="str">
-            <v>ホープフルアイリス+</v>
+            <v>リジェネレーション+</v>
           </cell>
         </row>
         <row r="342">
           <cell r="A342">
-            <v>414060</v>
+            <v>414050</v>
           </cell>
           <cell r="B342" t="str">
-            <v>パッシブサプライ+</v>
+            <v>ホープフルアイリス+</v>
           </cell>
         </row>
         <row r="343">
           <cell r="A343">
-            <v>414070</v>
+            <v>414060</v>
           </cell>
           <cell r="B343" t="str">
-            <v>ホーミングクルセイド+</v>
+            <v>パッシブサプライ+</v>
           </cell>
         </row>
         <row r="344">
           <cell r="A344">
-            <v>414080</v>
+            <v>414070</v>
           </cell>
           <cell r="B344" t="str">
-            <v>クイックヒール+</v>
+            <v>ホーミングクルセイド+</v>
           </cell>
         </row>
         <row r="345">
           <cell r="A345">
-            <v>414090</v>
+            <v>414080</v>
           </cell>
           <cell r="B345" t="str">
-            <v>リレイズ+</v>
+            <v>クイックヒール+</v>
           </cell>
         </row>
         <row r="346">
           <cell r="A346">
-            <v>415010</v>
+            <v>414090</v>
           </cell>
           <cell r="B346" t="str">
-            <v>イーグルアイ+</v>
+            <v>リレイズ+</v>
           </cell>
         </row>
         <row r="347">
           <cell r="A347">
-            <v>415020</v>
+            <v>415010</v>
           </cell>
           <cell r="B347" t="str">
-            <v>ネヴァーエンド+</v>
+            <v>イーグルアイ+</v>
           </cell>
         </row>
         <row r="348">
           <cell r="A348">
-            <v>415030</v>
+            <v>415020</v>
           </cell>
           <cell r="B348" t="str">
-            <v>グレイブアクト+</v>
+            <v>ネヴァーエンド+</v>
           </cell>
         </row>
         <row r="349">
           <cell r="A349">
-            <v>415040</v>
+            <v>415030</v>
           </cell>
           <cell r="B349" t="str">
-            <v>スカルグラッジ+</v>
+            <v>グレイブアクト+</v>
           </cell>
         </row>
         <row r="350">
           <cell r="A350">
-            <v>415050</v>
+            <v>415040</v>
           </cell>
           <cell r="B350" t="str">
-            <v>ネガティブドレイン+</v>
+            <v>スカルグラッジ+</v>
           </cell>
         </row>
         <row r="351">
           <cell r="A351">
-            <v>415060</v>
+            <v>415050</v>
           </cell>
           <cell r="B351" t="str">
-            <v>アンデッドペイン+</v>
+            <v>ネガティブドレイン+</v>
           </cell>
         </row>
         <row r="352">
           <cell r="A352">
-            <v>415070</v>
+            <v>415060</v>
           </cell>
           <cell r="B352" t="str">
-            <v>ジャックポッド+</v>
+            <v>アンデッドペイン+</v>
           </cell>
         </row>
         <row r="353">
           <cell r="A353">
-            <v>415080</v>
+            <v>415070</v>
           </cell>
           <cell r="B353" t="str">
-            <v>ヒールハント+</v>
+            <v>ジャックポッド+</v>
           </cell>
         </row>
         <row r="354">
           <cell r="A354">
-            <v>415090</v>
+            <v>415080</v>
           </cell>
           <cell r="B354" t="str">
-            <v>クイックカース+</v>
+            <v>ヒールハント+</v>
           </cell>
         </row>
         <row r="355">
           <cell r="A355">
-            <v>501010</v>
+            <v>415090</v>
           </cell>
           <cell r="B355" t="str">
-            <v>火傷耐性+20%</v>
+            <v>クイックカース+</v>
           </cell>
         </row>
         <row r="356">
           <cell r="A356">
-            <v>501020</v>
+            <v>501010</v>
           </cell>
           <cell r="B356" t="str">
-            <v>命中率+5%</v>
+            <v>火傷耐性+20%</v>
           </cell>
         </row>
         <row r="357">
           <cell r="A357">
-            <v>501030</v>
+            <v>501020</v>
           </cell>
           <cell r="B357" t="str">
-            <v>最大HP+2</v>
+            <v>命中率+5%</v>
           </cell>
         </row>
         <row r="358">
           <cell r="A358">
-            <v>501040</v>
+            <v>501030</v>
           </cell>
           <cell r="B358" t="str">
-            <v>ATK+2</v>
+            <v>最大HP+2</v>
           </cell>
         </row>
         <row r="359">
           <cell r="A359">
-            <v>501110</v>
+            <v>501040</v>
           </cell>
           <cell r="B359" t="str">
-            <v>DEF+2</v>
+            <v>ATK+2</v>
           </cell>
         </row>
         <row r="360">
           <cell r="A360">
-            <v>501120</v>
+            <v>501110</v>
           </cell>
           <cell r="B360" t="str">
-            <v>命中率+10%</v>
+            <v>DEF+2</v>
           </cell>
         </row>
         <row r="361">
           <cell r="A361">
-            <v>501130</v>
+            <v>501120</v>
           </cell>
           <cell r="B361" t="str">
-            <v>SPD+2</v>
+            <v>命中率+10%</v>
           </cell>
         </row>
         <row r="362">
           <cell r="A362">
-            <v>502010</v>
+            <v>501130</v>
           </cell>
           <cell r="B362" t="str">
-            <v>DEF+1</v>
+            <v>SPD+2</v>
           </cell>
         </row>
         <row r="363">
           <cell r="A363">
-            <v>502020</v>
+            <v>502010</v>
           </cell>
           <cell r="B363" t="str">
-            <v>SPD+1</v>
+            <v>DEF+1</v>
           </cell>
         </row>
         <row r="364">
           <cell r="A364">
-            <v>502030</v>
+            <v>502020</v>
           </cell>
           <cell r="B364" t="str">
             <v>SPD+1</v>
@@ -4077,79 +4077,79 @@
         </row>
         <row r="365">
           <cell r="A365">
-            <v>502040</v>
+            <v>502030</v>
           </cell>
           <cell r="B365" t="str">
-            <v>回避率+5%</v>
+            <v>SPD+1</v>
           </cell>
         </row>
         <row r="366">
           <cell r="A366">
-            <v>502110</v>
+            <v>502040</v>
           </cell>
           <cell r="B366" t="str">
-            <v>会心ダメージ率+25%</v>
+            <v>回避率+5%</v>
           </cell>
         </row>
         <row r="367">
           <cell r="A367">
-            <v>502120</v>
+            <v>502110</v>
           </cell>
           <cell r="B367" t="str">
-            <v>命中率+5%</v>
+            <v>会心ダメージ率+25%</v>
           </cell>
         </row>
         <row r="368">
           <cell r="A368">
-            <v>502121</v>
+            <v>502120</v>
           </cell>
           <cell r="B368" t="str">
-            <v>回避率+5%</v>
+            <v>命中率+5%</v>
           </cell>
         </row>
         <row r="369">
           <cell r="A369">
-            <v>502130</v>
+            <v>502121</v>
           </cell>
           <cell r="B369" t="str">
-            <v>SPD+2</v>
+            <v>回避率+5%</v>
           </cell>
         </row>
         <row r="370">
           <cell r="A370">
-            <v>503010</v>
+            <v>502130</v>
           </cell>
           <cell r="B370" t="str">
-            <v>DEF+1</v>
+            <v>SPD+2</v>
           </cell>
         </row>
         <row r="371">
           <cell r="A371">
-            <v>503020</v>
+            <v>503010</v>
           </cell>
           <cell r="B371" t="str">
-            <v>凍結耐性+20%</v>
+            <v>DEF+1</v>
           </cell>
         </row>
         <row r="372">
           <cell r="A372">
-            <v>503030</v>
+            <v>503020</v>
           </cell>
           <cell r="B372" t="str">
-            <v>最大HP+2</v>
+            <v>凍結耐性+20%</v>
           </cell>
         </row>
         <row r="373">
           <cell r="A373">
-            <v>503040</v>
+            <v>503030</v>
           </cell>
           <cell r="B373" t="str">
-            <v>DEF+2</v>
+            <v>最大HP+2</v>
           </cell>
         </row>
         <row r="374">
           <cell r="A374">
-            <v>503110</v>
+            <v>503040</v>
           </cell>
           <cell r="B374" t="str">
             <v>DEF+2</v>
@@ -4157,233 +4157,241 @@
         </row>
         <row r="375">
           <cell r="A375">
-            <v>503120</v>
+            <v>503110</v>
           </cell>
           <cell r="B375" t="str">
-            <v>ATK+2</v>
+            <v>DEF+2</v>
           </cell>
         </row>
         <row r="376">
           <cell r="A376">
-            <v>503130</v>
+            <v>503120</v>
           </cell>
           <cell r="B376" t="str">
-            <v>ダメージ軽減効果無視+10%</v>
+            <v>ATK+2</v>
           </cell>
         </row>
         <row r="377">
           <cell r="A377">
-            <v>504010</v>
+            <v>503130</v>
           </cell>
           <cell r="B377" t="str">
-            <v>Hp回復効果+2</v>
+            <v>ダメージ軽減効果無視+10%</v>
           </cell>
         </row>
         <row r="378">
           <cell r="A378">
-            <v>504020</v>
+            <v>504010</v>
           </cell>
           <cell r="B378" t="str">
-            <v>SPD+1</v>
+            <v>Hp回復効果+2</v>
           </cell>
         </row>
         <row r="379">
           <cell r="A379">
-            <v>504030</v>
+            <v>504020</v>
           </cell>
           <cell r="B379" t="str">
-            <v>命中率+5%</v>
+            <v>SPD+1</v>
           </cell>
         </row>
         <row r="380">
           <cell r="A380">
-            <v>504040</v>
+            <v>504030</v>
           </cell>
           <cell r="B380" t="str">
-            <v>最大HP+2</v>
+            <v>命中率+5%</v>
           </cell>
         </row>
         <row r="381">
           <cell r="A381">
-            <v>504110</v>
+            <v>504040</v>
           </cell>
           <cell r="B381" t="str">
-            <v>命中率+10%</v>
+            <v>最大HP+2</v>
           </cell>
         </row>
         <row r="382">
           <cell r="A382">
-            <v>504120</v>
+            <v>504110</v>
           </cell>
           <cell r="B382" t="str">
-            <v>最大HP+2</v>
+            <v>命中率+10%</v>
           </cell>
         </row>
         <row r="383">
           <cell r="A383">
-            <v>504130</v>
+            <v>504120</v>
           </cell>
           <cell r="B383" t="str">
-            <v>ダメージ軽減効果無視+10%</v>
+            <v>最大HP+2</v>
           </cell>
         </row>
         <row r="384">
           <cell r="A384">
-            <v>505010</v>
+            <v>504130</v>
           </cell>
           <cell r="B384" t="str">
-            <v>回避率+5%</v>
+            <v>ダメージ軽減効果無視+10%</v>
           </cell>
         </row>
         <row r="385">
           <cell r="A385">
-            <v>505020</v>
+            <v>505010</v>
           </cell>
           <cell r="B385" t="str">
-            <v>SPD+1</v>
+            <v>回避率+5%</v>
           </cell>
         </row>
         <row r="386">
           <cell r="A386">
-            <v>505030</v>
+            <v>505020</v>
           </cell>
           <cell r="B386" t="str">
-            <v>最大HP+2</v>
+            <v>SPD+1</v>
           </cell>
         </row>
         <row r="387">
           <cell r="A387">
-            <v>505040</v>
+            <v>505030</v>
           </cell>
           <cell r="B387" t="str">
-            <v>ATK+1</v>
+            <v>最大HP+2</v>
           </cell>
         </row>
         <row r="388">
           <cell r="A388">
-            <v>505110</v>
+            <v>505040</v>
           </cell>
           <cell r="B388" t="str">
-            <v>命中率+5%</v>
+            <v>ATK+1</v>
           </cell>
         </row>
         <row r="389">
           <cell r="A389">
-            <v>505111</v>
+            <v>505110</v>
           </cell>
           <cell r="B389" t="str">
-            <v>回避率+5%</v>
+            <v>命中率+5%</v>
           </cell>
         </row>
         <row r="390">
           <cell r="A390">
-            <v>505120</v>
+            <v>505111</v>
           </cell>
           <cell r="B390" t="str">
-            <v>ATK+1</v>
+            <v>回避率+5%</v>
           </cell>
         </row>
         <row r="391">
           <cell r="A391">
-            <v>505121</v>
+            <v>505120</v>
           </cell>
           <cell r="B391" t="str">
-            <v>SPD+1</v>
+            <v>ATK+1</v>
           </cell>
         </row>
         <row r="392">
           <cell r="A392">
-            <v>505130</v>
+            <v>505121</v>
           </cell>
           <cell r="B392" t="str">
-            <v>SPD+2</v>
+            <v>SPD+1</v>
           </cell>
         </row>
         <row r="393">
           <cell r="A393">
-            <v>506010</v>
+            <v>505130</v>
           </cell>
           <cell r="B393" t="str">
-            <v>最大HP+3</v>
+            <v>SPD+2</v>
           </cell>
         </row>
         <row r="394">
           <cell r="A394">
-            <v>506011</v>
+            <v>506010</v>
           </cell>
           <cell r="B394" t="str">
-            <v>DEF+1</v>
+            <v>最大HP+3</v>
           </cell>
         </row>
         <row r="395">
           <cell r="A395">
-            <v>506012</v>
+            <v>506011</v>
           </cell>
           <cell r="B395" t="str">
-            <v>SPD+1</v>
+            <v>DEF+1</v>
           </cell>
         </row>
         <row r="396">
           <cell r="A396">
-            <v>506013</v>
+            <v>506012</v>
           </cell>
           <cell r="B396" t="str">
-            <v>EXP+20%</v>
+            <v>SPD+1</v>
           </cell>
         </row>
         <row r="397">
           <cell r="A397">
-            <v>506020</v>
+            <v>506013</v>
           </cell>
           <cell r="B397" t="str">
-            <v>炎属性耐性+20%</v>
+            <v>EXP+20%</v>
           </cell>
         </row>
         <row r="398">
           <cell r="A398">
-            <v>506030</v>
+            <v>506020</v>
           </cell>
           <cell r="B398" t="str">
-            <v>雷属性耐性+20%</v>
+            <v>炎属性耐性+20%</v>
           </cell>
         </row>
         <row r="399">
           <cell r="A399">
-            <v>506040</v>
+            <v>506030</v>
           </cell>
           <cell r="B399" t="str">
-            <v>氷属性耐性+20%</v>
+            <v>雷属性耐性+20%</v>
           </cell>
         </row>
         <row r="400">
           <cell r="A400">
-            <v>506050</v>
+            <v>506040</v>
           </cell>
           <cell r="B400" t="str">
-            <v>光属性耐性+20%</v>
+            <v>氷属性耐性+20%</v>
           </cell>
         </row>
         <row r="401">
           <cell r="A401">
-            <v>506060</v>
+            <v>506050</v>
           </cell>
           <cell r="B401" t="str">
-            <v>闇属性耐性+20%</v>
+            <v>光属性耐性+20%</v>
           </cell>
         </row>
         <row r="402">
           <cell r="A402">
-            <v>507010</v>
+            <v>506060</v>
           </cell>
           <cell r="B402" t="str">
-            <v>獲得Exp+30%</v>
+            <v>闇属性耐性+20%</v>
           </cell>
         </row>
         <row r="403">
           <cell r="A403">
+            <v>507010</v>
+          </cell>
+          <cell r="B403" t="str">
+            <v>獲得Exp+30%</v>
+          </cell>
+        </row>
+        <row r="404">
+          <cell r="A404">
             <v>507020</v>
           </cell>
-          <cell r="B403" t="str">
+          <cell r="B404" t="str">
             <v>ATK⇔DEF交換</v>
           </cell>
         </row>
@@ -5991,16 +5999,16 @@
         <v>100</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H22">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I22">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -6015,19 +6023,19 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
+        <v>45</v>
+      </c>
+      <c r="Q22">
         <v>70</v>
       </c>
-      <c r="Q22">
-        <v>60</v>
-      </c>
       <c r="R22">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="S22" t="s">
         <v>19</v>

--- a/Assets/Data/Enemies.xlsx
+++ b/Assets/Data/Enemies.xlsx
@@ -461,8 +461,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -481,62 +481,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -550,21 +497,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -579,16 +548,47 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -603,14 +603,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -618,10 +618,10 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -634,7 +634,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -646,133 +790,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -784,31 +802,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -829,6 +829,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -843,17 +858,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -861,17 +870,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -891,11 +891,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -910,21 +925,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -933,145 +933,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3173,1007 +3173,1007 @@
         </row>
         <row r="252">
           <cell r="A252">
-            <v>320010</v>
+            <v>401010</v>
           </cell>
           <cell r="B252" t="str">
-            <v>訓練所Lv1</v>
+            <v>ファイアボール+</v>
           </cell>
         </row>
         <row r="253">
           <cell r="A253">
-            <v>320011</v>
+            <v>401020</v>
           </cell>
           <cell r="B253" t="str">
-            <v>訓練所Lv2</v>
+            <v>バーンストーム+</v>
           </cell>
         </row>
         <row r="254">
           <cell r="A254">
-            <v>320012</v>
+            <v>401030</v>
           </cell>
           <cell r="B254" t="str">
-            <v>訓練所Lv3</v>
+            <v>ヒートスタンプ+</v>
           </cell>
         </row>
         <row r="255">
           <cell r="A255">
-            <v>320020</v>
+            <v>401040</v>
           </cell>
           <cell r="B255" t="str">
-            <v>研究施設Lv1</v>
+            <v>ソードアダプト+</v>
           </cell>
         </row>
         <row r="256">
           <cell r="A256">
-            <v>320021</v>
+            <v>401050</v>
           </cell>
           <cell r="B256" t="str">
-            <v>研究施設Lv2</v>
+            <v>フレイムレイン+</v>
           </cell>
         </row>
         <row r="257">
           <cell r="A257">
-            <v>320022</v>
+            <v>401060</v>
           </cell>
           <cell r="B257" t="str">
-            <v>研究施設Lv3</v>
+            <v>イクスティンクション+</v>
           </cell>
         </row>
         <row r="258">
           <cell r="A258">
-            <v>320030</v>
+            <v>401070</v>
           </cell>
           <cell r="B258" t="str">
-            <v>資料館Lv1</v>
+            <v>バーニングソウル+</v>
           </cell>
         </row>
         <row r="259">
           <cell r="A259">
-            <v>320031</v>
+            <v>401080</v>
           </cell>
           <cell r="B259" t="str">
-            <v>資料館Lv2</v>
+            <v>レイジングバウンサー+</v>
           </cell>
         </row>
         <row r="260">
           <cell r="A260">
-            <v>320032</v>
+            <v>402010</v>
           </cell>
           <cell r="B260" t="str">
-            <v>資料館Lv3</v>
+            <v>ディスチャージ+</v>
           </cell>
         </row>
         <row r="261">
           <cell r="A261">
-            <v>320040</v>
+            <v>402020</v>
           </cell>
           <cell r="B261" t="str">
-            <v>潜伏技術Lv1</v>
+            <v>イベイドコード+</v>
           </cell>
         </row>
         <row r="262">
           <cell r="A262">
-            <v>321010</v>
+            <v>402030</v>
           </cell>
           <cell r="B262" t="str">
-            <v>炎の祭壇</v>
+            <v>ショックインパルス+</v>
           </cell>
         </row>
         <row r="263">
           <cell r="A263">
-            <v>321020</v>
+            <v>402040</v>
           </cell>
           <cell r="B263" t="str">
-            <v>稲妻の祭壇</v>
+            <v>トラストチェイン+</v>
           </cell>
         </row>
         <row r="264">
           <cell r="A264">
-            <v>321030</v>
+            <v>402050</v>
           </cell>
           <cell r="B264" t="str">
-            <v>蒼の祭壇</v>
+            <v>スペルバニシング+</v>
           </cell>
         </row>
         <row r="265">
           <cell r="A265">
-            <v>321040</v>
+            <v>402060</v>
           </cell>
           <cell r="B265" t="str">
-            <v>光の祭壇</v>
+            <v>アーテニーストライク+</v>
           </cell>
         </row>
         <row r="266">
           <cell r="A266">
-            <v>321050</v>
+            <v>402070</v>
           </cell>
           <cell r="B266" t="str">
-            <v>月の祭壇</v>
+            <v>コンセントレイト+</v>
           </cell>
         </row>
         <row r="267">
           <cell r="A267">
-            <v>322010</v>
+            <v>402080</v>
           </cell>
           <cell r="B267" t="str">
-            <v>食糧庫Lv1</v>
+            <v>ディレイマジック+</v>
           </cell>
         </row>
         <row r="268">
           <cell r="A268">
-            <v>322020</v>
+            <v>403010</v>
           </cell>
           <cell r="B268" t="str">
-            <v>攻撃技術Lv1</v>
+            <v>アイスブレイド+</v>
           </cell>
         </row>
         <row r="269">
           <cell r="A269">
-            <v>322030</v>
+            <v>403020</v>
           </cell>
           <cell r="B269" t="str">
-            <v>防御技術Lv1</v>
+            <v>カウンターオーラ+</v>
           </cell>
         </row>
         <row r="270">
           <cell r="A270">
-            <v>322040</v>
+            <v>403030</v>
           </cell>
           <cell r="B270" t="str">
-            <v>詠唱技術Lv1</v>
+            <v>ラインプロテクト+</v>
           </cell>
         </row>
         <row r="271">
           <cell r="A271">
-            <v>401010</v>
+            <v>403040</v>
           </cell>
           <cell r="B271" t="str">
-            <v>ファイアボール+</v>
+            <v>エスコートソール+</v>
           </cell>
         </row>
         <row r="272">
           <cell r="A272">
-            <v>401020</v>
+            <v>403050</v>
           </cell>
           <cell r="B272" t="str">
-            <v>バーンストーム+</v>
+            <v>ディープフリーズ+</v>
           </cell>
         </row>
         <row r="273">
           <cell r="A273">
-            <v>401030</v>
+            <v>403060</v>
           </cell>
           <cell r="B273" t="str">
-            <v>ヒートスタンプ+</v>
+            <v>バブルブロウ+</v>
           </cell>
         </row>
         <row r="274">
           <cell r="A274">
-            <v>401040</v>
+            <v>403070</v>
           </cell>
           <cell r="B274" t="str">
-            <v>ソードアダプト+</v>
+            <v>アクアミラージュ+</v>
           </cell>
         </row>
         <row r="275">
           <cell r="A275">
-            <v>401050</v>
+            <v>403080</v>
           </cell>
           <cell r="B275" t="str">
-            <v>フレイムレイン+</v>
+            <v>フロストシールド+</v>
           </cell>
         </row>
         <row r="276">
           <cell r="A276">
-            <v>401060</v>
+            <v>404010</v>
           </cell>
           <cell r="B276" t="str">
-            <v>イクスティンクション+</v>
+            <v>セイントレーザー+</v>
           </cell>
         </row>
         <row r="277">
           <cell r="A277">
-            <v>401070</v>
+            <v>404020</v>
           </cell>
           <cell r="B277" t="str">
-            <v>バーニングソウル+</v>
+            <v>ペネトレイト+</v>
           </cell>
         </row>
         <row r="278">
           <cell r="A278">
-            <v>401080</v>
+            <v>404030</v>
           </cell>
           <cell r="B278" t="str">
-            <v>レイジングバウンサー+</v>
+            <v>ヒーリング+</v>
           </cell>
         </row>
         <row r="279">
           <cell r="A279">
-            <v>402010</v>
+            <v>404040</v>
           </cell>
           <cell r="B279" t="str">
-            <v>ディスチャージ+</v>
+            <v>リザイアフォトン+</v>
           </cell>
         </row>
         <row r="280">
           <cell r="A280">
-            <v>402020</v>
+            <v>404050</v>
           </cell>
           <cell r="B280" t="str">
-            <v>イベイドコード+</v>
+            <v>べネディクション+</v>
           </cell>
         </row>
         <row r="281">
           <cell r="A281">
-            <v>402030</v>
+            <v>404060</v>
           </cell>
           <cell r="B281" t="str">
-            <v>ショックインパルス+</v>
+            <v>ホーリーグレイス+</v>
           </cell>
         </row>
         <row r="282">
           <cell r="A282">
-            <v>402040</v>
+            <v>404070</v>
           </cell>
           <cell r="B282" t="str">
-            <v>トラストチェイン+</v>
+            <v>キュアエール+</v>
           </cell>
         </row>
         <row r="283">
           <cell r="A283">
-            <v>402050</v>
+            <v>404080</v>
           </cell>
           <cell r="B283" t="str">
-            <v>スペルバニシング+</v>
+            <v>ラインバリア+</v>
           </cell>
         </row>
         <row r="284">
           <cell r="A284">
-            <v>402060</v>
+            <v>405010</v>
           </cell>
           <cell r="B284" t="str">
-            <v>アーテニーストライク+</v>
+            <v>ダークプリズン+</v>
           </cell>
         </row>
         <row r="285">
           <cell r="A285">
-            <v>402070</v>
+            <v>405020</v>
           </cell>
           <cell r="B285" t="str">
-            <v>コンセントレイト+</v>
+            <v>ユーサネイジア+</v>
           </cell>
         </row>
         <row r="286">
           <cell r="A286">
-            <v>402080</v>
+            <v>405030</v>
           </cell>
           <cell r="B286" t="str">
-            <v>ディレイマジック+</v>
+            <v>ドレインヒール+</v>
           </cell>
         </row>
         <row r="287">
           <cell r="A287">
-            <v>403010</v>
+            <v>405040</v>
           </cell>
           <cell r="B287" t="str">
-            <v>アイスブレイド+</v>
+            <v>アビサルデスペア+</v>
           </cell>
         </row>
         <row r="288">
           <cell r="A288">
-            <v>403020</v>
+            <v>405050</v>
           </cell>
           <cell r="B288" t="str">
-            <v>カウンターオーラ+</v>
+            <v>ディプラヴィティ+</v>
           </cell>
         </row>
         <row r="289">
           <cell r="A289">
-            <v>403030</v>
+            <v>405060</v>
           </cell>
           <cell r="B289" t="str">
-            <v>ラインプロテクト+</v>
+            <v>ダークネス+</v>
           </cell>
         </row>
         <row r="290">
           <cell r="A290">
-            <v>403040</v>
+            <v>405070</v>
           </cell>
           <cell r="B290" t="str">
-            <v>エスコートソール+</v>
+            <v>シェイディークラウド+</v>
           </cell>
         </row>
         <row r="291">
           <cell r="A291">
-            <v>403050</v>
+            <v>405080</v>
           </cell>
           <cell r="B291" t="str">
-            <v>ディープフリーズ+</v>
+            <v>ポイズンブロウ+</v>
           </cell>
         </row>
         <row r="292">
           <cell r="A292">
-            <v>403060</v>
+            <v>411010</v>
           </cell>
           <cell r="B292" t="str">
-            <v>バブルブロウ+</v>
+            <v>ウルフソウル+</v>
           </cell>
         </row>
         <row r="293">
           <cell r="A293">
-            <v>403070</v>
+            <v>411020</v>
           </cell>
           <cell r="B293" t="str">
-            <v>アクアミラージュ+</v>
+            <v>プリディカメント+</v>
           </cell>
         </row>
         <row r="294">
           <cell r="A294">
-            <v>403080</v>
+            <v>411030</v>
           </cell>
           <cell r="B294" t="str">
-            <v>フロストシールド+</v>
+            <v>アサルトシフト+</v>
           </cell>
         </row>
         <row r="295">
           <cell r="A295">
-            <v>404010</v>
+            <v>411040</v>
           </cell>
           <cell r="B295" t="str">
-            <v>セイントレーザー+</v>
+            <v>アクティブギフト+</v>
           </cell>
         </row>
         <row r="296">
           <cell r="A296">
-            <v>404020</v>
+            <v>411050</v>
           </cell>
           <cell r="B296" t="str">
-            <v>ペネトレイト+</v>
+            <v>イグナイテッド+</v>
           </cell>
         </row>
         <row r="297">
           <cell r="A297">
-            <v>404030</v>
+            <v>411060</v>
           </cell>
           <cell r="B297" t="str">
-            <v>ヒーリング+</v>
+            <v>ライジングファイア+</v>
           </cell>
         </row>
         <row r="298">
           <cell r="A298">
-            <v>404040</v>
+            <v>411070</v>
           </cell>
           <cell r="B298" t="str">
-            <v>リザイアフォトン+</v>
+            <v>ルージュバック+</v>
           </cell>
         </row>
         <row r="299">
           <cell r="A299">
-            <v>404050</v>
+            <v>411080</v>
           </cell>
           <cell r="B299" t="str">
-            <v>べネディクション+</v>
+            <v>パワーエール+</v>
           </cell>
         </row>
         <row r="300">
           <cell r="A300">
-            <v>404060</v>
+            <v>411090</v>
           </cell>
           <cell r="B300" t="str">
-            <v>ホーリーグレイス+</v>
+            <v>スレイプニル+</v>
           </cell>
         </row>
         <row r="301">
           <cell r="A301">
-            <v>404070</v>
+            <v>412010</v>
           </cell>
           <cell r="B301" t="str">
-            <v>キュアエール+</v>
+            <v>エクステンション+</v>
           </cell>
         </row>
         <row r="302">
           <cell r="A302">
-            <v>404080</v>
+            <v>412020</v>
           </cell>
           <cell r="B302" t="str">
-            <v>ラインバリア+</v>
+            <v>ヘブンリーラック+</v>
           </cell>
         </row>
         <row r="303">
           <cell r="A303">
-            <v>405010</v>
+            <v>412030</v>
           </cell>
           <cell r="B303" t="str">
-            <v>ダークプリズン+</v>
+            <v>スウィフトカレント+</v>
           </cell>
         </row>
         <row r="304">
           <cell r="A304">
-            <v>405020</v>
+            <v>412040</v>
           </cell>
           <cell r="B304" t="str">
-            <v>ユーサネイジア+</v>
+            <v>イヴェイドオール+</v>
           </cell>
         </row>
         <row r="305">
           <cell r="A305">
-            <v>405030</v>
+            <v>412050</v>
           </cell>
           <cell r="B305" t="str">
-            <v>ドレインヒール+</v>
+            <v>クイックムーブ+</v>
           </cell>
         </row>
         <row r="306">
           <cell r="A306">
-            <v>405040</v>
+            <v>412060</v>
           </cell>
           <cell r="B306" t="str">
-            <v>アビサルデスペア+</v>
+            <v>チェイスマジック+</v>
           </cell>
         </row>
         <row r="307">
           <cell r="A307">
-            <v>405050</v>
+            <v>412070</v>
           </cell>
           <cell r="B307" t="str">
-            <v>ディプラヴィティ+</v>
+            <v>ソーサリーコネクト+</v>
           </cell>
         </row>
         <row r="308">
           <cell r="A308">
-            <v>405060</v>
+            <v>412080</v>
           </cell>
           <cell r="B308" t="str">
-            <v>ダークネス+</v>
+            <v>ウィンドライズ+</v>
           </cell>
         </row>
         <row r="309">
           <cell r="A309">
-            <v>405070</v>
+            <v>412090</v>
           </cell>
           <cell r="B309" t="str">
-            <v>シェイディークラウド+</v>
+            <v>アウトオブオーダー+</v>
           </cell>
         </row>
         <row r="310">
           <cell r="A310">
-            <v>405080</v>
+            <v>413010</v>
           </cell>
           <cell r="B310" t="str">
-            <v>ポイズンブロウ+</v>
+            <v>アーマーコード+</v>
           </cell>
         </row>
         <row r="311">
           <cell r="A311">
-            <v>411010</v>
+            <v>413020</v>
           </cell>
           <cell r="B311" t="str">
-            <v>ウルフソウル+</v>
+            <v>クイックバリア+</v>
           </cell>
         </row>
         <row r="312">
           <cell r="A312">
-            <v>411020</v>
+            <v>413030</v>
           </cell>
           <cell r="B312" t="str">
-            <v>プリディカメント+</v>
+            <v>クイックキュア+</v>
           </cell>
         </row>
         <row r="313">
           <cell r="A313">
-            <v>411030</v>
+            <v>413040</v>
           </cell>
           <cell r="B313" t="str">
-            <v>アサルトシフト+</v>
+            <v>セルフシールド+</v>
           </cell>
         </row>
         <row r="314">
           <cell r="A314">
-            <v>411040</v>
+            <v>413050</v>
           </cell>
           <cell r="B314" t="str">
-            <v>アクティブギフト+</v>
+            <v>パッシブジャミング+</v>
           </cell>
         </row>
         <row r="315">
           <cell r="A315">
-            <v>411050</v>
+            <v>413060</v>
           </cell>
           <cell r="B315" t="str">
-            <v>イグナイテッド+</v>
+            <v>サプライカバー+</v>
           </cell>
         </row>
         <row r="316">
           <cell r="A316">
-            <v>411060</v>
+            <v>413070</v>
           </cell>
           <cell r="B316" t="str">
-            <v>ライジングファイア+</v>
+            <v>アシッドラッシュ+</v>
           </cell>
         </row>
         <row r="317">
           <cell r="A317">
-            <v>411070</v>
+            <v>413080</v>
           </cell>
           <cell r="B317" t="str">
-            <v>ルージュバック+</v>
+            <v>ライフスティール+</v>
           </cell>
         </row>
         <row r="318">
           <cell r="A318">
-            <v>411080</v>
+            <v>413090</v>
           </cell>
           <cell r="B318" t="str">
-            <v>パワーエール+</v>
+            <v>アイスセイバー+</v>
           </cell>
         </row>
         <row r="319">
           <cell r="A319">
-            <v>411090</v>
+            <v>414010</v>
           </cell>
           <cell r="B319" t="str">
-            <v>スレイプニル+</v>
+            <v>ディバインシールド+</v>
           </cell>
         </row>
         <row r="320">
           <cell r="A320">
-            <v>412010</v>
+            <v>414020</v>
           </cell>
           <cell r="B320" t="str">
-            <v>エクステンション+</v>
+            <v>ライフディバイド+</v>
           </cell>
         </row>
         <row r="321">
           <cell r="A321">
-            <v>412020</v>
+            <v>414030</v>
           </cell>
           <cell r="B321" t="str">
-            <v>ヘブンリーラック+</v>
+            <v>エイミングスコープ+</v>
           </cell>
         </row>
         <row r="322">
           <cell r="A322">
-            <v>412030</v>
+            <v>414040</v>
           </cell>
           <cell r="B322" t="str">
-            <v>スウィフトカレント+</v>
+            <v>リジェネレーション+</v>
           </cell>
         </row>
         <row r="323">
           <cell r="A323">
-            <v>412040</v>
+            <v>414050</v>
           </cell>
           <cell r="B323" t="str">
-            <v>イヴェイドオール+</v>
+            <v>ホープフルアイリス+</v>
           </cell>
         </row>
         <row r="324">
           <cell r="A324">
-            <v>412050</v>
+            <v>414060</v>
           </cell>
           <cell r="B324" t="str">
-            <v>クイックムーブ+</v>
+            <v>パッシブサプライ+</v>
           </cell>
         </row>
         <row r="325">
           <cell r="A325">
-            <v>412060</v>
+            <v>414070</v>
           </cell>
           <cell r="B325" t="str">
-            <v>チェイスマジック+</v>
+            <v>ホーミングクルセイド+</v>
           </cell>
         </row>
         <row r="326">
           <cell r="A326">
-            <v>412070</v>
+            <v>414080</v>
           </cell>
           <cell r="B326" t="str">
-            <v>ソーサリーコネクト+</v>
+            <v>クイックヒール+</v>
           </cell>
         </row>
         <row r="327">
           <cell r="A327">
-            <v>412080</v>
+            <v>414090</v>
           </cell>
           <cell r="B327" t="str">
-            <v>ウィンドライズ+</v>
+            <v>リレイズ+</v>
           </cell>
         </row>
         <row r="328">
           <cell r="A328">
-            <v>412090</v>
+            <v>415010</v>
           </cell>
           <cell r="B328" t="str">
-            <v>アウトオブオーダー+</v>
+            <v>イーグルアイ+</v>
           </cell>
         </row>
         <row r="329">
           <cell r="A329">
-            <v>413010</v>
+            <v>415020</v>
           </cell>
           <cell r="B329" t="str">
-            <v>アーマーコード+</v>
+            <v>ネヴァーエンド+</v>
           </cell>
         </row>
         <row r="330">
           <cell r="A330">
-            <v>413020</v>
+            <v>415030</v>
           </cell>
           <cell r="B330" t="str">
-            <v>クイックバリア+</v>
+            <v>グレイブアクト+</v>
           </cell>
         </row>
         <row r="331">
           <cell r="A331">
-            <v>413030</v>
+            <v>415040</v>
           </cell>
           <cell r="B331" t="str">
-            <v>クイックキュア+</v>
+            <v>スカルグラッジ+</v>
           </cell>
         </row>
         <row r="332">
           <cell r="A332">
-            <v>413040</v>
+            <v>415050</v>
           </cell>
           <cell r="B332" t="str">
-            <v>セルフシールド+</v>
+            <v>ネガティブドレイン+</v>
           </cell>
         </row>
         <row r="333">
           <cell r="A333">
-            <v>413050</v>
+            <v>415060</v>
           </cell>
           <cell r="B333" t="str">
-            <v>パッシブジャミング+</v>
+            <v>アンデッドペイン+</v>
           </cell>
         </row>
         <row r="334">
           <cell r="A334">
-            <v>413060</v>
+            <v>415070</v>
           </cell>
           <cell r="B334" t="str">
-            <v>サプライカバー+</v>
+            <v>ジャックポッド+</v>
           </cell>
         </row>
         <row r="335">
           <cell r="A335">
-            <v>413070</v>
+            <v>415080</v>
           </cell>
           <cell r="B335" t="str">
-            <v>アシッドラッシュ+</v>
+            <v>ヒールハント+</v>
           </cell>
         </row>
         <row r="336">
           <cell r="A336">
-            <v>413080</v>
+            <v>415090</v>
           </cell>
           <cell r="B336" t="str">
-            <v>ライフスティール+</v>
+            <v>クイックカース+</v>
           </cell>
         </row>
         <row r="337">
           <cell r="A337">
-            <v>413090</v>
+            <v>501010</v>
           </cell>
           <cell r="B337" t="str">
-            <v>アイスセイバー+</v>
+            <v>火傷耐性+20%</v>
           </cell>
         </row>
         <row r="338">
           <cell r="A338">
-            <v>414010</v>
+            <v>501020</v>
           </cell>
           <cell r="B338" t="str">
-            <v>ディバインシールド+</v>
+            <v>命中率+5%</v>
           </cell>
         </row>
         <row r="339">
           <cell r="A339">
-            <v>414020</v>
+            <v>501030</v>
           </cell>
           <cell r="B339" t="str">
-            <v>ライフディバイド+</v>
+            <v>最大HP+2</v>
           </cell>
         </row>
         <row r="340">
           <cell r="A340">
-            <v>414030</v>
+            <v>501040</v>
           </cell>
           <cell r="B340" t="str">
-            <v>エイミングスコープ+</v>
+            <v>ATK+2</v>
           </cell>
         </row>
         <row r="341">
           <cell r="A341">
-            <v>414040</v>
+            <v>501110</v>
           </cell>
           <cell r="B341" t="str">
-            <v>リジェネレーション+</v>
+            <v>DEF+2</v>
           </cell>
         </row>
         <row r="342">
           <cell r="A342">
-            <v>414050</v>
+            <v>501120</v>
           </cell>
           <cell r="B342" t="str">
-            <v>ホープフルアイリス+</v>
+            <v>命中率+10%</v>
           </cell>
         </row>
         <row r="343">
           <cell r="A343">
-            <v>414060</v>
+            <v>501130</v>
           </cell>
           <cell r="B343" t="str">
-            <v>パッシブサプライ+</v>
+            <v>SPD+2</v>
           </cell>
         </row>
         <row r="344">
           <cell r="A344">
-            <v>414070</v>
+            <v>501210</v>
           </cell>
           <cell r="B344" t="str">
-            <v>ホーミングクルセイド+</v>
+            <v>火傷耐性+20%</v>
           </cell>
         </row>
         <row r="345">
           <cell r="A345">
-            <v>414080</v>
+            <v>501220</v>
           </cell>
           <cell r="B345" t="str">
-            <v>クイックヒール+</v>
+            <v>命中率+5%</v>
           </cell>
         </row>
         <row r="346">
           <cell r="A346">
-            <v>414090</v>
+            <v>501230</v>
           </cell>
           <cell r="B346" t="str">
-            <v>リレイズ+</v>
+            <v>最大HP+2</v>
           </cell>
         </row>
         <row r="347">
           <cell r="A347">
-            <v>415010</v>
+            <v>501240</v>
           </cell>
           <cell r="B347" t="str">
-            <v>イーグルアイ+</v>
+            <v>ATK+2</v>
           </cell>
         </row>
         <row r="348">
           <cell r="A348">
-            <v>415020</v>
+            <v>502010</v>
           </cell>
           <cell r="B348" t="str">
-            <v>ネヴァーエンド+</v>
+            <v>DEF+1</v>
           </cell>
         </row>
         <row r="349">
           <cell r="A349">
-            <v>415030</v>
+            <v>502020</v>
           </cell>
           <cell r="B349" t="str">
-            <v>グレイブアクト+</v>
+            <v>SPD+1</v>
           </cell>
         </row>
         <row r="350">
           <cell r="A350">
-            <v>415040</v>
+            <v>502030</v>
           </cell>
           <cell r="B350" t="str">
-            <v>スカルグラッジ+</v>
+            <v>SPD+1</v>
           </cell>
         </row>
         <row r="351">
           <cell r="A351">
-            <v>415050</v>
+            <v>502040</v>
           </cell>
           <cell r="B351" t="str">
-            <v>ネガティブドレイン+</v>
+            <v>回避率+5%</v>
           </cell>
         </row>
         <row r="352">
           <cell r="A352">
-            <v>415060</v>
+            <v>502110</v>
           </cell>
           <cell r="B352" t="str">
-            <v>アンデッドペイン+</v>
+            <v>会心ダメージ率+25%</v>
           </cell>
         </row>
         <row r="353">
           <cell r="A353">
-            <v>415070</v>
+            <v>502120</v>
           </cell>
           <cell r="B353" t="str">
-            <v>ジャックポッド+</v>
+            <v>命中率+5%</v>
           </cell>
         </row>
         <row r="354">
           <cell r="A354">
-            <v>415080</v>
+            <v>502121</v>
           </cell>
           <cell r="B354" t="str">
-            <v>ヒールハント+</v>
+            <v>回避率+5%</v>
           </cell>
         </row>
         <row r="355">
           <cell r="A355">
-            <v>415090</v>
+            <v>502130</v>
           </cell>
           <cell r="B355" t="str">
-            <v>クイックカース+</v>
+            <v>SPD+2</v>
           </cell>
         </row>
         <row r="356">
           <cell r="A356">
-            <v>501010</v>
+            <v>502210</v>
           </cell>
           <cell r="B356" t="str">
-            <v>火傷耐性+20%</v>
+            <v>DEF+1</v>
           </cell>
         </row>
         <row r="357">
           <cell r="A357">
-            <v>501020</v>
+            <v>502220</v>
           </cell>
           <cell r="B357" t="str">
-            <v>命中率+5%</v>
+            <v>SPD+1</v>
           </cell>
         </row>
         <row r="358">
           <cell r="A358">
-            <v>501030</v>
+            <v>502230</v>
           </cell>
           <cell r="B358" t="str">
-            <v>最大HP+2</v>
+            <v>SPD+1</v>
           </cell>
         </row>
         <row r="359">
           <cell r="A359">
-            <v>501040</v>
+            <v>502240</v>
           </cell>
           <cell r="B359" t="str">
-            <v>ATK+2</v>
+            <v>回避率+5%</v>
           </cell>
         </row>
         <row r="360">
           <cell r="A360">
-            <v>501110</v>
+            <v>503010</v>
           </cell>
           <cell r="B360" t="str">
-            <v>DEF+2</v>
+            <v>DEF+1</v>
           </cell>
         </row>
         <row r="361">
           <cell r="A361">
-            <v>501120</v>
+            <v>503020</v>
           </cell>
           <cell r="B361" t="str">
-            <v>命中率+10%</v>
+            <v>凍結耐性+20%</v>
           </cell>
         </row>
         <row r="362">
           <cell r="A362">
-            <v>501130</v>
+            <v>503030</v>
           </cell>
           <cell r="B362" t="str">
-            <v>SPD+2</v>
+            <v>最大HP+2</v>
           </cell>
         </row>
         <row r="363">
           <cell r="A363">
-            <v>502010</v>
+            <v>503040</v>
           </cell>
           <cell r="B363" t="str">
-            <v>DEF+1</v>
+            <v>DEF+2</v>
           </cell>
         </row>
         <row r="364">
           <cell r="A364">
-            <v>502020</v>
+            <v>503110</v>
           </cell>
           <cell r="B364" t="str">
-            <v>SPD+1</v>
+            <v>DEF+2</v>
           </cell>
         </row>
         <row r="365">
           <cell r="A365">
-            <v>502030</v>
+            <v>503120</v>
           </cell>
           <cell r="B365" t="str">
-            <v>SPD+1</v>
+            <v>ATK+2</v>
           </cell>
         </row>
         <row r="366">
           <cell r="A366">
-            <v>502040</v>
+            <v>503130</v>
           </cell>
           <cell r="B366" t="str">
-            <v>回避率+5%</v>
+            <v>ダメージ軽減効果無視+10%</v>
           </cell>
         </row>
         <row r="367">
           <cell r="A367">
-            <v>502110</v>
+            <v>503210</v>
           </cell>
           <cell r="B367" t="str">
-            <v>会心ダメージ率+25%</v>
+            <v>DEF+1</v>
           </cell>
         </row>
         <row r="368">
           <cell r="A368">
-            <v>502120</v>
+            <v>503220</v>
           </cell>
           <cell r="B368" t="str">
-            <v>命中率+5%</v>
+            <v>凍結耐性+20%</v>
           </cell>
         </row>
         <row r="369">
           <cell r="A369">
-            <v>502121</v>
+            <v>503230</v>
           </cell>
           <cell r="B369" t="str">
-            <v>回避率+5%</v>
+            <v>最大HP+2</v>
           </cell>
         </row>
         <row r="370">
           <cell r="A370">
-            <v>502130</v>
+            <v>503240</v>
           </cell>
           <cell r="B370" t="str">
-            <v>SPD+2</v>
+            <v>DEF+2</v>
           </cell>
         </row>
         <row r="371">
           <cell r="A371">
-            <v>503010</v>
+            <v>504010</v>
           </cell>
           <cell r="B371" t="str">
-            <v>DEF+1</v>
+            <v>Hp回復効果+2</v>
           </cell>
         </row>
         <row r="372">
           <cell r="A372">
-            <v>503020</v>
+            <v>504020</v>
           </cell>
           <cell r="B372" t="str">
-            <v>凍結耐性+20%</v>
+            <v>SPD+1</v>
           </cell>
         </row>
         <row r="373">
           <cell r="A373">
-            <v>503030</v>
+            <v>504030</v>
           </cell>
           <cell r="B373" t="str">
-            <v>最大HP+2</v>
+            <v>命中率+5%</v>
           </cell>
         </row>
         <row r="374">
           <cell r="A374">
-            <v>503040</v>
+            <v>504040</v>
           </cell>
           <cell r="B374" t="str">
-            <v>DEF+2</v>
+            <v>最大HP+2</v>
           </cell>
         </row>
         <row r="375">
           <cell r="A375">
-            <v>503110</v>
+            <v>504110</v>
           </cell>
           <cell r="B375" t="str">
-            <v>DEF+2</v>
+            <v>命中率+10%</v>
           </cell>
         </row>
         <row r="376">
           <cell r="A376">
-            <v>503120</v>
+            <v>504120</v>
           </cell>
           <cell r="B376" t="str">
-            <v>ATK+2</v>
+            <v>最大HP+2</v>
           </cell>
         </row>
         <row r="377">
           <cell r="A377">
-            <v>503130</v>
+            <v>504130</v>
           </cell>
           <cell r="B377" t="str">
             <v>ダメージ軽減効果無視+10%</v>
@@ -4181,7 +4181,7 @@
         </row>
         <row r="378">
           <cell r="A378">
-            <v>504010</v>
+            <v>504210</v>
           </cell>
           <cell r="B378" t="str">
             <v>Hp回復効果+2</v>
@@ -4189,7 +4189,7 @@
         </row>
         <row r="379">
           <cell r="A379">
-            <v>504020</v>
+            <v>504220</v>
           </cell>
           <cell r="B379" t="str">
             <v>SPD+1</v>
@@ -4197,7 +4197,7 @@
         </row>
         <row r="380">
           <cell r="A380">
-            <v>504030</v>
+            <v>504230</v>
           </cell>
           <cell r="B380" t="str">
             <v>命中率+5%</v>
@@ -4205,7 +4205,7 @@
         </row>
         <row r="381">
           <cell r="A381">
-            <v>504040</v>
+            <v>504240</v>
           </cell>
           <cell r="B381" t="str">
             <v>最大HP+2</v>
@@ -4213,55 +4213,55 @@
         </row>
         <row r="382">
           <cell r="A382">
-            <v>504110</v>
+            <v>505010</v>
           </cell>
           <cell r="B382" t="str">
-            <v>命中率+10%</v>
+            <v>回避率+5%</v>
           </cell>
         </row>
         <row r="383">
           <cell r="A383">
-            <v>504120</v>
+            <v>505020</v>
           </cell>
           <cell r="B383" t="str">
-            <v>最大HP+2</v>
+            <v>SPD+1</v>
           </cell>
         </row>
         <row r="384">
           <cell r="A384">
-            <v>504130</v>
+            <v>505030</v>
           </cell>
           <cell r="B384" t="str">
-            <v>ダメージ軽減効果無視+10%</v>
+            <v>最大HP+2</v>
           </cell>
         </row>
         <row r="385">
           <cell r="A385">
-            <v>505010</v>
+            <v>505040</v>
           </cell>
           <cell r="B385" t="str">
-            <v>回避率+5%</v>
+            <v>ATK+1</v>
           </cell>
         </row>
         <row r="386">
           <cell r="A386">
-            <v>505020</v>
+            <v>505110</v>
           </cell>
           <cell r="B386" t="str">
-            <v>SPD+1</v>
+            <v>命中率+5%</v>
           </cell>
         </row>
         <row r="387">
           <cell r="A387">
-            <v>505030</v>
+            <v>505111</v>
           </cell>
           <cell r="B387" t="str">
-            <v>最大HP+2</v>
+            <v>回避率+5%</v>
           </cell>
         </row>
         <row r="388">
           <cell r="A388">
-            <v>505040</v>
+            <v>505120</v>
           </cell>
           <cell r="B388" t="str">
             <v>ATK+1</v>
@@ -4269,31 +4269,31 @@
         </row>
         <row r="389">
           <cell r="A389">
-            <v>505110</v>
+            <v>505121</v>
           </cell>
           <cell r="B389" t="str">
-            <v>命中率+5%</v>
+            <v>SPD+1</v>
           </cell>
         </row>
         <row r="390">
           <cell r="A390">
-            <v>505111</v>
+            <v>505130</v>
           </cell>
           <cell r="B390" t="str">
-            <v>回避率+5%</v>
+            <v>SPD+2</v>
           </cell>
         </row>
         <row r="391">
           <cell r="A391">
-            <v>505120</v>
+            <v>505210</v>
           </cell>
           <cell r="B391" t="str">
-            <v>ATK+1</v>
+            <v>回避率+5%</v>
           </cell>
         </row>
         <row r="392">
           <cell r="A392">
-            <v>505121</v>
+            <v>505220</v>
           </cell>
           <cell r="B392" t="str">
             <v>SPD+1</v>
@@ -4301,97 +4301,105 @@
         </row>
         <row r="393">
           <cell r="A393">
-            <v>505130</v>
+            <v>505230</v>
           </cell>
           <cell r="B393" t="str">
-            <v>SPD+2</v>
+            <v>最大HP+2</v>
           </cell>
         </row>
         <row r="394">
           <cell r="A394">
-            <v>506010</v>
+            <v>505240</v>
           </cell>
           <cell r="B394" t="str">
-            <v>最大HP+3</v>
+            <v>ATK+1</v>
           </cell>
         </row>
         <row r="395">
           <cell r="A395">
-            <v>506011</v>
+            <v>506010</v>
           </cell>
           <cell r="B395" t="str">
-            <v>DEF+1</v>
+            <v>最大HP+3</v>
           </cell>
         </row>
         <row r="396">
           <cell r="A396">
-            <v>506012</v>
+            <v>506011</v>
           </cell>
           <cell r="B396" t="str">
-            <v>SPD+1</v>
+            <v>DEF+1</v>
           </cell>
         </row>
         <row r="397">
           <cell r="A397">
-            <v>506013</v>
+            <v>506012</v>
           </cell>
           <cell r="B397" t="str">
-            <v>EXP+20%</v>
+            <v>SPD+1</v>
           </cell>
         </row>
         <row r="398">
           <cell r="A398">
-            <v>506020</v>
+            <v>506013</v>
           </cell>
           <cell r="B398" t="str">
-            <v>炎属性耐性+20%</v>
+            <v>EXP+20%</v>
           </cell>
         </row>
         <row r="399">
           <cell r="A399">
-            <v>506030</v>
+            <v>506020</v>
           </cell>
           <cell r="B399" t="str">
-            <v>雷属性耐性+20%</v>
+            <v>炎属性耐性+20%</v>
           </cell>
         </row>
         <row r="400">
           <cell r="A400">
-            <v>506040</v>
+            <v>506030</v>
           </cell>
           <cell r="B400" t="str">
-            <v>氷属性耐性+20%</v>
+            <v>雷属性耐性+20%</v>
           </cell>
         </row>
         <row r="401">
           <cell r="A401">
-            <v>506050</v>
+            <v>506040</v>
           </cell>
           <cell r="B401" t="str">
-            <v>光属性耐性+20%</v>
+            <v>氷属性耐性+20%</v>
           </cell>
         </row>
         <row r="402">
           <cell r="A402">
-            <v>506060</v>
+            <v>506050</v>
           </cell>
           <cell r="B402" t="str">
-            <v>闇属性耐性+20%</v>
+            <v>光属性耐性+20%</v>
           </cell>
         </row>
         <row r="403">
           <cell r="A403">
-            <v>507010</v>
+            <v>506060</v>
           </cell>
           <cell r="B403" t="str">
-            <v>獲得Exp+30%</v>
+            <v>闇属性耐性+20%</v>
           </cell>
         </row>
         <row r="404">
           <cell r="A404">
+            <v>507010</v>
+          </cell>
+          <cell r="B404" t="str">
+            <v>獲得Exp+30%</v>
+          </cell>
+        </row>
+        <row r="405">
+          <cell r="A405">
             <v>507020</v>
           </cell>
-          <cell r="B404" t="str">
+          <cell r="B405" t="str">
             <v>ATK⇔DEF交換</v>
           </cell>
         </row>
@@ -6061,13 +6069,13 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="H23">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I23">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -6082,19 +6090,19 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>110</v>
+        <v>45</v>
       </c>
       <c r="Q23">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="R23">
-        <v>80</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:18">
